--- a/inst/extdata/adam-spec.xlsx
+++ b/inst/extdata/adam-spec.xlsx
@@ -14,6 +14,10 @@
     <sheet name="Methods" sheetId="5" r:id="rId5"/>
     <sheet name="Comments" sheetId="6" r:id="rId6"/>
     <sheet name="Documents" sheetId="7" r:id="rId7"/>
+    <sheet name="WhereClauses" sheetId="8" r:id="rId8"/>
+    <sheet name="Standards" sheetId="9" r:id="rId9"/>
+    <sheet name="Analysis Displays" sheetId="10" r:id="rId10"/>
+    <sheet name="Analysis Results" sheetId="11" r:id="rId11"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -357,7 +361,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -387,36 +391,400 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>StudyName</t>
+          <t>study_oid</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CDISC-Sample</t>
+          <t>STDY.www.cdisc.org/CDISC-Sample/ADaM</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>StudyDescription</t>
+          <t>file_oid</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CDISC-Sample Data Definition</t>
+          <t>www.cdisc.org/CDISC-Sample/ADaM/1/Define-XML_2.1.0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>odm_context</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Submission</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>metadata_version_oid</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>MDV.CDISC01.ADaMIG.1.1.ADaM.2.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>metadata_version_name</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Study CDISC-Sample, Data Definitions</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>metadata_version_description</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Study CDISC-Sample, Data Definitions</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>originator</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CDISC Data Exchange Standards Team</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>StudyName</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CDISC-Sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>StudyDescription</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CDISC-Sample Data Definition</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>ProtocolName</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>CDISC-Sample</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>RD.Table_14-5.02</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Table 14-5.02</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Incidence of Treatment Emergent Serious Adverse Events by Treatment Group</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>LF.CSR</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:O3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Display</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Reason</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Purpose</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Variables</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Where Clause</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Join Comment</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Documentation Refs</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Programming Context</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Programming Code</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Programming Document</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>RD.Table_14-5.02</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>AR.Table_14-5.02.R.1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Incidence of Treatment Emergent Serious Adverse Events by Treatment Group</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>SPECIFIED IN SAP</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>PRIMARY OUTCOME MEASURE</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>ADAE</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>AEBODSYS AEDECOD</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>WC.Table_14-5.02.R.1.ADAE</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>COM.JOIN-ADSL-ADAE</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Unique count of subjects that experienced an Adverse Event by Preferred Term, System Organ Class, and Treatment Group and percentages based on the number of subjects in the safety population within each treatment group. The total number of times an event occurred was recorded by Preferred Term, System Organ Class, and Treatment Group. Fisher's exact test was used for treatment comparison of event rates.</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>LF.CSR</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>SAS version 9.2</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>LF.at14-5-02.sas</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>RD.Table_14-5.02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>AR.Table_14-5.02.R.1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Incidence of Treatment Emergent Serious Adverse Events by Treatment Group</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>SPECIFIED IN SAP</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>PRIMARY OUTCOME MEASURE</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>ADSL</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>WC.Table_14-5.02.R.1.ADSL</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>COM.JOIN-ADSL-ADAE</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Unique count of subjects that experienced an Adverse Event by Preferred Term, System Organ Class, and Treatment Group and percentages based on the number of subjects in the safety population within each treatment group. The total number of times an event occurred was recorded by Preferred Term, System Organ Class, and Treatment Group. Fisher's exact test was used for treatment comparison of event rates.</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>LF.CSR</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>SAS version 9.2</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>LF.at14-5-02.sas</t>
         </is>
       </c>
     </row>
@@ -427,7 +795,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -471,6 +839,36 @@
           <t>Comment</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>SAS Dataset Name</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Purpose</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Repeating</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Reference Data</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Has No Data</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -508,6 +906,26 @@
           <t>COM.ADSL</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>ADSL</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Analysis</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -525,6 +943,11 @@
           <t>OCCURRENCE DATA STRUCTURE</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ADVERSE EVENT</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>one record per subject per adverse event</t>
@@ -543,6 +966,26 @@
       <c r="H3" t="inlineStr">
         <is>
           <t>COM.ADAE</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ADAE</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Analysis</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -553,7 +996,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R105"/>
+  <dimension ref="A1:U105"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -624,27 +1067,42 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>Origin Document</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>Pages</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Method</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Predecessor</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Comment</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>SAS Field Name</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Has No Data</t>
         </is>
       </c>
     </row>
@@ -669,7 +1127,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F2">
@@ -683,6 +1141,11 @@
       <c r="L2" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>STUDYID</t>
         </is>
       </c>
     </row>
@@ -707,7 +1170,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F3">
@@ -721,6 +1184,11 @@
       <c r="L3" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>USUBJID</t>
         </is>
       </c>
     </row>
@@ -745,7 +1213,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F4">
@@ -759,6 +1227,11 @@
       <c r="L4" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>SUBJID</t>
         </is>
       </c>
     </row>
@@ -783,7 +1256,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F5">
@@ -797,6 +1270,11 @@
       <c r="L5" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>SITEID</t>
         </is>
       </c>
     </row>
@@ -821,7 +1299,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F6">
@@ -837,9 +1315,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>MT.ADSL.SITEGR1</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>SITEGR1</t>
         </is>
       </c>
     </row>
@@ -864,7 +1352,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F7">
@@ -883,6 +1371,11 @@
       <c r="L7" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>ARM</t>
         </is>
       </c>
     </row>
@@ -907,7 +1400,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F8">
@@ -926,6 +1419,11 @@
       <c r="L8" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>TRT01P</t>
         </is>
       </c>
     </row>
@@ -971,9 +1469,19 @@
           <t>Assigned</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>COM.ADSL.TRT01PN</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>TRT01PN</t>
         </is>
       </c>
     </row>
@@ -998,7 +1506,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F10">
@@ -1019,9 +1527,19 @@
           <t>Assigned</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>COM.ADSL.TRT01A</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>TRT01A</t>
         </is>
       </c>
     </row>
@@ -1067,9 +1585,19 @@
           <t>Assigned</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
         <is>
           <t>COM.ADSL.TRT01AN</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>TRT01AN</t>
         </is>
       </c>
     </row>
@@ -1115,9 +1643,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
         <is>
           <t>MT.ADSL.TRTSDT</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>TRTSDT</t>
         </is>
       </c>
     </row>
@@ -1163,9 +1701,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
         <is>
           <t>MT.ADSL.TRTEDT</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>TRTEDT</t>
         </is>
       </c>
     </row>
@@ -1206,9 +1754,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
         <is>
           <t>MT.ADSL.TRTDURD</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>TRTDURD</t>
         </is>
       </c>
     </row>
@@ -1257,9 +1815,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
         <is>
           <t>MT.ADSL.AVGDD</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>AVGDD</t>
         </is>
       </c>
     </row>
@@ -1308,9 +1876,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
         <is>
           <t>MT.ADSL.CUMDOSE</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>CUMDOSE</t>
         </is>
       </c>
     </row>
@@ -1351,6 +1929,11 @@
           <t>Predecessor</t>
         </is>
       </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>AGE</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18">
@@ -1373,7 +1956,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F18">
@@ -1394,9 +1977,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
         <is>
           <t>MT.ADSL.AGEGR1</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>AGEGR1</t>
         </is>
       </c>
     </row>
@@ -1442,9 +2035,19 @@
           <t>Assigned</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
         <is>
           <t>COM.ADSL.AGEGR1N</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>AGEGR1N</t>
         </is>
       </c>
     </row>
@@ -1469,7 +2072,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F20">
@@ -1488,6 +2091,11 @@
       <c r="L20" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>AGEU</t>
         </is>
       </c>
     </row>
@@ -1512,7 +2120,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F21">
@@ -1531,6 +2139,11 @@
       <c r="L21" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>RACE</t>
         </is>
       </c>
     </row>
@@ -1576,9 +2189,19 @@
           <t>Assigned</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
         <is>
           <t>COM.ADSL.RACEN</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>RACEN</t>
         </is>
       </c>
     </row>
@@ -1603,7 +2226,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F23">
@@ -1622,6 +2245,11 @@
       <c r="L23" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>SEX</t>
         </is>
       </c>
     </row>
@@ -1646,7 +2274,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F24">
@@ -1665,6 +2293,11 @@
       <c r="L24" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>ETHNIC</t>
         </is>
       </c>
     </row>
@@ -1689,7 +2322,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F25">
@@ -1710,9 +2343,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
         <is>
           <t>MT.ADSL.SAFFL</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>SAFFL</t>
         </is>
       </c>
     </row>
@@ -1737,7 +2380,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F26">
@@ -1758,9 +2401,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
         <is>
           <t>MT.ADSL.ITTFL</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>ITTFL</t>
         </is>
       </c>
     </row>
@@ -1785,7 +2438,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F27">
@@ -1806,9 +2459,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
         <is>
           <t>MT.ADSL.EFFFL</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>EFFFL</t>
         </is>
       </c>
     </row>
@@ -1833,7 +2496,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F28">
@@ -1854,9 +2517,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
         <is>
           <t>MT.ADSL.COMP8FL</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>COMP8FL</t>
         </is>
       </c>
     </row>
@@ -1881,7 +2554,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F29">
@@ -1902,9 +2575,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
         <is>
           <t>MT.ADSL.COMP16FL</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>COMP16FL</t>
         </is>
       </c>
     </row>
@@ -1929,7 +2612,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F30">
@@ -1950,9 +2633,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
         <is>
           <t>MT.ADSL.COMP24FL</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>COMP24FL</t>
         </is>
       </c>
     </row>
@@ -1977,7 +2670,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F31">
@@ -1998,9 +2691,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
         <is>
           <t>MT.ADSL.DISCONFL</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>DISCONFL</t>
         </is>
       </c>
     </row>
@@ -2025,7 +2728,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F32">
@@ -2046,9 +2749,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
         <is>
           <t>MT.ADSL.DSRAEFL</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>DSRAEFL</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2786,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F33">
@@ -2092,6 +2805,11 @@
       <c r="L33" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>DTHFL</t>
         </is>
       </c>
     </row>
@@ -2140,9 +2858,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
         <is>
           <t>MT.ADSL.BMIBL</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>BMIBL</t>
         </is>
       </c>
     </row>
@@ -2167,7 +2895,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F35">
@@ -2188,9 +2916,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
         <is>
           <t>MT.ADSL.BMIBLGR1</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>BMIBLGR1</t>
         </is>
       </c>
     </row>
@@ -2239,9 +2977,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
         <is>
           <t>MT.ADSL.HEIGHTBL</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>HEIGHTBL</t>
         </is>
       </c>
     </row>
@@ -2290,9 +3038,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
         <is>
           <t>MT.ADSL.WEIGHTBL</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>WEIGHTBL</t>
         </is>
       </c>
     </row>
@@ -2333,9 +3091,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
         <is>
           <t>MT.ADSL.EDUCLVL</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>EDUCLVL</t>
         </is>
       </c>
     </row>
@@ -2381,9 +3149,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
         <is>
           <t>MT.ADSL.DISONDT</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>DISONDT</t>
         </is>
       </c>
     </row>
@@ -2432,9 +3210,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr">
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
         <is>
           <t>MT.ADSL.DURDIS</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>DURDIS</t>
         </is>
       </c>
     </row>
@@ -2459,7 +3247,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F41">
@@ -2480,9 +3268,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
         <is>
           <t>MT.ADSL.DURDSGR1</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>DURDSGR1</t>
         </is>
       </c>
     </row>
@@ -2528,9 +3326,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
         <is>
           <t>MT.ADSL.VISIT1DT</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>VISIT1DT</t>
         </is>
       </c>
     </row>
@@ -2568,6 +3376,11 @@
           <t>Predecessor</t>
         </is>
       </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>RFSTDTC</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44">
@@ -2603,6 +3416,11 @@
           <t>Predecessor</t>
         </is>
       </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>RFENDTC</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45">
@@ -2641,9 +3459,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
         <is>
           <t>MT.ADSL.VISNUMEN</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>VISNUMEN</t>
         </is>
       </c>
     </row>
@@ -2684,9 +3512,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr">
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
         <is>
           <t>MT.ADSL.RFENDT</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>RFENDT</t>
         </is>
       </c>
     </row>
@@ -2711,7 +3549,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F47">
@@ -2732,9 +3570,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr">
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
         <is>
           <t>MT.ADSL.EOSSTT</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>EOSSTT</t>
         </is>
       </c>
     </row>
@@ -2759,7 +3607,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F48">
@@ -2780,9 +3628,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr">
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
         <is>
           <t>MT.ADSL.DCSREAS</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>DCSREAS</t>
         </is>
       </c>
     </row>
@@ -2807,7 +3665,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F49">
@@ -2826,6 +3684,11 @@
       <c r="L49" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>EOSDISP</t>
         </is>
       </c>
     </row>
@@ -2866,9 +3729,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
         <is>
           <t>MT.ADSL.MMS1TSBL</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>MMS1TSBL</t>
         </is>
       </c>
     </row>
@@ -2893,7 +3766,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F51">
@@ -2907,6 +3780,11 @@
       <c r="L51" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>STUDYID</t>
         </is>
       </c>
     </row>
@@ -2931,7 +3809,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F52">
@@ -2945,6 +3823,11 @@
       <c r="L52" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>SITEID</t>
         </is>
       </c>
     </row>
@@ -2969,7 +3852,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F53">
@@ -2983,6 +3866,11 @@
       <c r="L53" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>USUBJID</t>
         </is>
       </c>
     </row>
@@ -3007,7 +3895,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F54">
@@ -3026,6 +3914,11 @@
       <c r="L54" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>TRTA</t>
         </is>
       </c>
     </row>
@@ -3071,6 +3964,11 @@
           <t>Predecessor</t>
         </is>
       </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>TRTAN</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56">
@@ -3109,6 +4007,11 @@
           <t>Predecessor</t>
         </is>
       </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>AGE</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57">
@@ -3131,7 +4034,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F57">
@@ -3150,6 +4053,11 @@
       <c r="L57" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>AGEGR1</t>
         </is>
       </c>
     </row>
@@ -3195,6 +4103,11 @@
           <t>Predecessor</t>
         </is>
       </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>AGEGR1N</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59">
@@ -3217,7 +4130,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F59">
@@ -3236,6 +4149,11 @@
       <c r="L59" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>RACE</t>
         </is>
       </c>
     </row>
@@ -3281,6 +4199,11 @@
           <t>Predecessor</t>
         </is>
       </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>RACEN</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61">
@@ -3303,7 +4226,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F61">
@@ -3322,6 +4245,11 @@
       <c r="L61" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>SEX</t>
         </is>
       </c>
     </row>
@@ -3346,7 +4274,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F62">
@@ -3365,6 +4293,11 @@
       <c r="L62" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>SAFFL</t>
         </is>
       </c>
     </row>
@@ -3410,6 +4343,11 @@
           <t>Predecessor</t>
         </is>
       </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>TRTSDT</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64">
@@ -3453,6 +4391,11 @@
           <t>Predecessor</t>
         </is>
       </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>TRTEDT</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65">
@@ -3496,9 +4439,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O65" t="inlineStr">
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
         <is>
           <t>MT.ADAE.ASTDT</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>ASTDT</t>
         </is>
       </c>
     </row>
@@ -3523,7 +4476,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F66">
@@ -3544,9 +4497,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O66" t="inlineStr">
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
         <is>
           <t>MT.ADAE.ASTDTF</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>ASTDTF</t>
         </is>
       </c>
     </row>
@@ -3587,9 +4550,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O67" t="inlineStr">
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
         <is>
           <t>MT.ADAE.ASTDY</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>ASTDY</t>
         </is>
       </c>
     </row>
@@ -3635,9 +4608,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O68" t="inlineStr">
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
         <is>
           <t>MT.ADAE.AENDT</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>AENDT</t>
         </is>
       </c>
     </row>
@@ -3678,9 +4661,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O69" t="inlineStr">
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
         <is>
           <t>MT.ADAE.AENDY</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>AENDY</t>
         </is>
       </c>
     </row>
@@ -3721,9 +4714,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O70" t="inlineStr">
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
         <is>
           <t>MT.ADAE.ADURN</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>ADURN</t>
         </is>
       </c>
     </row>
@@ -3748,7 +4751,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F71">
@@ -3764,9 +4767,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O71" t="inlineStr">
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
         <is>
           <t>MT.ADAE.ADURU</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>ADURU</t>
         </is>
       </c>
     </row>
@@ -3791,7 +4804,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F72">
@@ -3805,6 +4818,11 @@
       <c r="L72" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>AETERM</t>
         </is>
       </c>
     </row>
@@ -3829,7 +4847,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F73">
@@ -3843,6 +4861,11 @@
       <c r="L73" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>AELLT</t>
         </is>
       </c>
     </row>
@@ -3883,6 +4906,11 @@
           <t>Predecessor</t>
         </is>
       </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>AELLTCD</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75">
@@ -3905,7 +4933,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F75">
@@ -3919,6 +4947,11 @@
       <c r="L75" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>AEDECOD</t>
         </is>
       </c>
     </row>
@@ -3959,6 +4992,11 @@
           <t>Predecessor</t>
         </is>
       </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>AEPTCD</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77">
@@ -3981,7 +5019,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F77">
@@ -3995,6 +5033,11 @@
       <c r="L77" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>AEHLT</t>
         </is>
       </c>
     </row>
@@ -4035,6 +5078,11 @@
           <t>Predecessor</t>
         </is>
       </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>AEHLTCD</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79">
@@ -4057,7 +5105,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F79">
@@ -4071,6 +5119,11 @@
       <c r="L79" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>AEHLGT</t>
         </is>
       </c>
     </row>
@@ -4111,6 +5164,11 @@
           <t>Predecessor</t>
         </is>
       </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>AEHLGTCD</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81">
@@ -4133,7 +5191,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F81">
@@ -4147,6 +5205,11 @@
       <c r="L81" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>AEBODSYS</t>
         </is>
       </c>
     </row>
@@ -4171,7 +5234,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F82">
@@ -4185,6 +5248,11 @@
       <c r="L82" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>AESOC</t>
         </is>
       </c>
     </row>
@@ -4225,6 +5293,11 @@
           <t>Predecessor</t>
         </is>
       </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>AESOCCD</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84">
@@ -4247,7 +5320,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F84">
@@ -4266,6 +5339,11 @@
       <c r="L84" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>AESEV</t>
         </is>
       </c>
     </row>
@@ -4290,7 +5368,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F85">
@@ -4309,6 +5387,11 @@
       <c r="L85" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>AESER</t>
         </is>
       </c>
     </row>
@@ -4333,7 +5416,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F86">
@@ -4352,6 +5435,11 @@
       <c r="L86" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>AESCAN</t>
         </is>
       </c>
     </row>
@@ -4376,7 +5464,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F87">
@@ -4395,6 +5483,11 @@
       <c r="L87" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>AESCONG</t>
         </is>
       </c>
     </row>
@@ -4419,7 +5512,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F88">
@@ -4438,6 +5531,11 @@
       <c r="L88" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>AESDISAB</t>
         </is>
       </c>
     </row>
@@ -4462,7 +5560,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F89">
@@ -4481,6 +5579,11 @@
       <c r="L89" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>AESDTH</t>
         </is>
       </c>
     </row>
@@ -4505,7 +5608,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F90">
@@ -4524,6 +5627,11 @@
       <c r="L90" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>AESHOSP</t>
         </is>
       </c>
     </row>
@@ -4548,7 +5656,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F91">
@@ -4567,6 +5675,11 @@
       <c r="L91" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>AESLIFE</t>
         </is>
       </c>
     </row>
@@ -4591,7 +5704,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F92">
@@ -4610,6 +5723,11 @@
       <c r="L92" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>AESOD</t>
         </is>
       </c>
     </row>
@@ -4634,7 +5752,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F93">
@@ -4653,6 +5771,11 @@
       <c r="L93" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>AEREL</t>
         </is>
       </c>
     </row>
@@ -4677,7 +5800,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F94">
@@ -4691,6 +5814,11 @@
       <c r="L94" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>AEACN</t>
         </is>
       </c>
     </row>
@@ -4715,7 +5843,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F95">
@@ -4734,6 +5862,11 @@
       <c r="L95" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>AEOUT</t>
         </is>
       </c>
     </row>
@@ -4774,6 +5907,11 @@
           <t>Predecessor</t>
         </is>
       </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>AESEQ</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97">
@@ -4796,7 +5934,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F97">
@@ -4817,9 +5955,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O97" t="inlineStr">
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
         <is>
           <t>MT.ADAE.TRTEMFL</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>TRTEMFL</t>
         </is>
       </c>
     </row>
@@ -4844,7 +5992,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F98">
@@ -4865,9 +6013,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O98" t="inlineStr">
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
         <is>
           <t>MT.ADAE.AOCCFL</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>AOCCFL</t>
         </is>
       </c>
     </row>
@@ -4892,7 +6050,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F99">
@@ -4913,9 +6071,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O99" t="inlineStr">
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
         <is>
           <t>MT.ADAE.AOCCSFL</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>AOCCSFL</t>
         </is>
       </c>
     </row>
@@ -4940,7 +6108,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F100">
@@ -4961,9 +6129,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O100" t="inlineStr">
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
         <is>
           <t>MT.ADAE.AOCCPFL</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>AOCCPFL</t>
         </is>
       </c>
     </row>
@@ -4988,7 +6166,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F101">
@@ -5009,9 +6187,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O101" t="inlineStr">
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
         <is>
           <t>MT.ADAE.AOCC02FL</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>AOCC02FL</t>
         </is>
       </c>
     </row>
@@ -5036,7 +6224,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F102">
@@ -5057,9 +6245,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O102" t="inlineStr">
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
         <is>
           <t>MT.ADAE.AOCC03FL</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>AOCC03FL</t>
         </is>
       </c>
     </row>
@@ -5084,7 +6282,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F103">
@@ -5105,9 +6303,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O103" t="inlineStr">
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
         <is>
           <t>MT.ADAE.AOCC04FL</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>AOCC04FL</t>
         </is>
       </c>
     </row>
@@ -5132,7 +6340,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F104">
@@ -5148,9 +6356,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O104" t="inlineStr">
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
         <is>
           <t>MT.ADAE.CQ01NAM</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>CQ01NAM</t>
         </is>
       </c>
     </row>
@@ -5175,7 +6393,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F105">
@@ -5196,9 +6414,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O105" t="inlineStr">
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
         <is>
           <t>MT.ADAE.AOCC01FL</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>AOCC01FL</t>
         </is>
       </c>
     </row>
@@ -5209,7 +6437,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D202"/>
+  <dimension ref="A1:J202"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -5233,6 +6461,36 @@
           <t>Decoded Value</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>NCI Codelist Code</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>SAS Format Name</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>NCI Term Code</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5245,6 +6503,19 @@
           <t>&lt;65</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Age Group</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5257,6 +6528,19 @@
           <t>65-80</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Age Group</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5269,6 +6553,19 @@
           <t>&gt;80</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Age Group</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="J4">
+        <v>3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5289,6 +6586,16 @@
           <t>&lt;65</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Age Group (N)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5309,6 +6616,16 @@
           <t>65-80</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Age Group (N)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5329,6 +6646,16 @@
           <t>&gt;80</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Age Group (N)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5341,6 +6668,26 @@
           <t>YEARS</t>
         </is>
       </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Age Unit</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>C66781</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>C29848</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5356,6 +6703,16 @@
           <t>Placebo</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Actual Treatment</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5371,6 +6728,16 @@
           <t>Xanomeline Low Dose</t>
         </is>
       </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Actual Treatment</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5386,6 +6753,16 @@
           <t>Xanomeline High Dose</t>
         </is>
       </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Actual Treatment</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5406,6 +6783,16 @@
           <t>Placebo</t>
         </is>
       </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Actual Treatment (N)</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5426,6 +6813,16 @@
           <t>Xanomeline Low Dose</t>
         </is>
       </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Actual Treatment (N)</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5446,6 +6843,16 @@
           <t>Xanomeline High Dose</t>
         </is>
       </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Actual Treatment (N)</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5461,6 +6868,16 @@
           <t>Baseline</t>
         </is>
       </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Analysis Visit</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -5476,6 +6893,16 @@
           <t>Week 8</t>
         </is>
       </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Analysis Visit</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -5491,6 +6918,16 @@
           <t>Week 16</t>
         </is>
       </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Analysis Visit</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -5506,6 +6943,16 @@
           <t>Week 24</t>
         </is>
       </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Analysis Visit</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -5526,6 +6973,16 @@
           <t>Baseline</t>
         </is>
       </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Analysis Visit (N)</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -5546,6 +7003,16 @@
           <t>Week 8</t>
         </is>
       </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Analysis Visit (N)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -5566,6 +7033,16 @@
           <t>Week 16</t>
         </is>
       </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Analysis Visit (N)</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -5586,6 +7063,16 @@
           <t>Week 24</t>
         </is>
       </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Analysis Visit (N)</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -5598,6 +7085,26 @@
           <t>DAYS</t>
         </is>
       </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Unit - AWU</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>C71620</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>C25301</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -5615,6 +7122,19 @@
           <t>Normal</t>
         </is>
       </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Body Mass Index Category</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="J24">
+        <v>1</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -5632,6 +7152,19 @@
           <t>Overweight</t>
         </is>
       </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Body Mass Index Category</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="J25">
+        <v>2</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -5649,6 +7182,19 @@
           <t>Obese</t>
         </is>
       </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Body Mass Index Category</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="J26">
+        <v>3</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -5669,6 +7215,26 @@
           <t>Day Imputed: Day is imputed</t>
         </is>
       </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Date Imputation Flag</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>C81223</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>C81212</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -5689,6 +7255,26 @@
           <t>Month Imputed: Month and day are imputed</t>
         </is>
       </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Date Imputation Flag</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>C81223</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>C81211</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -5709,6 +7295,26 @@
           <t>Year Imputed: Entire date (year, month and day) is imputed</t>
         </is>
       </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Date Imputation Flag</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>C81223</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>C81210</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -5724,6 +7330,26 @@
           <t>COMPLETED</t>
         </is>
       </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Completion/Reason for Non-Completion</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>C66727</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>C25250</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -5739,6 +7365,26 @@
           <t>ADVERSE EVENT</t>
         </is>
       </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Completion/Reason for Non-Completion</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>C66727</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>C41331</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -5754,6 +7400,26 @@
           <t>DEATH</t>
         </is>
       </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Completion/Reason for Non-Completion</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>C66727</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>C28554</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -5769,6 +7435,26 @@
           <t>LACK OF EFFICACY</t>
         </is>
       </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Completion/Reason for Non-Completion</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>C66727</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>C48226</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -5784,6 +7470,26 @@
           <t>LOST TO FOLLOW-UP</t>
         </is>
       </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Completion/Reason for Non-Completion</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>C66727</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>C48227</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -5799,6 +7505,26 @@
           <t>PHYSICIAN DECISION</t>
         </is>
       </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Completion/Reason for Non-Completion</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>C66727</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>C48250</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -5814,6 +7540,26 @@
           <t>PROTOCOL VIOLATION</t>
         </is>
       </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Completion/Reason for Non-Completion</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>C66727</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>C142185</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -5829,6 +7575,26 @@
           <t>STUDY TERMINATED BY SPONSOR</t>
         </is>
       </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Completion/Reason for Non-Completion</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>C66727</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>C49632</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -5844,6 +7610,26 @@
           <t>WITHDRAWAL BY SUBJECT</t>
         </is>
       </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Completion/Reason for Non-Completion</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>C66727</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>C49634</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -5859,6 +7645,16 @@
           <t>Completed</t>
         </is>
       </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Reason for Discontinuation</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -5874,6 +7670,16 @@
           <t>Adverse Event</t>
         </is>
       </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Reason for Discontinuation</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -5889,6 +7695,16 @@
           <t>Death</t>
         </is>
       </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Reason for Discontinuation</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -5904,6 +7720,16 @@
           <t>I/E Not Met</t>
         </is>
       </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Reason for Discontinuation</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -5919,6 +7745,16 @@
           <t>Lack of Efficacy</t>
         </is>
       </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Reason for Discontinuation</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -5934,6 +7770,16 @@
           <t>Lost to Follow-up</t>
         </is>
       </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Reason for Discontinuation</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -5949,6 +7795,16 @@
           <t>Physician Decision</t>
         </is>
       </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Reason for Discontinuation</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -5964,6 +7820,16 @@
           <t>Protocol Violation</t>
         </is>
       </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Reason for Discontinuation</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -5979,6 +7845,16 @@
           <t>Sponsor Decision</t>
         </is>
       </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Reason for Discontinuation</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5994,6 +7870,16 @@
           <t>Withdrew Consent</t>
         </is>
       </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Reason for Discontinuation</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -6011,6 +7897,26 @@
           <t>Last Observation Carried Forward</t>
         </is>
       </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Derivation Type</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>C81224</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>C81198</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -6023,6 +7929,19 @@
           <t>&lt;12</t>
         </is>
       </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Disease Duration Group</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="J50">
+        <v>1</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -6035,6 +7954,19 @@
           <t>&gt;=12</t>
         </is>
       </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Disease Duration Group</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="J51">
+        <v>2</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -6047,6 +7979,26 @@
           <t>COMPLETED</t>
         </is>
       </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Subject Trial Status</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>C124296</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>C25250</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -6059,6 +8011,26 @@
           <t>DISCONTINUED</t>
         </is>
       </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Subject Trial Status</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>C124296</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>C25484</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -6071,6 +8043,26 @@
           <t>HISPANIC OR LATINO</t>
         </is>
       </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Ethnic Group</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>C66790</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>C17459</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -6083,6 +8075,26 @@
           <t>NOT HISPANIC OR LATINO</t>
         </is>
       </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Ethnic Group</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>C66790</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>C41222</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -6103,6 +8115,16 @@
           <t>Word Recall Task</t>
         </is>
       </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>ADAS-Cog Parameter Code</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -6123,6 +8145,16 @@
           <t>Naming Objects And Fingers (Refer To 5 C</t>
         </is>
       </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>ADAS-Cog Parameter Code</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -6143,6 +8175,16 @@
           <t>Delayed Word Recall</t>
         </is>
       </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>ADAS-Cog Parameter Code</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -6163,6 +8205,16 @@
           <t>Commands</t>
         </is>
       </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>ADAS-Cog Parameter Code</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -6183,6 +8235,16 @@
           <t>Constructional Praxis</t>
         </is>
       </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>ADAS-Cog Parameter Code</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -6203,6 +8265,16 @@
           <t>Ideational Praxis</t>
         </is>
       </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>ADAS-Cog Parameter Code</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -6223,6 +8295,16 @@
           <t>Orientation</t>
         </is>
       </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>ADAS-Cog Parameter Code</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -6243,6 +8325,16 @@
           <t>Word Recognition</t>
         </is>
       </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>ADAS-Cog Parameter Code</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -6263,6 +8355,16 @@
           <t>Attention/Visual Search Task</t>
         </is>
       </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>ADAS-Cog Parameter Code</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -6283,6 +8385,16 @@
           <t>Maze Solution</t>
         </is>
       </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>ADAS-Cog Parameter Code</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -6303,6 +8415,16 @@
           <t>Spoken Language Ability</t>
         </is>
       </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>ADAS-Cog Parameter Code</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -6323,6 +8445,16 @@
           <t>Comprehension Of Spoken Language</t>
         </is>
       </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>ADAS-Cog Parameter Code</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -6343,6 +8475,16 @@
           <t>Word Finding Difficulty In Spontaneous Speech</t>
         </is>
       </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>ADAS-Cog Parameter Code</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -6363,6 +8505,16 @@
           <t>Recall Of Test Instructions</t>
         </is>
       </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>ADAS-Cog Parameter Code</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -6383,6 +8535,16 @@
           <t>Adas-Cog(11) Subscore</t>
         </is>
       </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>ADAS-Cog Parameter Code</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -6403,6 +8565,16 @@
           <t>Word Recall Task</t>
         </is>
       </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>ADAS-Cog Parameter Code (N)</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -6423,6 +8595,16 @@
           <t>Naming Objects And Fingers (Refer To 5 C</t>
         </is>
       </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>ADAS-Cog Parameter Code (N)</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -6443,6 +8625,16 @@
           <t>Delayed Word Recall</t>
         </is>
       </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>ADAS-Cog Parameter Code (N)</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -6463,6 +8655,16 @@
           <t>Commands</t>
         </is>
       </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>ADAS-Cog Parameter Code (N)</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -6483,6 +8685,16 @@
           <t>Constructional Praxis</t>
         </is>
       </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>ADAS-Cog Parameter Code (N)</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -6503,6 +8715,16 @@
           <t>Ideational Praxis</t>
         </is>
       </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>ADAS-Cog Parameter Code (N)</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -6523,6 +8745,16 @@
           <t>Orientation</t>
         </is>
       </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>ADAS-Cog Parameter Code (N)</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -6543,6 +8775,16 @@
           <t>Word Recognition</t>
         </is>
       </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>ADAS-Cog Parameter Code (N)</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -6563,6 +8805,16 @@
           <t>Attention/Visual Search Task</t>
         </is>
       </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>ADAS-Cog Parameter Code (N)</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -6583,6 +8835,16 @@
           <t>Maze Solution</t>
         </is>
       </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>ADAS-Cog Parameter Code (N)</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -6603,6 +8865,16 @@
           <t>Spoken Language Ability</t>
         </is>
       </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>ADAS-Cog Parameter Code (N)</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -6623,6 +8895,16 @@
           <t>Comprehension Of Spoken Language</t>
         </is>
       </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>ADAS-Cog Parameter Code (N)</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -6643,6 +8925,16 @@
           <t>Word Finding Difficulty In Spontaneous S</t>
         </is>
       </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>ADAS-Cog Parameter Code (N)</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -6663,6 +8955,16 @@
           <t>Recall Of Test Instructions</t>
         </is>
       </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>ADAS-Cog Parameter Code (N)</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -6683,6 +8985,16 @@
           <t>Adas-Cog(11) Subscore</t>
         </is>
       </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>ADAS-Cog Parameter Code (N)</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -6698,6 +9010,16 @@
           <t>Word Recall Task</t>
         </is>
       </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>ADAS-Cog Parameter</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -6713,6 +9035,16 @@
           <t>Naming Objects And Fingers (Refer To 5 C</t>
         </is>
       </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>ADAS-Cog Parameter</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -6728,6 +9060,16 @@
           <t>Delayed Word Recall</t>
         </is>
       </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>ADAS-Cog Parameter</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -6743,6 +9085,16 @@
           <t>Commands</t>
         </is>
       </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>ADAS-Cog Parameter</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -6758,6 +9110,16 @@
           <t>Constructional Praxis</t>
         </is>
       </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>ADAS-Cog Parameter</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -6773,6 +9135,16 @@
           <t>Ideational Praxis</t>
         </is>
       </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>ADAS-Cog Parameter</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -6788,6 +9160,16 @@
           <t>Orientation</t>
         </is>
       </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>ADAS-Cog Parameter</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -6803,6 +9185,16 @@
           <t>Word Recognition</t>
         </is>
       </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>ADAS-Cog Parameter</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -6818,6 +9210,16 @@
           <t>Attention/Visual Search Task</t>
         </is>
       </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>ADAS-Cog Parameter</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -6833,6 +9235,16 @@
           <t>Maze Solution</t>
         </is>
       </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>ADAS-Cog Parameter</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -6848,6 +9260,16 @@
           <t>Spoken Language Ability</t>
         </is>
       </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>ADAS-Cog Parameter</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -6863,6 +9285,16 @@
           <t>Comprehension Of Spoken Language</t>
         </is>
       </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>ADAS-Cog Parameter</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -6878,6 +9310,16 @@
           <t>Word Finding Difficulty In Spontaneous S</t>
         </is>
       </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>ADAS-Cog Parameter</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -6893,6 +9335,16 @@
           <t>Recall Of Test Instructions</t>
         </is>
       </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>ADAS-Cog Parameter</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -6908,6 +9360,16 @@
           <t>Adas-Cog(11) Subscore</t>
         </is>
       </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>ADAS-Cog Parameter</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6923,6 +9385,16 @@
           <t>&lt;=1</t>
         </is>
       </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Analysis Window Range</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -6938,6 +9410,16 @@
           <t>2-84</t>
         </is>
       </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Analysis Window Range</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -6953,6 +9435,16 @@
           <t>85-140</t>
         </is>
       </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Analysis Window Range</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -6968,6 +9460,16 @@
           <t>&gt;140</t>
         </is>
       </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Analysis Window Range</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -6983,6 +9485,26 @@
           <t>WHITE</t>
         </is>
       </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>C74457</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>C41261</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -6998,6 +9520,26 @@
           <t>BLACK OR AFRICAN AMERICAN</t>
         </is>
       </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>C74457</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>C16352</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -7013,6 +9555,26 @@
           <t>ASIAN</t>
         </is>
       </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>C74457</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>C41260</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -7028,6 +9590,26 @@
           <t>AMERICAN INDIAN OR ALASKA NATIVE</t>
         </is>
       </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>C74457</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>C41259</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -7045,6 +9627,16 @@
           <t>WHITE</t>
         </is>
       </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Race (N)</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -7062,6 +9654,16 @@
           <t>BLACK OR AFRICAN AMERICAN</t>
         </is>
       </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Race (N)</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -7079,6 +9681,16 @@
           <t>AMERICAN INDIAN OR ALASKA NATIVE</t>
         </is>
       </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Race (N)</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -7096,6 +9708,16 @@
           <t>ASIAN</t>
         </is>
       </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Race (N)</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -7113,6 +9735,26 @@
           <t>Female</t>
         </is>
       </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Sex</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>C66731</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>C16576</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -7130,6 +9772,26 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Sex</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>C66731</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>C20197</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -7147,6 +9809,26 @@
           <t>Unknown</t>
         </is>
       </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Sex</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>C66731</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>C17998</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -7162,6 +9844,16 @@
           <t>SCREENING 1</t>
         </is>
       </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Visit</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -7177,6 +9869,16 @@
           <t>UNSCHEDULED 1.1</t>
         </is>
       </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Visit</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -7192,6 +9894,16 @@
           <t>UNSCHEDULED 1.2</t>
         </is>
       </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Visit</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -7207,6 +9919,16 @@
           <t>UNSCHEDULED 1.3</t>
         </is>
       </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Visit</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -7222,6 +9944,16 @@
           <t>SCREENING 2</t>
         </is>
       </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Visit</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -7237,6 +9969,16 @@
           <t>BASELINE</t>
         </is>
       </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Visit</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -7252,6 +9994,16 @@
           <t>UNSCHEDULED 3.1</t>
         </is>
       </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Visit</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -7267,6 +10019,16 @@
           <t>AMBUL ECG PLACEMENT</t>
         </is>
       </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Visit</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -7282,6 +10044,16 @@
           <t>WEEK 2</t>
         </is>
       </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Visit</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -7297,6 +10069,16 @@
           <t>UNSCHEDULED 4.1</t>
         </is>
       </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Visit</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -7312,6 +10094,16 @@
           <t>UNSCHEDULED 4.2</t>
         </is>
       </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Visit</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -7327,6 +10119,16 @@
           <t>WEEK 4</t>
         </is>
       </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Visit</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -7342,6 +10144,16 @@
           <t>UNSCHEDULED 5.1</t>
         </is>
       </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Visit</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -7357,6 +10169,16 @@
           <t>AMBUL ECG REMOVAL</t>
         </is>
       </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Visit</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -7372,6 +10194,16 @@
           <t>UNSCHEDULED 6.1</t>
         </is>
       </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Visit</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -7387,6 +10219,16 @@
           <t>WEEK 6</t>
         </is>
       </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Visit</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -7402,6 +10244,16 @@
           <t>UNSCHEDULED 7.1</t>
         </is>
       </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Visit</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -7417,6 +10269,16 @@
           <t>WEEK 8</t>
         </is>
       </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Visit</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -7432,6 +10294,16 @@
           <t>WEEK 10 (T)</t>
         </is>
       </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Visit</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -7447,6 +10319,16 @@
           <t>UNSCHEDULED 8.2</t>
         </is>
       </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Visit</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -7462,6 +10344,16 @@
           <t>WEEK 12</t>
         </is>
       </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Visit</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -7477,6 +10369,16 @@
           <t>WEEK 14 (T)</t>
         </is>
       </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Visit</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -7492,6 +10394,16 @@
           <t>UNSCHEDULED 9.2</t>
         </is>
       </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Visit</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -7507,6 +10419,16 @@
           <t>UNSCHEDULED 9.3</t>
         </is>
       </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Visit</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -7522,6 +10444,16 @@
           <t>WEEK 16</t>
         </is>
       </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Visit</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -7537,6 +10469,16 @@
           <t>WEEK 18 (T)</t>
         </is>
       </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Visit</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -7552,6 +10494,16 @@
           <t>UNSCHEDULED 10.2</t>
         </is>
       </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Visit</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -7567,6 +10519,16 @@
           <t>WEEK 20</t>
         </is>
       </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Visit</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -7582,6 +10544,16 @@
           <t>WEEK 22 (T)</t>
         </is>
       </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Visit</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -7597,6 +10569,16 @@
           <t>UNSCHEDULED 11.2</t>
         </is>
       </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Visit</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -7612,6 +10594,16 @@
           <t>WEEK 24</t>
         </is>
       </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Visit</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -7627,6 +10619,16 @@
           <t>UNSCHEDULED 12.1</t>
         </is>
       </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Visit</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -7642,6 +10644,16 @@
           <t>WEEK 26</t>
         </is>
       </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Visit</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -7657,6 +10669,16 @@
           <t>UNSCHEDULED 13.1</t>
         </is>
       </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Visit</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -7672,6 +10694,16 @@
           <t>AE FOLLOW-UP</t>
         </is>
       </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Visit</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -7687,6 +10719,16 @@
           <t>RETRIEVAL</t>
         </is>
       </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Visit</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -7702,6 +10744,16 @@
           <t>Rash followup</t>
         </is>
       </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Visit</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -7722,6 +10774,16 @@
           <t>SCREENING 1</t>
         </is>
       </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Visit Number</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -7742,6 +10804,16 @@
           <t>UNSCHEDULED 1.1</t>
         </is>
       </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Visit Number</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -7762,6 +10834,16 @@
           <t>UNSCHEDULED 1.2</t>
         </is>
       </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Visit Number</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -7782,6 +10864,16 @@
           <t>UNSCHEDULED 1.3</t>
         </is>
       </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Visit Number</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -7802,6 +10894,16 @@
           <t>SCREENING 2</t>
         </is>
       </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Visit Number</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -7822,6 +10924,16 @@
           <t>BASELINE</t>
         </is>
       </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Visit Number</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -7842,6 +10954,16 @@
           <t>UNSCHEDULED 3.1</t>
         </is>
       </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Visit Number</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -7862,6 +10984,16 @@
           <t>AMBUL ECG PLACEMENT</t>
         </is>
       </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Visit Number</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -7882,6 +11014,16 @@
           <t>WEEK 2</t>
         </is>
       </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Visit Number</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -7902,6 +11044,16 @@
           <t>UNSCHEDULED 4.1</t>
         </is>
       </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Visit Number</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -7922,6 +11074,16 @@
           <t>UNSCHEDULED 4.2</t>
         </is>
       </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Visit Number</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -7942,6 +11104,16 @@
           <t>WEEK 4</t>
         </is>
       </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Visit Number</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -7962,6 +11134,16 @@
           <t>UNSCHEDULED 5.1</t>
         </is>
       </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Visit Number</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -7982,6 +11164,16 @@
           <t>AMBUL ECG REMOVAL</t>
         </is>
       </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Visit Number</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -8002,6 +11194,16 @@
           <t>UNSCHEDULED 6.1</t>
         </is>
       </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Visit Number</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -8022,6 +11224,16 @@
           <t>WEEK 6</t>
         </is>
       </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Visit Number</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -8042,6 +11254,16 @@
           <t>UNSCHEDULED 7.1</t>
         </is>
       </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Visit Number</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -8062,6 +11284,16 @@
           <t>WEEK 8</t>
         </is>
       </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Visit Number</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -8082,6 +11314,16 @@
           <t>WEEK 10 (T)</t>
         </is>
       </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Visit Number</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -8102,6 +11344,16 @@
           <t>UNSCHEDULED 8.2</t>
         </is>
       </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Visit Number</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -8122,6 +11374,16 @@
           <t>WEEK 12</t>
         </is>
       </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Visit Number</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -8142,6 +11404,16 @@
           <t>WEEK 14 (T)</t>
         </is>
       </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Visit Number</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -8162,6 +11434,16 @@
           <t>UNSCHEDULED 9.2</t>
         </is>
       </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Visit Number</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -8182,6 +11464,16 @@
           <t>UNSCHEDULED 9.3</t>
         </is>
       </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Visit Number</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -8202,6 +11494,16 @@
           <t>WEEK 16</t>
         </is>
       </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Visit Number</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -8222,6 +11524,16 @@
           <t>WEEK 18 (T)</t>
         </is>
       </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Visit Number</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -8242,6 +11554,16 @@
           <t>UNSCHEDULED 10.2</t>
         </is>
       </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Visit Number</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -8262,6 +11584,16 @@
           <t>WEEK 20</t>
         </is>
       </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Visit Number</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -8282,6 +11614,16 @@
           <t>WEEK 22 (T)</t>
         </is>
       </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Visit Number</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -8302,6 +11644,16 @@
           <t>UNSCHEDULED 11.2</t>
         </is>
       </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Visit Number</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -8322,6 +11674,16 @@
           <t>WEEK 24</t>
         </is>
       </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Visit Number</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -8342,6 +11704,16 @@
           <t>UNSCHEDULED 12.1</t>
         </is>
       </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Visit Number</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -8362,6 +11734,16 @@
           <t>WEEK 26</t>
         </is>
       </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Visit Number</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -8382,6 +11764,16 @@
           <t>UNSCHEDULED 13.1</t>
         </is>
       </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Visit Number</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -8402,6 +11794,16 @@
           <t>AE FOLLOW-UP</t>
         </is>
       </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Visit Number</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -8422,6 +11824,16 @@
           <t>RETRIEVAL</t>
         </is>
       </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Visit Number</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -8442,6 +11854,16 @@
           <t>Rash followup</t>
         </is>
       </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Visit Number</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -8459,6 +11881,26 @@
           <t>No</t>
         </is>
       </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>No Yes Response</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>C66742</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>C49487</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -8476,6 +11918,26 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>No Yes Response</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>C66742</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>C49488</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -8493,6 +11955,26 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>No Yes Response - Y subset</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>C66742</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>C49488</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -8510,6 +11992,29 @@
           <t>Grade 1</t>
         </is>
       </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Severity/Intensity Scale for Adverse Events</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>C66769</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>C41338</t>
+        </is>
+      </c>
+      <c r="J193">
+        <v>1</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -8527,6 +12032,29 @@
           <t>Grade 2</t>
         </is>
       </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Severity/Intensity Scale for Adverse Events</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>C66769</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>C41339</t>
+        </is>
+      </c>
+      <c r="J194">
+        <v>2</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -8544,6 +12072,29 @@
           <t>Grade 3</t>
         </is>
       </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Severity/Intensity Scale for Adverse Events</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>C66769</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>C41340</t>
+        </is>
+      </c>
+      <c r="J195">
+        <v>3</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -8556,6 +12107,19 @@
           <t>NONE</t>
         </is>
       </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Causality</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="J196">
+        <v>1</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -8568,6 +12132,19 @@
           <t>POSSIBLE</t>
         </is>
       </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Causality</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="J197">
+        <v>2</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -8580,6 +12157,19 @@
           <t>PROBABLE</t>
         </is>
       </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Causality</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="J198">
+        <v>3</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -8592,6 +12182,19 @@
           <t>REMOTE</t>
         </is>
       </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Causality</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="J199">
+        <v>4</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -8604,6 +12207,26 @@
           <t>RECOVERED/RESOLVED</t>
         </is>
       </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Outcome of Adverse Event</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>C66768</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>C49498</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -8616,6 +12239,26 @@
           <t>NOT RECOVERED/NOT RESOLVED</t>
         </is>
       </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Outcome of Adverse Event</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>C66768</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>C49494</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -8626,6 +12269,26 @@
       <c r="C202" t="inlineStr">
         <is>
           <t>FATAL</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Outcome of Adverse Event</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>C66768</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>C48275</t>
         </is>
       </c>
     </row>
@@ -10204,7 +13867,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -10223,6 +13886,11 @@
           <t>Href</t>
         </is>
       </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10240,6 +13908,11 @@
           <t>adsl.xpt</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>archive</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10257,6 +13930,11 @@
           <t>adqsadas.xpt</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>archive</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10274,6 +13952,11 @@
           <t>adae.xpt</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>archive</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10291,6 +13974,11 @@
           <t>adrg.pdf</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>supplemental</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -10308,6 +13996,11 @@
           <t>../programs/adqsadas-sas.txt</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -10325,6 +14018,11 @@
           <t>../programs/adae-sas.txt</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10342,6 +14040,11 @@
           <t>../programs/adsl-sas.txt</t>
         </is>
       </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10359,6 +14062,11 @@
           <t>../dummy-csr/dummy-csr.pdf</t>
         </is>
       </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -10374,6 +14082,319 @@
       <c r="C10" t="inlineStr">
         <is>
           <t>../programs/at14-5-02-sas.txt</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Comparator</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>WC.Table_14-5.02.R.1.ADAE</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ADAE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>TRTEMFL</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>EQ</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>WC.Table_14-5.02.R.1.ADAE</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ADAE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>AESER</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>EQ</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>WC.Table_14-5.02.R.1.ADSL</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ADSL</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>SAFFL</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>EQ</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Version</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Publishing Set</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>STD.01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ADaMIG</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>IG</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>STD.CT.01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CDISC/NCI</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2017-09-29</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>ADaM</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>COM.STDCT.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>STD.CT.02</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CDISC/NCI</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2018-06-29</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>SDTM</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>COM.STDCT.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>STD.5</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CDISC/NCI</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>DEFINE-XML</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>COM.STD5</t>
         </is>
       </c>
     </row>

--- a/inst/extdata/adam-spec.xlsx
+++ b/inst/extdata/adam-spec.xlsx
@@ -6437,7 +6437,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J202"/>
+  <dimension ref="A1:J69"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -6857,237 +6857,300 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CL.AVISIT</t>
-        </is>
-      </c>
-      <c r="B15">
+          <t>CL.BMICAT</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>&lt;25</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Body Mass Index Category</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="J15">
         <v>1</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Analysis Visit</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CL.AVISIT</t>
-        </is>
-      </c>
-      <c r="B16">
+          <t>CL.BMICAT</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>25-&lt;30</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Overweight</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Body Mass Index Category</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="J16">
         <v>2</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Week 8</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Analysis Visit</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CL.AVISIT</t>
-        </is>
-      </c>
-      <c r="B17">
+          <t>CL.BMICAT</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>&gt;30</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Obese</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Body Mass Index Category</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="J17">
         <v>3</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Week 16</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Analysis Visit</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CL.AVISIT</t>
+          <t>CL.DATEFL</t>
         </is>
       </c>
       <c r="B18">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Week 24</t>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Day Imputed: Day is imputed</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Analysis Visit</t>
+          <t>Date Imputation Flag</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>text</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>C81223</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>C81212</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CL.AVISITN</t>
+          <t>CL.DATEFL</t>
         </is>
       </c>
       <c r="B19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Baseline</t>
+          <t>Month Imputed: Month and day are imputed</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Analysis Visit (N)</t>
+          <t>Date Imputation Flag</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>C81223</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>C81211</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CL.AVISITN</t>
+          <t>CL.DATEFL</t>
         </is>
       </c>
       <c r="B20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Week 8</t>
+          <t>Year Imputed: Entire date (year, month and day) is imputed</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Analysis Visit (N)</t>
+          <t>Date Imputation Flag</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>C81223</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>C81210</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CL.AVISITN</t>
+          <t>CL.DISCCD</t>
         </is>
       </c>
       <c r="B21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Week 16</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Analysis Visit (N)</t>
+          <t>Completion/Reason for Non-Completion</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>C66727</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>C25250</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CL.AVISITN</t>
+          <t>CL.DISCCD</t>
         </is>
       </c>
       <c r="B22">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Week 24</t>
+          <t>ADVERSE EVENT</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Analysis Visit (N)</t>
+          <t>Completion/Reason for Non-Completion</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>C66727</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>C41331</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CL.AWU</t>
-        </is>
+          <t>CL.DISCCD</t>
+        </is>
+      </c>
+      <c r="B23">
+        <v>3</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>DAYS</t>
+          <t>DEATH</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Unit - AWU</t>
+          <t>Completion/Reason for Non-Completion</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -7097,34 +7160,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>C71620</t>
+          <t>C66727</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>C25301</t>
+          <t>C28554</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CL.BMICAT</t>
-        </is>
+          <t>CL.DISCCD</t>
+        </is>
+      </c>
+      <c r="B24">
+        <v>4</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>&lt;25</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Normal</t>
+          <t>LACK OF EFFICACY</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Body Mass Index Category</t>
+          <t>Completion/Reason for Non-Completion</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -7132,29 +7193,34 @@
           <t>text</t>
         </is>
       </c>
-      <c r="J24">
-        <v>1</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>C66727</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>C48226</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CL.BMICAT</t>
-        </is>
+          <t>CL.DISCCD</t>
+        </is>
+      </c>
+      <c r="B25">
+        <v>5</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>25-&lt;30</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Overweight</t>
+          <t>LOST TO FOLLOW-UP</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Body Mass Index Category</t>
+          <t>Completion/Reason for Non-Completion</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -7162,29 +7228,34 @@
           <t>text</t>
         </is>
       </c>
-      <c r="J25">
-        <v>2</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>C66727</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>C48227</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CL.BMICAT</t>
-        </is>
+          <t>CL.DISCCD</t>
+        </is>
+      </c>
+      <c r="B26">
+        <v>6</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>&gt;30</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Obese</t>
+          <t>PHYSICIAN DECISION</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Body Mass Index Category</t>
+          <t>Completion/Reason for Non-Completion</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -7192,32 +7263,34 @@
           <t>text</t>
         </is>
       </c>
-      <c r="J26">
-        <v>3</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>C66727</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>C48250</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CL.DATEFL</t>
+          <t>CL.DISCCD</t>
         </is>
       </c>
       <c r="B27">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Day Imputed: Day is imputed</t>
+          <t>PROTOCOL VIOLATION</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Date Imputation Flag</t>
+          <t>Completion/Reason for Non-Completion</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -7227,37 +7300,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>C81223</t>
+          <t>C66727</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>C81212</t>
+          <t>C142185</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CL.DATEFL</t>
+          <t>CL.DISCCD</t>
         </is>
       </c>
       <c r="B28">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Month Imputed: Month and day are imputed</t>
+          <t>STUDY TERMINATED BY SPONSOR</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Date Imputation Flag</t>
+          <t>Completion/Reason for Non-Completion</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -7267,37 +7335,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>C81223</t>
+          <t>C66727</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>C81211</t>
+          <t>C49632</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CL.DATEFL</t>
+          <t>CL.DISCCD</t>
         </is>
       </c>
       <c r="B29">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Year Imputed: Entire date (year, month and day) is imputed</t>
+          <t>WITHDRAWAL BY SUBJECT</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Date Imputation Flag</t>
+          <t>Completion/Reason for Non-Completion</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -7307,19 +7370,19 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>C81223</t>
+          <t>C66727</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>C81210</t>
+          <t>C49634</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CL.DISCCD</t>
+          <t>CL.DISCREAS</t>
         </is>
       </c>
       <c r="B30">
@@ -7327,34 +7390,24 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Completion/Reason for Non-Completion</t>
+          <t>Reason for Discontinuation</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
           <t>text</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>C66727</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>C25250</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CL.DISCCD</t>
+          <t>CL.DISCREAS</t>
         </is>
       </c>
       <c r="B31">
@@ -7362,34 +7415,24 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ADVERSE EVENT</t>
+          <t>Adverse Event</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Completion/Reason for Non-Completion</t>
+          <t>Reason for Discontinuation</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
           <t>text</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>C66727</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>C41331</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CL.DISCCD</t>
+          <t>CL.DISCREAS</t>
         </is>
       </c>
       <c r="B32">
@@ -7397,34 +7440,24 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>DEATH</t>
+          <t>Death</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Completion/Reason for Non-Completion</t>
+          <t>Reason for Discontinuation</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
           <t>text</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>C66727</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>C28554</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CL.DISCCD</t>
+          <t>CL.DISCREAS</t>
         </is>
       </c>
       <c r="B33">
@@ -7432,34 +7465,24 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>LACK OF EFFICACY</t>
+          <t>I/E Not Met</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Completion/Reason for Non-Completion</t>
+          <t>Reason for Discontinuation</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
           <t>text</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>C66727</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>C48226</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CL.DISCCD</t>
+          <t>CL.DISCREAS</t>
         </is>
       </c>
       <c r="B34">
@@ -7467,34 +7490,24 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>LOST TO FOLLOW-UP</t>
+          <t>Lack of Efficacy</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Completion/Reason for Non-Completion</t>
+          <t>Reason for Discontinuation</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
           <t>text</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>C66727</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>C48227</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CL.DISCCD</t>
+          <t>CL.DISCREAS</t>
         </is>
       </c>
       <c r="B35">
@@ -7502,34 +7515,24 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>PHYSICIAN DECISION</t>
+          <t>Lost to Follow-up</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Completion/Reason for Non-Completion</t>
+          <t>Reason for Discontinuation</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
           <t>text</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>C66727</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>C48250</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CL.DISCCD</t>
+          <t>CL.DISCREAS</t>
         </is>
       </c>
       <c r="B36">
@@ -7537,34 +7540,24 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>PROTOCOL VIOLATION</t>
+          <t>Physician Decision</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Completion/Reason for Non-Completion</t>
+          <t>Reason for Discontinuation</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
           <t>text</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>C66727</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>C142185</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CL.DISCCD</t>
+          <t>CL.DISCREAS</t>
         </is>
       </c>
       <c r="B37">
@@ -7572,34 +7565,24 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>STUDY TERMINATED BY SPONSOR</t>
+          <t>Protocol Violation</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Completion/Reason for Non-Completion</t>
+          <t>Reason for Discontinuation</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
           <t>text</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>C66727</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>C49632</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CL.DISCCD</t>
+          <t>CL.DISCREAS</t>
         </is>
       </c>
       <c r="B38">
@@ -7607,27 +7590,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>WITHDRAWAL BY SUBJECT</t>
+          <t>Sponsor Decision</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Completion/Reason for Non-Completion</t>
+          <t>Reason for Discontinuation</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
           <t>text</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>C66727</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>C49634</t>
         </is>
       </c>
     </row>
@@ -7638,11 +7611,11 @@
         </is>
       </c>
       <c r="B39">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Withdrew Consent</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -7659,247 +7632,303 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CL.DISCREAS</t>
-        </is>
-      </c>
-      <c r="B40">
-        <v>2</v>
+          <t>CL.DURDISC</t>
+        </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Adverse Event</t>
+          <t>&lt;12</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Reason for Discontinuation</t>
+          <t>Disease Duration Group</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
           <t>text</t>
         </is>
+      </c>
+      <c r="J40">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CL.DISCREAS</t>
-        </is>
-      </c>
-      <c r="B41">
-        <v>3</v>
+          <t>CL.DURDISC</t>
+        </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Death</t>
+          <t>&gt;=12</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Reason for Discontinuation</t>
+          <t>Disease Duration Group</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
           <t>text</t>
         </is>
+      </c>
+      <c r="J41">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CL.DISCREAS</t>
-        </is>
-      </c>
-      <c r="B42">
-        <v>4</v>
+          <t>CL.EOSSTT</t>
+        </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>I/E Not Met</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Reason for Discontinuation</t>
+          <t>Subject Trial Status</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
           <t>text</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>C124296</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>C25250</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CL.DISCREAS</t>
-        </is>
-      </c>
-      <c r="B43">
-        <v>5</v>
+          <t>CL.EOSSTT</t>
+        </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Lack of Efficacy</t>
+          <t>DISCONTINUED</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Reason for Discontinuation</t>
+          <t>Subject Trial Status</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
           <t>text</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>C124296</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>C25484</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CL.DISCREAS</t>
-        </is>
-      </c>
-      <c r="B44">
-        <v>6</v>
+          <t>CL.ETHNIC</t>
+        </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Lost to Follow-up</t>
+          <t>HISPANIC OR LATINO</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Reason for Discontinuation</t>
+          <t>Ethnic Group</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
           <t>text</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>C66790</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>C17459</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CL.DISCREAS</t>
-        </is>
-      </c>
-      <c r="B45">
-        <v>7</v>
+          <t>CL.ETHNIC</t>
+        </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Physician Decision</t>
+          <t>NOT HISPANIC OR LATINO</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Reason for Discontinuation</t>
+          <t>Ethnic Group</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
           <t>text</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>C66790</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>C41222</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CL.DISCREAS</t>
+          <t>CL.RACE</t>
         </is>
       </c>
       <c r="B46">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Protocol Violation</t>
+          <t>WHITE</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Reason for Discontinuation</t>
+          <t>Race</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
           <t>text</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>C74457</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>C41261</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CL.DISCREAS</t>
+          <t>CL.RACE</t>
         </is>
       </c>
       <c r="B47">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sponsor Decision</t>
+          <t>BLACK OR AFRICAN AMERICAN</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Reason for Discontinuation</t>
+          <t>Race</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
           <t>text</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>C74457</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>C16352</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CL.DISCREAS</t>
+          <t>CL.RACE</t>
         </is>
       </c>
       <c r="B48">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Withdrew Consent</t>
+          <t>ASIAN</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Reason for Discontinuation</t>
+          <t>Race</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
           <t>text</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>C74457</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>C41260</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>CL.DTYPE</t>
-        </is>
+          <t>CL.RACE</t>
+        </is>
+      </c>
+      <c r="B49">
+        <v>4</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>LOCF</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Last Observation Carried Forward</t>
+          <t>AMERICAN INDIAN OR ALASKA NATIVE</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Derivation Type</t>
+          <t>Race</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -7909,143 +7938,142 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>C81224</t>
+          <t>C74457</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>C81198</t>
+          <t>C41259</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>CL.DURDISC</t>
+          <t>CL.RACEN</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>&lt;12</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>WHITE</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Disease Duration Group</t>
+          <t>Race (N)</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="J50">
-        <v>1</v>
+          <t>integer</t>
+        </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CL.DURDISC</t>
+          <t>CL.RACEN</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>&gt;=12</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>BLACK OR AFRICAN AMERICAN</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Disease Duration Group</t>
+          <t>Race (N)</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="J51">
-        <v>2</v>
+          <t>integer</t>
+        </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CL.EOSSTT</t>
+          <t>CL.RACEN</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>AMERICAN INDIAN OR ALASKA NATIVE</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Subject Trial Status</t>
+          <t>Race (N)</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>C124296</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>C25250</t>
+          <t>integer</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CL.EOSSTT</t>
+          <t>CL.RACEN</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>DISCONTINUED</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>ASIAN</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Subject Trial Status</t>
+          <t>Race (N)</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>C124296</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>C25484</t>
+          <t>integer</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CL.ETHNIC</t>
+          <t>CL.SEX</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>HISPANIC OR LATINO</t>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Female</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Ethnic Group</t>
+          <t>Sex</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -8055,29 +8083,34 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>C66790</t>
+          <t>C66731</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>C17459</t>
+          <t>C16576</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>CL.ETHNIC</t>
+          <t>CL.SEX</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>NOT HISPANIC OR LATINO</t>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Male</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Ethnic Group</t>
+          <t>Sex</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -8087,427 +8120,461 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>C66790</t>
+          <t>C66731</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>C41222</t>
+          <t>C20197</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CL.PARAMCD_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B56">
-        <v>1</v>
+          <t>CL.SEX</t>
+        </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ACITM01</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Word Recall Task</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>ADAS-Cog Parameter Code</t>
+          <t>Sex</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
           <t>text</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>C66731</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>C17998</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>CL.PARAMCD_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B57">
-        <v>2</v>
+          <t>CL.YN</t>
+        </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ACITM02</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Naming Objects And Fingers (Refer To 5 C</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>ADAS-Cog Parameter Code</t>
+          <t>No Yes Response</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
           <t>text</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>C66742</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>C49487</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>CL.PARAMCD_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B58">
-        <v>3</v>
+          <t>CL.YN</t>
+        </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ACITM03</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Delayed Word Recall</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>ADAS-Cog Parameter Code</t>
+          <t>No Yes Response</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
           <t>text</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>C66742</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>C49488</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>CL.PARAMCD_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B59">
-        <v>4</v>
+          <t>CL.Y_BLANK</t>
+        </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ACITM04</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Commands</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ADAS-Cog Parameter Code</t>
+          <t>No Yes Response - Y subset</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
           <t>text</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>C66742</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>C49488</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>CL.PARAMCD_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B60">
-        <v>5</v>
+          <t>CL.AESEV</t>
+        </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ACITM05</t>
+          <t>MILD</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Constructional Praxis</t>
+          <t>Grade 1</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>ADAS-Cog Parameter Code</t>
+          <t>Severity/Intensity Scale for Adverse Events</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
           <t>text</t>
         </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>C66769</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>C41338</t>
+        </is>
+      </c>
+      <c r="J60">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>CL.PARAMCD_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B61">
-        <v>6</v>
+          <t>CL.AESEV</t>
+        </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ACITM06</t>
+          <t>MODERATE</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Ideational Praxis</t>
+          <t>Grade 2</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>ADAS-Cog Parameter Code</t>
+          <t>Severity/Intensity Scale for Adverse Events</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
           <t>text</t>
         </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>C66769</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>C41339</t>
+        </is>
+      </c>
+      <c r="J61">
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>CL.PARAMCD_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B62">
-        <v>7</v>
+          <t>CL.AESEV</t>
+        </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ACITM07</t>
+          <t>SEVERE</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Orientation</t>
+          <t>Grade 3</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>ADAS-Cog Parameter Code</t>
+          <t>Severity/Intensity Scale for Adverse Events</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
           <t>text</t>
         </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>C66769</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>C41340</t>
+        </is>
+      </c>
+      <c r="J62">
+        <v>3</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>CL.PARAMCD_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B63">
-        <v>8</v>
+          <t>CL.AECAUS</t>
+        </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ACITM08</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Word Recognition</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ADAS-Cog Parameter Code</t>
+          <t>Causality</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
           <t>text</t>
         </is>
+      </c>
+      <c r="J63">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>CL.PARAMCD_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B64">
-        <v>9</v>
+          <t>CL.AECAUS</t>
+        </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ACITM09</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Attention/Visual Search Task</t>
+          <t>POSSIBLE</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>ADAS-Cog Parameter Code</t>
+          <t>Causality</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
           <t>text</t>
         </is>
+      </c>
+      <c r="J64">
+        <v>2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>CL.PARAMCD_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B65">
-        <v>10</v>
+          <t>CL.AECAUS</t>
+        </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ACITM10</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Maze Solution</t>
+          <t>PROBABLE</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>ADAS-Cog Parameter Code</t>
+          <t>Causality</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
           <t>text</t>
         </is>
+      </c>
+      <c r="J65">
+        <v>3</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>CL.PARAMCD_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B66">
-        <v>11</v>
+          <t>CL.AECAUS</t>
+        </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ACITM11</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>Spoken Language Ability</t>
+          <t>REMOTE</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>ADAS-Cog Parameter Code</t>
+          <t>Causality</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
           <t>text</t>
         </is>
+      </c>
+      <c r="J66">
+        <v>4</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>CL.PARAMCD_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B67">
-        <v>12</v>
+          <t>CL.OUT</t>
+        </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ACITM12</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Comprehension Of Spoken Language</t>
+          <t>RECOVERED/RESOLVED</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>ADAS-Cog Parameter Code</t>
+          <t>Outcome of Adverse Event</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
           <t>text</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>C66768</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>C49498</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>CL.PARAMCD_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B68">
-        <v>13</v>
+          <t>CL.OUT</t>
+        </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ACITM13</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>Word Finding Difficulty In Spontaneous Speech</t>
+          <t>NOT RECOVERED/NOT RESOLVED</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>ADAS-Cog Parameter Code</t>
+          <t>Outcome of Adverse Event</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
           <t>text</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>C66768</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>C49494</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CL.PARAMCD_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B69">
-        <v>14</v>
+          <t>CL.OUT</t>
+        </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ACITM14</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>Recall Of Test Instructions</t>
+          <t>FATAL</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>ADAS-Cog Parameter Code</t>
+          <t>Outcome of Adverse Event</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -8515,3778 +8582,12 @@
           <t>text</t>
         </is>
       </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>CL.PARAMCD_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B70">
-        <v>15</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>ACTOT</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>Adas-Cog(11) Subscore</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>ADAS-Cog Parameter Code</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>CL.PARAMN_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B71">
-        <v>1</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Word Recall Task</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>ADAS-Cog Parameter Code (N)</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>CL.PARAMN_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B72">
-        <v>2</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>Naming Objects And Fingers (Refer To 5 C</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>ADAS-Cog Parameter Code (N)</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>CL.PARAMN_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B73">
-        <v>3</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Delayed Word Recall</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>ADAS-Cog Parameter Code (N)</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>CL.PARAMN_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B74">
-        <v>4</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>Commands</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>ADAS-Cog Parameter Code (N)</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>CL.PARAMN_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B75">
-        <v>5</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>Constructional Praxis</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>ADAS-Cog Parameter Code (N)</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>CL.PARAMN_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B76">
-        <v>6</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>Ideational Praxis</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>ADAS-Cog Parameter Code (N)</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>CL.PARAMN_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B77">
-        <v>7</v>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>Orientation</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>ADAS-Cog Parameter Code (N)</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>CL.PARAMN_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B78">
-        <v>8</v>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>Word Recognition</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>ADAS-Cog Parameter Code (N)</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>CL.PARAMN_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B79">
-        <v>9</v>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>Attention/Visual Search Task</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>ADAS-Cog Parameter Code (N)</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>CL.PARAMN_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B80">
-        <v>10</v>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>Maze Solution</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>ADAS-Cog Parameter Code (N)</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>CL.PARAMN_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B81">
-        <v>11</v>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>Spoken Language Ability</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>ADAS-Cog Parameter Code (N)</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>CL.PARAMN_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B82">
-        <v>12</v>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>Comprehension Of Spoken Language</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>ADAS-Cog Parameter Code (N)</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>CL.PARAMN_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B83">
-        <v>13</v>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>Word Finding Difficulty In Spontaneous S</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>ADAS-Cog Parameter Code (N)</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>CL.PARAMN_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B84">
-        <v>14</v>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>Recall Of Test Instructions</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>ADAS-Cog Parameter Code (N)</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>CL.PARAMN_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B85">
-        <v>15</v>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>Adas-Cog(11) Subscore</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>ADAS-Cog Parameter Code (N)</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>CL.PARAM_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B86">
-        <v>1</v>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Word Recall Task</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>ADAS-Cog Parameter</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>CL.PARAM_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B87">
-        <v>2</v>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Naming Objects And Fingers (Refer To 5 C</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>ADAS-Cog Parameter</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>CL.PARAM_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B88">
-        <v>3</v>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Delayed Word Recall</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>ADAS-Cog Parameter</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>CL.PARAM_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B89">
-        <v>4</v>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Commands</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>ADAS-Cog Parameter</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>CL.PARAM_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B90">
-        <v>5</v>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Constructional Praxis</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>ADAS-Cog Parameter</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>CL.PARAM_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B91">
-        <v>6</v>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Ideational Praxis</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>ADAS-Cog Parameter</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>CL.PARAM_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B92">
-        <v>7</v>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Orientation</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>ADAS-Cog Parameter</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>CL.PARAM_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B93">
-        <v>8</v>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Word Recognition</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>ADAS-Cog Parameter</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>CL.PARAM_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B94">
-        <v>9</v>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Attention/Visual Search Task</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>ADAS-Cog Parameter</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>CL.PARAM_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B95">
-        <v>10</v>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Maze Solution</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>ADAS-Cog Parameter</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>CL.PARAM_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B96">
-        <v>11</v>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Spoken Language Ability</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>ADAS-Cog Parameter</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>CL.PARAM_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B97">
-        <v>12</v>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Comprehension Of Spoken Language</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>ADAS-Cog Parameter</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>CL.PARAM_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B98">
-        <v>13</v>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Word Finding Difficulty In Spontaneous S</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>ADAS-Cog Parameter</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>CL.PARAM_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B99">
-        <v>14</v>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Recall Of Test Instructions</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>ADAS-Cog Parameter</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>CL.PARAM_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B100">
-        <v>15</v>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Adas-Cog(11) Subscore</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>ADAS-Cog Parameter</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>CL.AWRANGE_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B101">
-        <v>1</v>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>&lt;=1</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>Analysis Window Range</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>CL.AWRANGE_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B102">
-        <v>2</v>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>2-84</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>Analysis Window Range</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>CL.AWRANGE_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B103">
-        <v>3</v>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>85-140</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>Analysis Window Range</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>CL.AWRANGE_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B104">
-        <v>4</v>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>&gt;140</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>Analysis Window Range</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>CL.RACE</t>
-        </is>
-      </c>
-      <c r="B105">
-        <v>1</v>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>WHITE</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>Race</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>C74457</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>C41261</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>CL.RACE</t>
-        </is>
-      </c>
-      <c r="B106">
-        <v>2</v>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>BLACK OR AFRICAN AMERICAN</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>Race</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>C74457</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>C16352</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>CL.RACE</t>
-        </is>
-      </c>
-      <c r="B107">
-        <v>3</v>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>ASIAN</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>Race</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>C74457</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>C41260</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>CL.RACE</t>
-        </is>
-      </c>
-      <c r="B108">
-        <v>4</v>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>AMERICAN INDIAN OR ALASKA NATIVE</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>Race</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>C74457</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>C41259</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>CL.RACEN</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>WHITE</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>Race (N)</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>CL.RACEN</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>BLACK OR AFRICAN AMERICAN</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>Race (N)</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>CL.RACEN</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>AMERICAN INDIAN OR ALASKA NATIVE</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>Race (N)</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>CL.RACEN</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>ASIAN</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>Race (N)</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>CL.SEX</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>Sex</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>C66731</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>C16576</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>CL.SEX</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>Sex</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>C66731</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>C20197</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>CL.SEX</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>Sex</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>C66731</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>C17998</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>CL.VISIT</t>
-        </is>
-      </c>
-      <c r="B116">
-        <v>1</v>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>SCREENING 1</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>Visit</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>CL.VISIT</t>
-        </is>
-      </c>
-      <c r="B117">
-        <v>2</v>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>UNSCHEDULED 1.1</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>Visit</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>CL.VISIT</t>
-        </is>
-      </c>
-      <c r="B118">
-        <v>3</v>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>UNSCHEDULED 1.2</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>Visit</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>CL.VISIT</t>
-        </is>
-      </c>
-      <c r="B119">
-        <v>4</v>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>UNSCHEDULED 1.3</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>Visit</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>CL.VISIT</t>
-        </is>
-      </c>
-      <c r="B120">
-        <v>5</v>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>SCREENING 2</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>Visit</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>CL.VISIT</t>
-        </is>
-      </c>
-      <c r="B121">
-        <v>6</v>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>BASELINE</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>Visit</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>CL.VISIT</t>
-        </is>
-      </c>
-      <c r="B122">
-        <v>7</v>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>UNSCHEDULED 3.1</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>Visit</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>CL.VISIT</t>
-        </is>
-      </c>
-      <c r="B123">
-        <v>8</v>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>AMBUL ECG PLACEMENT</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>Visit</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>CL.VISIT</t>
-        </is>
-      </c>
-      <c r="B124">
-        <v>9</v>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>WEEK 2</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>Visit</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>CL.VISIT</t>
-        </is>
-      </c>
-      <c r="B125">
-        <v>10</v>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>UNSCHEDULED 4.1</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>Visit</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>CL.VISIT</t>
-        </is>
-      </c>
-      <c r="B126">
-        <v>11</v>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>UNSCHEDULED 4.2</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>Visit</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>CL.VISIT</t>
-        </is>
-      </c>
-      <c r="B127">
-        <v>12</v>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>WEEK 4</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>Visit</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>CL.VISIT</t>
-        </is>
-      </c>
-      <c r="B128">
-        <v>13</v>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>UNSCHEDULED 5.1</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>Visit</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>CL.VISIT</t>
-        </is>
-      </c>
-      <c r="B129">
-        <v>14</v>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>AMBUL ECG REMOVAL</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>Visit</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>CL.VISIT</t>
-        </is>
-      </c>
-      <c r="B130">
-        <v>15</v>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>UNSCHEDULED 6.1</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>Visit</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>CL.VISIT</t>
-        </is>
-      </c>
-      <c r="B131">
-        <v>16</v>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>WEEK 6</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>Visit</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>CL.VISIT</t>
-        </is>
-      </c>
-      <c r="B132">
-        <v>17</v>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>UNSCHEDULED 7.1</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>Visit</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>CL.VISIT</t>
-        </is>
-      </c>
-      <c r="B133">
-        <v>18</v>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>WEEK 8</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>Visit</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>CL.VISIT</t>
-        </is>
-      </c>
-      <c r="B134">
-        <v>19</v>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>WEEK 10 (T)</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>Visit</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>CL.VISIT</t>
-        </is>
-      </c>
-      <c r="B135">
-        <v>20</v>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>UNSCHEDULED 8.2</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>Visit</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>CL.VISIT</t>
-        </is>
-      </c>
-      <c r="B136">
-        <v>21</v>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>WEEK 12</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>Visit</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>CL.VISIT</t>
-        </is>
-      </c>
-      <c r="B137">
-        <v>22</v>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>WEEK 14 (T)</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>Visit</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>CL.VISIT</t>
-        </is>
-      </c>
-      <c r="B138">
-        <v>23</v>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>UNSCHEDULED 9.2</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>Visit</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>CL.VISIT</t>
-        </is>
-      </c>
-      <c r="B139">
-        <v>24</v>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>UNSCHEDULED 9.3</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>Visit</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>CL.VISIT</t>
-        </is>
-      </c>
-      <c r="B140">
-        <v>25</v>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>WEEK 16</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>Visit</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>CL.VISIT</t>
-        </is>
-      </c>
-      <c r="B141">
-        <v>26</v>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>WEEK 18 (T)</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>Visit</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>CL.VISIT</t>
-        </is>
-      </c>
-      <c r="B142">
-        <v>27</v>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>UNSCHEDULED 10.2</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>Visit</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>CL.VISIT</t>
-        </is>
-      </c>
-      <c r="B143">
-        <v>28</v>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>WEEK 20</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>Visit</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>CL.VISIT</t>
-        </is>
-      </c>
-      <c r="B144">
-        <v>29</v>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>WEEK 22 (T)</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>Visit</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>CL.VISIT</t>
-        </is>
-      </c>
-      <c r="B145">
-        <v>30</v>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>UNSCHEDULED 11.2</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>Visit</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>CL.VISIT</t>
-        </is>
-      </c>
-      <c r="B146">
-        <v>31</v>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>WEEK 24</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>Visit</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>CL.VISIT</t>
-        </is>
-      </c>
-      <c r="B147">
-        <v>32</v>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>UNSCHEDULED 12.1</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>Visit</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>CL.VISIT</t>
-        </is>
-      </c>
-      <c r="B148">
-        <v>33</v>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>WEEK 26</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>Visit</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>CL.VISIT</t>
-        </is>
-      </c>
-      <c r="B149">
-        <v>34</v>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>UNSCHEDULED 13.1</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>Visit</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>CL.VISIT</t>
-        </is>
-      </c>
-      <c r="B150">
-        <v>35</v>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>AE FOLLOW-UP</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>Visit</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>CL.VISIT</t>
-        </is>
-      </c>
-      <c r="B151">
-        <v>36</v>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>RETRIEVAL</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>Visit</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>CL.VISIT</t>
-        </is>
-      </c>
-      <c r="B152">
-        <v>37</v>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Rash followup</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>Visit</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>CL.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B153">
-        <v>1</v>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>SCREENING 1</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>Visit Number</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>CL.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B154">
-        <v>2</v>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>UNSCHEDULED 1.1</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>Visit Number</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>CL.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B155">
-        <v>3</v>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>UNSCHEDULED 1.2</t>
-        </is>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>Visit Number</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>CL.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B156">
-        <v>4</v>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>1.3</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>UNSCHEDULED 1.3</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>Visit Number</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>CL.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B157">
-        <v>5</v>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>SCREENING 2</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>Visit Number</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>CL.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B158">
-        <v>6</v>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>BASELINE</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>Visit Number</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>CL.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B159">
-        <v>7</v>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>UNSCHEDULED 3.1</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>Visit Number</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>CL.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B160">
-        <v>8</v>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>AMBUL ECG PLACEMENT</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>Visit Number</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>CL.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B161">
-        <v>9</v>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>WEEK 2</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>Visit Number</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>CL.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B162">
-        <v>10</v>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>4.1</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>UNSCHEDULED 4.1</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>Visit Number</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>CL.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B163">
-        <v>11</v>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>4.2</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>UNSCHEDULED 4.2</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>Visit Number</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>CL.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B164">
-        <v>12</v>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>WEEK 4</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>Visit Number</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>CL.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B165">
-        <v>13</v>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>5.1</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>UNSCHEDULED 5.1</t>
-        </is>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>Visit Number</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>CL.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B166">
-        <v>14</v>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>AMBUL ECG REMOVAL</t>
-        </is>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>Visit Number</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>CL.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B167">
-        <v>15</v>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>6.1</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>UNSCHEDULED 6.1</t>
-        </is>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>Visit Number</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>CL.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B168">
-        <v>16</v>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>WEEK 6</t>
-        </is>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>Visit Number</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>CL.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B169">
-        <v>17</v>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>7.1</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>UNSCHEDULED 7.1</t>
-        </is>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>Visit Number</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>CL.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B170">
-        <v>18</v>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>WEEK 8</t>
-        </is>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>Visit Number</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>CL.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B171">
-        <v>19</v>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>8.1</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>WEEK 10 (T)</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>Visit Number</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>CL.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B172">
-        <v>20</v>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>8.2</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>UNSCHEDULED 8.2</t>
-        </is>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>Visit Number</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>CL.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B173">
-        <v>21</v>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>WEEK 12</t>
-        </is>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>Visit Number</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>CL.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B174">
-        <v>22</v>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>9.1</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>WEEK 14 (T)</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>Visit Number</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>CL.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B175">
-        <v>23</v>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>9.2</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>UNSCHEDULED 9.2</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>Visit Number</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>CL.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B176">
-        <v>24</v>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>9.3</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>UNSCHEDULED 9.3</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>Visit Number</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>CL.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B177">
-        <v>25</v>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>WEEK 16</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>Visit Number</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>CL.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B178">
-        <v>26</v>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>10.1</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>WEEK 18 (T)</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>Visit Number</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>CL.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B179">
-        <v>27</v>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>10.2</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>UNSCHEDULED 10.2</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>Visit Number</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>CL.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B180">
-        <v>28</v>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>WEEK 20</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>Visit Number</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>CL.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B181">
-        <v>29</v>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>11.1</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>WEEK 22 (T)</t>
-        </is>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>Visit Number</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>CL.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B182">
-        <v>30</v>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>11.2</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>UNSCHEDULED 11.2</t>
-        </is>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>Visit Number</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>CL.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B183">
-        <v>31</v>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>WEEK 24</t>
-        </is>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>Visit Number</t>
-        </is>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>CL.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B184">
-        <v>32</v>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>12.1</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>UNSCHEDULED 12.1</t>
-        </is>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>Visit Number</t>
-        </is>
-      </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>CL.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B185">
-        <v>33</v>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>WEEK 26</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>Visit Number</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>CL.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B186">
-        <v>34</v>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>13.1</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>UNSCHEDULED 13.1</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>Visit Number</t>
-        </is>
-      </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>CL.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B187">
-        <v>35</v>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>AE FOLLOW-UP</t>
-        </is>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>Visit Number</t>
-        </is>
-      </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>CL.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B188">
-        <v>36</v>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>RETRIEVAL</t>
-        </is>
-      </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>Visit Number</t>
-        </is>
-      </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>CL.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B189">
-        <v>37</v>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>501</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>Rash followup</t>
-        </is>
-      </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>Visit Number</t>
-        </is>
-      </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>CL.YN</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>No Yes Response</t>
-        </is>
-      </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>C66742</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>C49487</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>CL.YN</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>No Yes Response</t>
-        </is>
-      </c>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>C66742</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr">
-        <is>
-          <t>C49488</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>CL.Y_BLANK</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>No Yes Response - Y subset</t>
-        </is>
-      </c>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>C66742</t>
-        </is>
-      </c>
-      <c r="I192" t="inlineStr">
-        <is>
-          <t>C49488</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>CL.AESEV</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>MILD</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>Grade 1</t>
-        </is>
-      </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>Severity/Intensity Scale for Adverse Events</t>
-        </is>
-      </c>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>C66769</t>
-        </is>
-      </c>
-      <c r="I193" t="inlineStr">
-        <is>
-          <t>C41338</t>
-        </is>
-      </c>
-      <c r="J193">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>CL.AESEV</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>MODERATE</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>Grade 2</t>
-        </is>
-      </c>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>Severity/Intensity Scale for Adverse Events</t>
-        </is>
-      </c>
-      <c r="F194" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>C66769</t>
-        </is>
-      </c>
-      <c r="I194" t="inlineStr">
-        <is>
-          <t>C41339</t>
-        </is>
-      </c>
-      <c r="J194">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>CL.AESEV</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>SEVERE</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>Grade 3</t>
-        </is>
-      </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>Severity/Intensity Scale for Adverse Events</t>
-        </is>
-      </c>
-      <c r="F195" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>C66769</t>
-        </is>
-      </c>
-      <c r="I195" t="inlineStr">
-        <is>
-          <t>C41340</t>
-        </is>
-      </c>
-      <c r="J195">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>CL.AECAUS</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>Causality</t>
-        </is>
-      </c>
-      <c r="F196" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="J196">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>CL.AECAUS</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>POSSIBLE</t>
-        </is>
-      </c>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>Causality</t>
-        </is>
-      </c>
-      <c r="F197" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="J197">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>CL.AECAUS</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>PROBABLE</t>
-        </is>
-      </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>Causality</t>
-        </is>
-      </c>
-      <c r="F198" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="J198">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>CL.AECAUS</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>REMOTE</t>
-        </is>
-      </c>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>Causality</t>
-        </is>
-      </c>
-      <c r="F199" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="J199">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>CL.OUT</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>RECOVERED/RESOLVED</t>
-        </is>
-      </c>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t>Outcome of Adverse Event</t>
-        </is>
-      </c>
-      <c r="F200" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G200" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t>C66768</t>
         </is>
       </c>
-      <c r="I200" t="inlineStr">
-        <is>
-          <t>C49498</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>CL.OUT</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>NOT RECOVERED/NOT RESOLVED</t>
-        </is>
-      </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>Outcome of Adverse Event</t>
-        </is>
-      </c>
-      <c r="F201" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>C66768</t>
-        </is>
-      </c>
-      <c r="I201" t="inlineStr">
-        <is>
-          <t>C49494</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>CL.OUT</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>FATAL</t>
-        </is>
-      </c>
-      <c r="E202" t="inlineStr">
-        <is>
-          <t>Outcome of Adverse Event</t>
-        </is>
-      </c>
-      <c r="F202" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G202" t="inlineStr">
-        <is>
-          <t>C66768</t>
-        </is>
-      </c>
-      <c r="I202" t="inlineStr">
+      <c r="I69" t="inlineStr">
         <is>
           <t>C48275</t>
         </is>
@@ -12299,7 +8600,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H55"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -12347,12 +8648,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MT.ADQSADAS.AVISIT</t>
+          <t>MT.ADSL.SITEGR1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MT.ADQSADAS.AVISIT</t>
+          <t>MT.ADSL.SITEGR1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -12362,19 +8663,19 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Derived based on windowing algorithm described in SAP, Section 8.2</t>
+          <t>refer to SAP, Section 7.1 - if not pooled then SITEGR1=SITEID. If pooled, SITEGR1 will be 900</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MT.ADQSADAS.ADY</t>
+          <t>MT.ADSL.TRTSDT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MT.ADQSADAS.ADY</t>
+          <t>MT.ADSL.TRTSDT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -12384,19 +8685,19 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ADY = ADT - TRTSDT + 1, if ADT&gt;=TRTSDT. ADY = ADT - TRTSDT, if ADT&lt;TRTSDT.</t>
+          <t>SV.SVSTDTC where SV.VISITNUM=3, converted to SAS date</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MT.ADQSADAS.ADT</t>
+          <t>MT.ADSL.TRTEDT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MT.ADQSADAS.ADT</t>
+          <t>MT.ADSL.TRTEDT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -12406,19 +8707,19 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SAS date from QS.QSDTC</t>
+          <t>The date of final dose (from the CRF) is EX.EXENDTC on the subject's last EX record. If the date of final dose is missing for the subject and the subject discontinued after visit 3, use the date of discontinuation as the date of last dose. Convert the date to a SAS date.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MT.ADQSADAS.BASE</t>
+          <t>MT.ADSL.TRTDURD</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MT.ADQSADAS.BASE</t>
+          <t>MT.ADSL.TRTDURD</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -12428,19 +8729,19 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>QS.QSSTRESN where QS.QSBLFL=Y (QS.VISITNUM=3)</t>
+          <t>TRTEDT-TRTSDT+1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MT.ADQSADAS.CHG</t>
+          <t>MT.ADSL.AVGDD</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MT.ADQSADAS.CHG</t>
+          <t>MT.ADSL.AVGDD</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -12450,19 +8751,19 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>AVAL - BASE</t>
+          <t>CUMDOSE/TRTDURD</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MT.ADQSADAS.PCHG</t>
+          <t>MT.ADSL.CUMDOSE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MT.ADQSADAS.PCHG</t>
+          <t>MT.ADSL.CUMDOSE</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -12471,182 +8772,6 @@
         </is>
       </c>
       <c r="D7" t="inlineStr">
-        <is>
-          <t>100* (CHG/BASE)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>MT.ADQSADAS.ANL01FL</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>MT.ADQSADAS.ANL01FL</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Computation</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>If multiple visits fall into the same visit window, then the one closest to the target day is chosen for analysis. These are flagged with ANL01FL="Y".</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>MT.ADQSADAS.AWTDIFF</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>MT.ADQSADAS.AWTDIFF</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Computation</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Absolute difference between AWTARGET and ADY</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>MT.ADSL.SITEGR1</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>MT.ADSL.SITEGR1</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Computation</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>refer to SAP, Section 7.1 - if not pooled then SITEGR1=SITEID. If pooled, SITEGR1 will be 900</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>MT.ADSL.TRTSDT</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>MT.ADSL.TRTSDT</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Computation</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>SV.SVSTDTC where SV.VISITNUM=3, converted to SAS date</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>MT.ADSL.TRTEDT</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>MT.ADSL.TRTEDT</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Computation</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>The date of final dose (from the CRF) is EX.EXENDTC on the subject's last EX record. If the date of final dose is missing for the subject and the subject discontinued after visit 3, use the date of discontinuation as the date of last dose. Convert the date to a SAS date.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>MT.ADSL.TRTDURD</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>MT.ADSL.TRTDURD</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Computation</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>TRTEDT-TRTSDT+1</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>MT.ADSL.AVGDD</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>MT.ADSL.AVGDD</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Computation</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>CUMDOSE/TRTDURD</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>MT.ADSL.CUMDOSE</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>MT.ADSL.CUMDOSE</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Computation</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
         <is>
           <t>For TRT01PN=0 or 54: CUMDOSE=TRT01PN*TRTDURD. 
 For TRT01PN=81: CUMDOSE will be based on 
@@ -12659,15 +8784,191 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>MT.ADSL.AGEGR1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>MT.ADSL.AGEGR1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Grouping of AGE into &lt;65, 65-80, and &gt;80</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>MT.ADSL.SAFFL</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>MT.ADSL.SAFFL</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Y if ITTFL='Y' and TRTSDT ne missing. N otherwise</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>MT.ADSL.ITTFL</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>MT.ADSL.ITTFL</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Y if ARMCD ne ' '. N otherwise</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>MT.ADSL.EFFFL</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>MT.ADSL.EFFFL</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Y if SAFFL='Y AND subject has at least one record in QS for ADAS-Cog with QS.VISITNUM&gt;3 AND at least one record in QS for CIBIC+ with QS.VISITNUM&gt;3, N otherwise</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>MT.ADSL.COMP8FL</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>MT.ADSL.COMP8FL</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Y if subject has a SV.VISITNUM=8 and TRTEDT&gt;= date of visit 8, N otherwise</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>MT.ADSL.COMP16FL</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>MT.ADSL.COMP16FL</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Y if subject has a SV.VISITNUM=10 and TRTEDT&gt;=date of visit 10, N otherwise</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>MT.ADSL.COMP24FL</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>MT.ADSL.COMP24FL</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Y if subject has a SV.VISITNUM=12 and TRTEDT&gt;= date of visit 12 , N otherwise</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>MT.ADSL.DISCONFL</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>MT.ADSL.DISCONFL</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Y if EOSSTT='DISCONTINUED'. Null otherwise</t>
+        </is>
+      </c>
+    </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MT.ADSL.AGEGR1</t>
+          <t>MT.ADSL.DSRAEFL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MT.ADSL.AGEGR1</t>
+          <t>MT.ADSL.DSRAEFL</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -12677,19 +8978,19 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Grouping of AGE into &lt;65, 65-80, and &gt;80</t>
+          <t>Y if DCSREAS='Adverse Event'. Null otherwise</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MT.ADSL.SAFFL</t>
+          <t>MT.ADSL.BMIBL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MT.ADSL.SAFFL</t>
+          <t>MT.ADSL.BMIBL</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -12699,19 +9000,19 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Y if ITTFL='Y' and TRTSDT ne missing. N otherwise</t>
+          <t>WEIGHTBL / ((HEIGHTBL*100)**2)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MT.ADSL.ITTFL</t>
+          <t>MT.ADSL.BMIBLGR1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MT.ADSL.ITTFL</t>
+          <t>MT.ADSL.BMIBLGR1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -12721,19 +9022,19 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Y if ARMCD ne ' '. N otherwise</t>
+          <t>BMIBLGR1=Normal if . &lt; BMIBL &lt;25. BMIBLGR1=Overweight if 25 &lt;=BMIBL &lt;30. BMIBLGR1=Obese if BMIBL &gt;=30</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MT.ADSL.EFFFL</t>
+          <t>MT.ADSL.HEIGHTBL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MT.ADSL.EFFFL</t>
+          <t>MT.ADSL.HEIGHTBL</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -12743,19 +9044,19 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Y if SAFFL='Y AND subject has at least one record in QS for ADAS-Cog with QS.VISITNUM&gt;3 AND at least one record in QS for CIBIC+ with QS.VISITNUM&gt;3, N otherwise</t>
+          <t>VS.VSSTRESN where VS.VSTESTCD='HEIGHT' and VS.VISITNUM=1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MT.ADSL.COMP8FL</t>
+          <t>MT.ADSL.WEIGHTBL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MT.ADSL.COMP8FL</t>
+          <t>MT.ADSL.WEIGHTBL</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -12765,19 +9066,19 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Y if subject has a SV.VISITNUM=8 and TRTEDT&gt;= date of visit 8, N otherwise</t>
+          <t>VS.VSSTRESN where VS.VSTESTCD='WEIGHT' and VS.VISITNUM=3</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MT.ADSL.COMP16FL</t>
+          <t>MT.ADSL.EDUCLVL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MT.ADSL.COMP16FL</t>
+          <t>MT.ADSL.EDUCLVL</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -12787,19 +9088,19 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Y if subject has a SV.VISITNUM=10 and TRTEDT&gt;=date of visit 10, N otherwise</t>
+          <t>SC.SCSTRESN where SC.SCTESTCD="EDLEVEL"</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MT.ADSL.COMP24FL</t>
+          <t>MT.ADSL.DISONDT</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MT.ADSL.COMP24FL</t>
+          <t>MT.ADSL.DISONDT</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -12809,19 +9110,19 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Y if subject has a SV.VISITNUM=12 and TRTEDT&gt;= date of visit 12 , N otherwise</t>
+          <t>MH.MHSTDTC where MH.MHCAT='PRIMARY DIAGNOSIS' converted to SAS date</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MT.ADSL.DISCONFL</t>
+          <t>MT.ADSL.DURDIS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MT.ADSL.DISCONFL</t>
+          <t>MT.ADSL.DURDIS</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -12831,19 +9132,19 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Y if EOSSTT='DISCONTINUED'. Null otherwise</t>
+          <t>number of months between Date of VISIT 1 and DISONDT</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MT.ADSL.DSRAEFL</t>
+          <t>MT.ADSL.DURDSGR1</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MT.ADSL.DSRAEFL</t>
+          <t>MT.ADSL.DURDSGR1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -12853,19 +9154,19 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Y if DCSREAS='Adverse Event'. Null otherwise</t>
+          <t>grouping DURDIS values as &lt;12 and &gt;=12</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MT.ADSL.BMIBL</t>
+          <t>MT.ADSL.VISIT1DT</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MT.ADSL.BMIBL</t>
+          <t>MT.ADSL.VISIT1DT</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -12875,19 +9176,19 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>WEIGHTBL / ((HEIGHTBL*100)**2)</t>
+          <t>SV.SVSTDTC where SV.VISITNUM=1, converted to SAS date</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MT.ADSL.BMIBLGR1</t>
+          <t>MT.ADSL.VISNUMEN</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MT.ADSL.BMIBLGR1</t>
+          <t>MT.ADSL.VISNUMEN</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -12897,19 +9198,19 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>BMIBLGR1=Normal if . &lt; BMIBL &lt;25. BMIBLGR1=Overweight if 25 &lt;=BMIBL &lt;30. BMIBLGR1=Obese if BMIBL &gt;=30</t>
+          <t>If DS.VISITNUM=13 where DS.DSTERM='PROTOCOL COMPLETED' then VISNUMEN=12, otherwise VISNUMEN=DS.VISITNUM where DS.DSTERM='PROTOCOL COMPLETED'</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MT.ADSL.HEIGHTBL</t>
+          <t>MT.ADSL.RFENDT</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MT.ADSL.HEIGHTBL</t>
+          <t>MT.ADSL.RFENDT</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -12919,19 +9220,19 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VS.VSSTRESN where VS.VSTESTCD='HEIGHT' and VS.VISITNUM=1</t>
+          <t>RFENDTC converted to SAS date</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>MT.ADSL.WEIGHTBL</t>
+          <t>MT.ADSL.EOSSTT</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>MT.ADSL.WEIGHTBL</t>
+          <t>MT.ADSL.EOSSTT</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -12941,19 +9242,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VS.VSSTRESN where VS.VSTESTCD='WEIGHT' and VS.VISITNUM=3</t>
+          <t>If DS.DSDECOD='COMPLETED' then EOSSTT='COMPLETED'. Otherwise EOSSTT='DISCONTINUED'.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MT.ADSL.EDUCLVL</t>
+          <t>MT.ADSL.DCSREAS</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MT.ADSL.EDUCLVL</t>
+          <t>MT.ADSL.DCSREAS</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -12963,19 +9264,19 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>SC.SCSTRESN where SC.SCTESTCD="EDLEVEL"</t>
+          <t>If DS.DSCAT='DISPOSITION EVENT' and DS.DSTERM in('I/E NOT MET' 'SPONSOR DECISION' 'WITHDREW CONSENT') then DCSREAS=DS.DSTERM. Otherwise if DS.DSCAT='DISPOSITION EVENT' then DCSREAS=DS.DSDECOD. Convert to mixed case to match display format.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MT.ADSL.DISONDT</t>
+          <t>MT.ADSL.MMS1TSBL</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>MT.ADSL.DISONDT</t>
+          <t>MT.ADSL.MMS1TSBL</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -12985,19 +9286,19 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>MH.MHSTDTC where MH.MHCAT='PRIMARY DIAGNOSIS' converted to SAS date</t>
+          <t>Sum of FT.FTSTRESN values where FT.FTCAT="MMSE" for the subject (FT.FTTESTCD= 'MMS101A'-'MMS111')</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MT.ADSL.DURDIS</t>
+          <t>MT.ADAE.ASTDT</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>MT.ADSL.DURDIS</t>
+          <t>MT.ADAE.ASTDT</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -13007,19 +9308,19 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>number of months between Date of VISIT 1 and DISONDT</t>
+          <t>AE.AESTDTC, converted to a numeric SAS date. Some events with partial dates are imputed in a conservative manner. If the day component is missing, a value of '01' is used. If both the month and day are missing no imputation is performed as these dates clearly indicate a start prior to the beginning of treatment. There are no events with completely missing start dates.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MT.ADSL.DURDSGR1</t>
+          <t>MT.ADAE.ASTDTF</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>MT.ADSL.DURDSGR1</t>
+          <t>MT.ADAE.ASTDTF</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -13029,19 +9330,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>grouping DURDIS values as &lt;12 and &gt;=12</t>
+          <t>ASTDTF='D' if the day value within the character date is imputed. Note that only day values needed to be imputed for this study</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MT.ADSL.VISIT1DT</t>
+          <t>MT.ADAE.ASTDY</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>MT.ADSL.VISIT1DT</t>
+          <t>MT.ADAE.ASTDY</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -13051,19 +9352,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>SV.SVSTDTC where SV.VISITNUM=1, converted to SAS date</t>
+          <t>IF ASTDT&gt;=TRTSDT&gt;MISSING then ASTDY=ASTDT-TRTSDT+1 Else if TRTSDT&gt;ASTDT&gt;MISSING then ASTDY=ASTDT-TRTSDT</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MT.ADSL.VISNUMEN</t>
+          <t>MT.ADAE.AENDT</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>MT.ADSL.VISNUMEN</t>
+          <t>MT.ADAE.AENDT</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -13073,19 +9374,19 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>If DS.VISITNUM=13 where DS.DSTERM='PROTOCOL COMPLETED' then VISNUMEN=12, otherwise VISNUMEN=DS.VISITNUM where DS.DSTERM='PROTOCOL COMPLETED'</t>
+          <t>AE.AEENDTC, converted to a numeric SAS date</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MT.ADSL.RFENDT</t>
+          <t>MT.ADAE.AENDY</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>MT.ADSL.RFENDT</t>
+          <t>MT.ADAE.AENDY</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -13095,19 +9396,19 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>RFENDTC converted to SAS date</t>
+          <t>IF AENDT&gt;=TRTSDT&gt;MISSING then AENDY=AENDT-TRTSDT+1 Else if TRTSDT&gt;AENDT&gt;MISSING then AENDY=AENDT-TRTSDT</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MT.ADSL.EOSSTT</t>
+          <t>MT.ADAE.ADURN</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>MT.ADSL.EOSSTT</t>
+          <t>MT.ADAE.ADURN</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -13117,19 +9418,19 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>If DS.DSDECOD='COMPLETED' then EOSSTT='COMPLETED'. Otherwise EOSSTT='DISCONTINUED'.</t>
+          <t>ADURN=AENDT-ASTDT+1</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MT.ADSL.DCSREAS</t>
+          <t>MT.ADAE.ADURU</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>MT.ADSL.DCSREAS</t>
+          <t>MT.ADAE.ADURU</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -13139,19 +9440,19 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>If DS.DSCAT='DISPOSITION EVENT' and DS.DSTERM in('I/E NOT MET' 'SPONSOR DECISION' 'WITHDREW CONSENT') then DCSREAS=DS.DSTERM. Otherwise if DS.DSCAT='DISPOSITION EVENT' then DCSREAS=DS.DSDECOD. Convert to mixed case to match display format.</t>
+          <t>If ADURN is not missing then ADURU='DAY'</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MT.ADSL.MMS1TSBL</t>
+          <t>MT.ADAE.TRTEMFL</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>MT.ADSL.MMS1TSBL</t>
+          <t>MT.ADAE.TRTEMFL</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -13161,19 +9462,19 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Sum of FT.FTSTRESN values where FT.FTCAT="MMSE" for the subject (FT.FTTESTCD= 'MMS101A'-'MMS111')</t>
+          <t>If ASTDT &gt;= TRTSDT &gt; . then TRTEMFL='Y'. Otherwise TRTEMFL='N'</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MT.ADQSADAS.AVAL.ACTOT</t>
+          <t>MT.ADAE.AOCCFL</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>MT.ADQSADAS.AVAL.ACTOT</t>
+          <t>MT.ADAE.AOCCFL</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -13183,29 +9484,19 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Sum of ADAS scores for items 1, 2, 4, 5, 6, 7, 8, 11, 12, 13, and 14, see ADRG for details on adjusting for missing values.</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>LF.ADRG</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>Subset to TRTEMFL='Y' and sort by Subject (USUBJID), Start Date (ASTDT), and Sequence Number (AESEQ) and flag the first record (set AOCCFL=’Y’) within each Subject</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>MT.ADAE.ASTDT</t>
+          <t>MT.ADAE.AOCCSFL</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>MT.ADAE.ASTDT</t>
+          <t>MT.ADAE.AOCCSFL</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -13215,19 +9506,19 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>AE.AESTDTC, converted to a numeric SAS date. Some events with partial dates are imputed in a conservative manner. If the day component is missing, a value of '01' is used. If both the month and day are missing no imputation is performed as these dates clearly indicate a start prior to the beginning of treatment. There are no events with completely missing start dates.</t>
+          <t>Subset to TRTEMFL='Y' and sort by Subject (USUBJID), System Organ Class (AEBODSYS), Start Date (ASTDT), and Sequence Number (AESEQ) and flag the first record (set AOCCSFL=’Y’) within each Subject and SOC</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MT.ADAE.ASTDTF</t>
+          <t>MT.ADAE.AOCCPFL</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>MT.ADAE.ASTDTF</t>
+          <t>MT.ADAE.AOCCPFL</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -13237,19 +9528,19 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ASTDTF='D' if the day value within the character date is imputed. Note that only day values needed to be imputed for this study</t>
+          <t>Subset to TRTEMFL='Y' and sort by Subject (USUBJID), System Organ Class (AEBODSYS), Preferred Term (AEDECOD), Start Date (ASTDT), and Sequence Number (AESEQ) and flag the first record (set AOCCPFL=’Y’) within each Subject, SOC, and PT</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>MT.ADAE.ASTDY</t>
+          <t>MT.ADAE.AOCC02FL</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>MT.ADAE.ASTDY</t>
+          <t>MT.ADAE.AOCC02FL</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -13259,19 +9550,19 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>IF ASTDT&gt;=TRTSDT&gt;MISSING then ASTDY=ASTDT-TRTSDT+1 Else if TRTSDT&gt;ASTDT&gt;MISSING then ASTDY=ASTDT-TRTSDT</t>
+          <t>Subset to TRTEMFL='Y' and AESER='Y' and sort by Subject (USUBJID), Start Date (ASTDT), and Sequence Number (AESEQ) and flag the first record (set AOCC02FL=’Y’) within each Subject</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MT.ADAE.AENDT</t>
+          <t>MT.ADAE.AOCC03FL</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>MT.ADAE.AENDT</t>
+          <t>MT.ADAE.AOCC03FL</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -13281,19 +9572,19 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>AE.AEENDTC, converted to a numeric SAS date</t>
+          <t>Subset to TRTEMFL='Y' and AESER='Y' and sort by Subject (USUBJID), System Organ Class (AEBODSYS), Start Date (ASTDT), and Sequence Number (AESEQ) and flag the first record (set AOCC03FL=’Y’) within each Subject and SOC</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MT.ADAE.AENDY</t>
+          <t>MT.ADAE.AOCC04FL</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>MT.ADAE.AENDY</t>
+          <t>MT.ADAE.AOCC04FL</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -13303,19 +9594,19 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>IF AENDT&gt;=TRTSDT&gt;MISSING then AENDY=AENDT-TRTSDT+1 Else if TRTSDT&gt;AENDT&gt;MISSING then AENDY=AENDT-TRTSDT</t>
+          <t>Subset to TRTEMFL='Y' and AESER='Y' and sort by Subject (USUBJID), System Organ Class (AEBODSYS), Preferred Term (AEDECOD), Start Date (ASTDT), and Sequence Number (AESEQ) and flag the first record (set AOCC04FL=’Y’) within each Subject, SOC, and PT</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MT.ADAE.ADURN</t>
+          <t>MT.ADAE.CQ01NAM</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>MT.ADAE.ADURN</t>
+          <t>MT.ADAE.CQ01NAM</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -13325,19 +9616,19 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ADURN=AENDT-ASTDT+1</t>
+          <t>If AEDECOD contains any of the character strings of ('APPLICATION', 'DERMATITIS', 'ERYTHEMA', 'BLISTER') OR if AEBODSYS='SKIN AND SUBC UTANEOUS TISSUE DISORDERS' but AEDECOD is not in ('COLD SWEAT', 'HYPERHIDROSIS', 'ALOPECIA') then CQ01NAM='DERMATOLOGIC EVENTS' Otherwise CQ01NAM=NULL</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MT.ADAE.ADURU</t>
+          <t>MT.ADAE.AOCC01FL</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>MT.ADAE.ADURU</t>
+          <t>MT.ADAE.AOCC01FL</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -13346,204 +9637,6 @@
         </is>
       </c>
       <c r="D46" t="inlineStr">
-        <is>
-          <t>If ADURN is not missing then ADURU='DAY'</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>MT.ADAE.TRTEMFL</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>MT.ADAE.TRTEMFL</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Computation</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>If ASTDT &gt;= TRTSDT &gt; . then TRTEMFL='Y'. Otherwise TRTEMFL='N'</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>MT.ADAE.AOCCFL</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>MT.ADAE.AOCCFL</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Computation</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Subset to TRTEMFL='Y' and sort by Subject (USUBJID), Start Date (ASTDT), and Sequence Number (AESEQ) and flag the first record (set AOCCFL=’Y’) within each Subject</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>MT.ADAE.AOCCSFL</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>MT.ADAE.AOCCSFL</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Computation</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Subset to TRTEMFL='Y' and sort by Subject (USUBJID), System Organ Class (AEBODSYS), Start Date (ASTDT), and Sequence Number (AESEQ) and flag the first record (set AOCCSFL=’Y’) within each Subject and SOC</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>MT.ADAE.AOCCPFL</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>MT.ADAE.AOCCPFL</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Computation</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Subset to TRTEMFL='Y' and sort by Subject (USUBJID), System Organ Class (AEBODSYS), Preferred Term (AEDECOD), Start Date (ASTDT), and Sequence Number (AESEQ) and flag the first record (set AOCCPFL=’Y’) within each Subject, SOC, and PT</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>MT.ADAE.AOCC02FL</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>MT.ADAE.AOCC02FL</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Computation</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Subset to TRTEMFL='Y' and AESER='Y' and sort by Subject (USUBJID), Start Date (ASTDT), and Sequence Number (AESEQ) and flag the first record (set AOCC02FL=’Y’) within each Subject</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>MT.ADAE.AOCC03FL</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>MT.ADAE.AOCC03FL</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Computation</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Subset to TRTEMFL='Y' and AESER='Y' and sort by Subject (USUBJID), System Organ Class (AEBODSYS), Start Date (ASTDT), and Sequence Number (AESEQ) and flag the first record (set AOCC03FL=’Y’) within each Subject and SOC</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>MT.ADAE.AOCC04FL</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>MT.ADAE.AOCC04FL</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Computation</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Subset to TRTEMFL='Y' and AESER='Y' and sort by Subject (USUBJID), System Organ Class (AEBODSYS), Preferred Term (AEDECOD), Start Date (ASTDT), and Sequence Number (AESEQ) and flag the first record (set AOCC04FL=’Y’) within each Subject, SOC, and PT</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>MT.ADAE.CQ01NAM</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>MT.ADAE.CQ01NAM</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Computation</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>If AEDECOD contains any of the character strings of ('APPLICATION', 'DERMATITIS', 'ERYTHEMA', 'BLISTER') OR if AEBODSYS='SKIN AND SUBC UTANEOUS TISSUE DISORDERS' but AEDECOD is not in ('COLD SWEAT', 'HYPERHIDROSIS', 'ALOPECIA') then CQ01NAM='DERMATOLOGIC EVENTS' Otherwise CQ01NAM=NULL</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>MT.ADAE.AOCC01FL</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>MT.ADAE.AOCC01FL</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Computation</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
         <is>
           <t>Subset to CQ01NAM='' and TRTEMFL='Y' and sort by Subject (USUBJID), Start Date (ASTDT), and Sequence Number (AESEQ) and flag the first record (set AOCC01FL=’Y’) within each Subject (Flag First Treatment Emergent Dermatological Event for Time to Event Analysis)</t>
         </is>
@@ -13556,7 +9649,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -13618,243 +9711,106 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>COM.ADQSADAS</t>
+          <t>COM.JOIN-ADSL-ADAE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>See referenced dataset creation program and ADRG</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>LF.ADQSADAS.PGM</t>
+          <t>Get denominators for percentages from ADSL and counts and numerators from ADAE. Join ADAE with ADSL based on the unique subject identifier (USUBJID) keeping only records in ADAE for the numerator.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>COM.JOIN-ADSL-ADAE</t>
+          <t>COM.ADSL.TRT01PN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Get denominators for percentages from ADSL and counts and numerators from ADAE. Join ADAE with ADSL based on the unique subject identifier (USUBJID) keeping only records in ADAE for the numerator.</t>
+          <t>Numeric code for TRT01P</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>COM.ADQSADAS.AVISITN</t>
+          <t>COM.ADSL.TRT01A</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Numeric code for AVISIT</t>
+          <t>TRT01A=TRT01P, i.e., no difference between actual and randomized treatment in this study.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>COM.ADQSADAS.PARAMN</t>
+          <t>COM.ADSL.TRT01AN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Numeric code for PARAM</t>
+          <t>Numeric code for TRT01A</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>COM.ADQSADAS.AWRANGE</t>
+          <t>COM.ADSL.AGEGR1N</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Window range, specified in the SAP.</t>
+          <t>Numeric code for AGEGR1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>COM.ADQSADAS.AWTARGET</t>
+          <t>COM.ADSL.RACEN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Target day within the window, specified in the SAP.</t>
+          <t>Numeric code for RACE</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>COM.ADQSADAS.AWLO</t>
+          <t>COM.STDCT.01</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Start day of the window, specified in the SAP.</t>
+          <t>ADaM specific CT is applicable for a few variables only.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>COM.ADQSADAS.AWHI</t>
+          <t>COM.STDCT.02</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>End day of the window, specified in the SAP.</t>
+          <t>SDTM CT is applicable for variables copied from SDTM to ADaM.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>COM.ADQSADAS.AWU</t>
+          <t>COM.STD5</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
-        <is>
-          <t>Assigned as "DAYS".</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>COM.ADSL.TRT01PN</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Numeric code for TRT01P</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>COM.ADSL.TRT01A</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>TRT01A=TRT01P, i.e., no difference between actual and randomized treatment in this study.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>COM.ADSL.TRT01AN</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Numeric code for TRT01A</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>COM.ADSL.AGEGR1N</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Numeric code for AGEGR1</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>COM.ADSL.RACEN</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Numeric code for RACE</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>COM.ADQSADAS.DTYPE.ACITM01-ACITM14</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Value: null</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>COM.ADQSADAS.DTYPE.ACTOT</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Value: LOCF denotes that the LOCF imputation method was used to impute the value for the given parameter and analysis visit.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>COM.ADQSADAS.QSSEQ.ACTOT</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Set QSSEQ to missing for post baseline records. Set to QS.QSSEQ where QS.VISIT=BASELINE and QS.QSTESTCD=ACTOT.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>COM.STDCT.01</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>ADaM specific CT is applicable for a few variables only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>COM.STDCT.02</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>SDTM CT is applicable for variables copied from SDTM to ADaM.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>COM.STD5</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
         <is>
           <t>This is the CDISC CT Package 60 (2025-09-26) associated to the CDISC Define-XML Specification Version 2.1.10.</t>
         </is>
@@ -13867,7 +9823,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -13983,17 +9939,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LF.ADQSADAS.PGM</t>
+          <t>LF.CODE.001</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>adqsadas.sas</t>
+          <t>adae.sas</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>../programs/adqsadas-sas.txt</t>
+          <t>../programs/adae-sas.txt</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -14005,17 +9961,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LF.CODE.001</t>
+          <t>LF.ADSL.PGM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>adae.sas</t>
+          <t>adsl.sas</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>../programs/adae-sas.txt</t>
+          <t>../programs/adsl-sas.txt</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -14027,17 +9983,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LF.ADSL.PGM</t>
+          <t>LF.CSR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>adsl.sas</t>
+          <t>Clinical Study Report</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>../programs/adsl-sas.txt</t>
+          <t>../dummy-csr/dummy-csr.pdf</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -14049,42 +10005,20 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LF.CSR</t>
+          <t>LF.at14-5-02.sas</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Clinical Study Report</t>
+          <t>at14-5-02.sas</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>../dummy-csr/dummy-csr.pdf</t>
+          <t>../programs/at14-5-02-sas.txt</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>LF.at14-5-02.sas</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>at14-5-02.sas</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>../programs/at14-5-02-sas.txt</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
         <is>
           <t>other</t>
         </is>

--- a/inst/extdata/adam-spec.xlsx
+++ b/inst/extdata/adam-spec.xlsx
@@ -14,10 +14,9 @@
     <sheet name="Methods" sheetId="5" r:id="rId5"/>
     <sheet name="Comments" sheetId="6" r:id="rId6"/>
     <sheet name="Documents" sheetId="7" r:id="rId7"/>
-    <sheet name="WhereClauses" sheetId="8" r:id="rId8"/>
-    <sheet name="Standards" sheetId="9" r:id="rId9"/>
-    <sheet name="Analysis Displays" sheetId="10" r:id="rId10"/>
-    <sheet name="Analysis Results" sheetId="11" r:id="rId11"/>
+    <sheet name="Standards" sheetId="8" r:id="rId8"/>
+    <sheet name="Analysis Displays" sheetId="9" r:id="rId9"/>
+    <sheet name="Analysis Results" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -515,33 +514,88 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Display</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Document</t>
+          <t>Reason</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Pages</t>
+          <t>Purpose</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Variables</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Where Clause</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Selection Criteria</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Join Comment</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Documentation Refs</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Programming Context</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Programming Code</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Programming Document</t>
         </is>
       </c>
     </row>
@@ -553,7 +607,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Table 14-5.02</t>
+          <t>AR.Table_14-5.02.R.1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -563,226 +617,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>SPECIFIED IN SAP</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>PRIMARY OUTCOME MEASURE</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>ADAE.AEBODSYS, ADAE.AEDECOD</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>ADAE[TRTEMFL EQ Y and AESER EQ Y] ADSL[SAFFL EQ Y]</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>COM.JOIN-ADSL-ADAE</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Unique count of subjects that experienced an Adverse Event by Preferred Term, System Organ Class, and Treatment Group and percentages based on the number of subjects in the safety population within each treatment group. The total number of times an event occurred was recorded by Preferred Term, System Organ Class, and Treatment Group. Fisher's exact test was used for treatment comparison of event rates.</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
           <t>LF.CSR</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Display</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Reason</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Purpose</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Dataset</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Variables</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Parameter</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Where Clause</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Join Comment</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Documentation</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Documentation Refs</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Programming Context</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Programming Code</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Programming Document</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>RD.Table_14-5.02</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>AR.Table_14-5.02.R.1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Incidence of Treatment Emergent Serious Adverse Events by Treatment Group</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>SPECIFIED IN SAP</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>PRIMARY OUTCOME MEASURE</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>ADAE</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>AEBODSYS AEDECOD</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>WC.Table_14-5.02.R.1.ADAE</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>COM.JOIN-ADSL-ADAE</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Unique count of subjects that experienced an Adverse Event by Preferred Term, System Organ Class, and Treatment Group and percentages based on the number of subjects in the safety population within each treatment group. The total number of times an event occurred was recorded by Preferred Term, System Organ Class, and Treatment Group. Fisher's exact test was used for treatment comparison of event rates.</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>LF.CSR</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>SAS version 9.2</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>LF.at14-5-02.sas</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>RD.Table_14-5.02</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>AR.Table_14-5.02.R.1</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Incidence of Treatment Emergent Serious Adverse Events by Treatment Group</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>SPECIFIED IN SAP</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>PRIMARY OUTCOME MEASURE</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>ADSL</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>WC.Table_14-5.02.R.1.ADSL</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>COM.JOIN-ADSL-ADAE</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Unique count of subjects that experienced an Adverse Event by Preferred Term, System Organ Class, and Treatment Group and percentages based on the number of subjects in the safety population within each treatment group. The total number of times an event occurred was recorded by Preferred Term, System Organ Class, and Treatment Group. Fisher's exact test was used for treatment comparison of event rates.</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>LF.CSR</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>SAS version 9.2</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>LF.at14-5-02.sas</t>
         </is>
@@ -6437,7 +6310,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J69"/>
+  <dimension ref="A1:K69"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -6483,10 +6356,15 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>NCI Term Code</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
@@ -6513,7 +6391,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="J2">
+      <c r="K2">
         <v>1</v>
       </c>
     </row>
@@ -6538,7 +6416,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>2</v>
       </c>
     </row>
@@ -6563,7 +6441,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>3</v>
       </c>
     </row>
@@ -6683,7 +6561,7 @@
           <t>C66781</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>C29848</t>
         </is>
@@ -6880,7 +6758,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="J15">
+      <c r="K15">
         <v>1</v>
       </c>
     </row>
@@ -6910,7 +6788,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="J16">
+      <c r="K16">
         <v>2</v>
       </c>
     </row>
@@ -6940,7 +6818,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="J17">
+      <c r="K17">
         <v>3</v>
       </c>
     </row>
@@ -6978,7 +6856,7 @@
           <t>C81223</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>C81212</t>
         </is>
@@ -7018,7 +6896,7 @@
           <t>C81223</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>C81211</t>
         </is>
@@ -7058,7 +6936,7 @@
           <t>C81223</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>C81210</t>
         </is>
@@ -7093,7 +6971,7 @@
           <t>C66727</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>C25250</t>
         </is>
@@ -7128,7 +7006,7 @@
           <t>C66727</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>C41331</t>
         </is>
@@ -7163,7 +7041,7 @@
           <t>C66727</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>C28554</t>
         </is>
@@ -7198,7 +7076,7 @@
           <t>C66727</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>C48226</t>
         </is>
@@ -7233,7 +7111,7 @@
           <t>C66727</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>C48227</t>
         </is>
@@ -7268,7 +7146,7 @@
           <t>C66727</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>C48250</t>
         </is>
@@ -7303,7 +7181,7 @@
           <t>C66727</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>C142185</t>
         </is>
@@ -7338,7 +7216,7 @@
           <t>C66727</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>C49632</t>
         </is>
@@ -7373,7 +7251,7 @@
           <t>C66727</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>C49634</t>
         </is>
@@ -7650,7 +7528,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="J40">
+      <c r="K40">
         <v>1</v>
       </c>
     </row>
@@ -7675,7 +7553,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="J41">
+      <c r="K41">
         <v>2</v>
       </c>
     </row>
@@ -7705,7 +7583,7 @@
           <t>C124296</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>C25250</t>
         </is>
@@ -7737,7 +7615,7 @@
           <t>C124296</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>C25484</t>
         </is>
@@ -7769,7 +7647,7 @@
           <t>C66790</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>C17459</t>
         </is>
@@ -7801,7 +7679,7 @@
           <t>C66790</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>C41222</t>
         </is>
@@ -7836,7 +7714,7 @@
           <t>C74457</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>C41261</t>
         </is>
@@ -7871,7 +7749,7 @@
           <t>C74457</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>C16352</t>
         </is>
@@ -7906,7 +7784,7 @@
           <t>C74457</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>C41260</t>
         </is>
@@ -7941,7 +7819,7 @@
           <t>C74457</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>C41259</t>
         </is>
@@ -8086,7 +7964,7 @@
           <t>C66731</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t>C16576</t>
         </is>
@@ -8123,7 +8001,7 @@
           <t>C66731</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t>C20197</t>
         </is>
@@ -8160,7 +8038,7 @@
           <t>C66731</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>C17998</t>
         </is>
@@ -8197,7 +8075,7 @@
           <t>C66742</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t>C49487</t>
         </is>
@@ -8234,7 +8112,7 @@
           <t>C66742</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t>C49488</t>
         </is>
@@ -8271,7 +8149,7 @@
           <t>C66742</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t>C49488</t>
         </is>
@@ -8308,12 +8186,12 @@
           <t>C66769</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t>C41338</t>
         </is>
       </c>
-      <c r="J60">
+      <c r="K60">
         <v>1</v>
       </c>
     </row>
@@ -8348,12 +8226,12 @@
           <t>C66769</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t>C41339</t>
         </is>
       </c>
-      <c r="J61">
+      <c r="K61">
         <v>2</v>
       </c>
     </row>
@@ -8388,12 +8266,12 @@
           <t>C66769</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t>C41340</t>
         </is>
       </c>
-      <c r="J62">
+      <c r="K62">
         <v>3</v>
       </c>
     </row>
@@ -8418,7 +8296,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="J63">
+      <c r="K63">
         <v>1</v>
       </c>
     </row>
@@ -8443,7 +8321,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="J64">
+      <c r="K64">
         <v>2</v>
       </c>
     </row>
@@ -8468,7 +8346,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="J65">
+      <c r="K65">
         <v>3</v>
       </c>
     </row>
@@ -8493,7 +8371,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="J66">
+      <c r="K66">
         <v>4</v>
       </c>
     </row>
@@ -8523,7 +8401,7 @@
           <t>C66768</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
+      <c r="J67" t="inlineStr">
         <is>
           <t>C49498</t>
         </is>
@@ -8555,7 +8433,7 @@
           <t>C66768</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
+      <c r="J68" t="inlineStr">
         <is>
           <t>C49494</t>
         </is>
@@ -8587,7 +8465,7 @@
           <t>C66768</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
+      <c r="J69" t="inlineStr">
         <is>
           <t>C48275</t>
         </is>
@@ -10031,7 +9909,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -10042,25 +9920,30 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Dataset</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Variable</t>
+          <t>Type</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Comparator</t>
+          <t>Version</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Value</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Publishing Set</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
@@ -10069,81 +9952,138 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>WC.Table_14-5.02.R.1.ADAE</t>
+          <t>STD.01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ADAE</t>
+          <t>ADaMIG</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>TRTEMFL</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EQ</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>Final</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>WC.Table_14-5.02.R.1.ADAE</t>
+          <t>STD.CT.01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ADAE</t>
+          <t>CDISC/NCI</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AESER</t>
+          <t>CT</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EQ</t>
+          <t>2017-09-29</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>ADaM</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>COM.STDCT.01</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>WC.Table_14-5.02.R.1.ADSL</t>
+          <t>STD.CT.02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ADSL</t>
+          <t>CDISC/NCI</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SAFFL</t>
+          <t>CT</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EQ</t>
+          <t>2018-06-29</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>SDTM</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>COM.STDCT.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>STD.5</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CDISC/NCI</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>DEFINE-XML</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>COM.STD5</t>
         </is>
       </c>
     </row>
@@ -10154,7 +10094,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -10170,165 +10110,44 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Type</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Version</t>
+          <t>Document</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Publishing Set</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Comment</t>
+          <t>Pages</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>STD.01</t>
+          <t>RD.Table_14-5.02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ADaMIG</t>
+          <t>Table 14-5.02</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>Incidence of Treatment Emergent Serious Adverse Events by Treatment Group</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>LF.CSR</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Final</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>STD.CT.01</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>CDISC/NCI</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>CT</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2017-09-29</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Final</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>ADaM</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>COM.STDCT.01</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>STD.CT.02</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>CDISC/NCI</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>CT</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2018-06-29</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Final</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>SDTM</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>COM.STDCT.02</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>STD.5</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>CDISC/NCI</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>CT</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2025-09-26</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Final</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>DEFINE-XML</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>COM.STD5</t>
+          <t>3</t>
         </is>
       </c>
     </row>

--- a/inst/extdata/adam-spec.xlsx
+++ b/inst/extdata/adam-spec.xlsx
@@ -360,7 +360,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -378,132 +378,156 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>define_version</t>
+          <t>StudyName</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2.1.10</t>
+          <t>CDISC-Sample</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>study_oid</t>
+          <t>StudyDescription</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>STDY.www.cdisc.org/CDISC-Sample/ADaM</t>
+          <t>CDISC-Sample Data Definition</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>file_oid</t>
+          <t>ProtocolName</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>www.cdisc.org/CDISC-Sample/ADaM/1/Define-XML_2.1.0</t>
+          <t>CDISC-Sample</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>odm_context</t>
+          <t>DefineVersion</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Submission</t>
+          <t>2.1.10</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>metadata_version_oid</t>
+          <t>StudyOID</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MDV.CDISC01.ADaMIG.1.1.ADaM.2.1</t>
+          <t>STDY.www.cdisc.org/CDISC-Sample/ADaM</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>metadata_version_name</t>
+          <t>FileOID</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Study CDISC-Sample, Data Definitions</t>
+          <t>www.cdisc.org/CDISC-Sample/ADaM/1/Define-XML_2.1.0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>metadata_version_description</t>
+          <t>Context</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Study CDISC-Sample, Data Definitions</t>
+          <t>Submission</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>originator</t>
+          <t>MetaDataVersionOID</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CDISC Data Exchange Standards Team</t>
+          <t>MDV.CDISC01.ADaMIG.1.1.ADaM.2.1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>StudyName</t>
+          <t>MetaDataVersionName</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CDISC-Sample</t>
+          <t>Study CDISC-Sample, Data Definitions</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>StudyDescription</t>
+          <t>MetaDataVersionDescription</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CDISC-Sample Data Definition</t>
+          <t>Study CDISC-Sample, Data Definitions</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ProtocolName</t>
+          <t>Originator</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CDISC-Sample</t>
+          <t>CDISC Data Exchange Standards Team</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>StandardName</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ADaM-IG</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>StandardVersion</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1.1</t>
         </is>
       </c>
     </row>

--- a/inst/extdata/adam-spec.xlsx
+++ b/inst/extdata/adam-spec.xlsx
@@ -7,16 +7,19 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Define" sheetId="1" r:id="rId1"/>
+    <sheet name="Study" sheetId="1" r:id="rId1"/>
     <sheet name="Datasets" sheetId="2" r:id="rId2"/>
     <sheet name="Variables" sheetId="3" r:id="rId3"/>
     <sheet name="Codelists" sheetId="4" r:id="rId4"/>
     <sheet name="Methods" sheetId="5" r:id="rId5"/>
     <sheet name="Comments" sheetId="6" r:id="rId6"/>
     <sheet name="Documents" sheetId="7" r:id="rId7"/>
-    <sheet name="Standards" sheetId="8" r:id="rId8"/>
-    <sheet name="Analysis Displays" sheetId="9" r:id="rId9"/>
-    <sheet name="Analysis Results" sheetId="10" r:id="rId10"/>
+    <sheet name="WhereClauses" sheetId="8" r:id="rId8"/>
+    <sheet name="Dictionaries" sheetId="9" r:id="rId9"/>
+    <sheet name="Standards" sheetId="10" r:id="rId10"/>
+    <sheet name="Analysis Displays" sheetId="11" r:id="rId11"/>
+    <sheet name="Analysis Results" sheetId="12" r:id="rId12"/>
+    <sheet name="Analysis Criteria" sheetId="13" r:id="rId13"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -538,6 +541,255 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Version</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Publishing Set</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>STD.01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ADaMIG</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>IG</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>STD.CT.01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CDISC/NCI</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2017-09-29</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>ADaM</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>COM.STDCT.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>STD.CT.02</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CDISC/NCI</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2018-06-29</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>SDTM</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>COM.STDCT.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>STD.5</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CDISC/NCI</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>DEFINE-XML</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>COM.STD5</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>RD.Table_14-5.02</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Table 14-5.02</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Incidence of Treatment Emergent Serious Adverse Events by Treatment Group</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>LF.CSR</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -649,16 +901,6 @@
           <t>PRIMARY OUTCOME MEASURE</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>ADAE.AEBODSYS, ADAE.AEDECOD</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>ADAE[TRTEMFL EQ Y and AESER EQ Y] ADSL[SAFFL EQ Y]</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>COM.JOIN-ADSL-ADAE</t>
@@ -682,6 +924,92 @@
       <c r="P2" t="inlineStr">
         <is>
           <t>LF.at14-5-02.sas</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Display</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Variables</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Where Clause</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>RD.Table_14-5.02</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>AR.Table_14-5.02.R.1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ADAE</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>AEBODSYS AEDECOD</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>WC.Table_14-5.02.R.1.ADAE</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>RD.Table_14-5.02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>AR.Table_14-5.02.R.1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ADSL</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>WC.Table_14-5.02.R.1.ADSL</t>
         </is>
       </c>
     </row>
@@ -4755,6 +5083,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>CL.AEDICT</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>Predecessor</t>
@@ -4798,6 +5131,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>CL.AEDICTN</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>Predecessor</t>
@@ -4841,6 +5179,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>CL.AEDICT</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>Predecessor</t>
@@ -4884,6 +5227,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>CL.AEDICTN</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>Predecessor</t>
@@ -4927,6 +5275,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>CL.AEDICT</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>Predecessor</t>
@@ -4970,6 +5323,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>CL.AEDICTN</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>Predecessor</t>
@@ -5013,6 +5371,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>CL.AEDICT</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>Predecessor</t>
@@ -5056,6 +5419,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>CL.AEDICTN</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>Predecessor</t>
@@ -5099,6 +5467,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>CL.AEDICT</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>Predecessor</t>
@@ -5142,6 +5515,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>CL.AEDICT</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>Predecessor</t>
@@ -5183,6 +5561,11 @@
       <c r="I83" t="inlineStr">
         <is>
           <t>No</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>CL.AEDICTN</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -9933,7 +10316,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -9944,30 +10327,25 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Dataset</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Type</t>
+          <t>Variable</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Version</t>
+          <t>Comparator</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Value</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Publishing Set</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
@@ -9976,138 +10354,81 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>STD.01</t>
+          <t>WC.Table_14-5.02.R.1.ADAE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ADaMIG</t>
+          <t>ADAE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>TRTEMFL</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>EQ</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>STD.CT.01</t>
+          <t>WC.Table_14-5.02.R.1.ADAE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CDISC/NCI</t>
+          <t>ADAE</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CT</t>
+          <t>AESER</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2017-09-29</t>
+          <t>EQ</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Final</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>ADaM</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>COM.STDCT.01</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>STD.CT.02</t>
+          <t>WC.Table_14-5.02.R.1.ADSL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CDISC/NCI</t>
+          <t>ADSL</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CT</t>
+          <t>SAFFL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2018-06-29</t>
+          <t>EQ</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Final</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>SDTM</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>COM.STDCT.02</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>STD.5</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>CDISC/NCI</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>CT</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2025-09-26</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Final</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>DEFINE-XML</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>COM.STD5</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -10118,7 +10439,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -10134,44 +10455,91 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Data Type</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Document</t>
+          <t>Dictionary</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Pages</t>
+          <t>Version</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Href</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Ref</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>RD.Table_14-5.02</t>
+          <t>CL.AEDICT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Table 14-5.02</t>
+          <t>Adverse Event Dictionary</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Incidence of Treatment Emergent Serious Adverse Events by Treatment Group</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LF.CSR</t>
+          <t>MedDRA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>http://www.meddra.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CL.AEDICTN</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Adverse Event Dictionary (N)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>MedDRA</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>http://www.meddra.org/</t>
         </is>
       </c>
     </row>

--- a/inst/extdata/adam-spec.xlsx
+++ b/inst/extdata/adam-spec.xlsx
@@ -7,13 +7,19 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Define" sheetId="1" r:id="rId1"/>
+    <sheet name="Study" sheetId="1" r:id="rId1"/>
     <sheet name="Datasets" sheetId="2" r:id="rId2"/>
     <sheet name="Variables" sheetId="3" r:id="rId3"/>
     <sheet name="Codelists" sheetId="4" r:id="rId4"/>
     <sheet name="Methods" sheetId="5" r:id="rId5"/>
     <sheet name="Comments" sheetId="6" r:id="rId6"/>
     <sheet name="Documents" sheetId="7" r:id="rId7"/>
+    <sheet name="WhereClauses" sheetId="8" r:id="rId8"/>
+    <sheet name="Dictionaries" sheetId="9" r:id="rId9"/>
+    <sheet name="Standards" sheetId="10" r:id="rId10"/>
+    <sheet name="Analysis Displays" sheetId="11" r:id="rId11"/>
+    <sheet name="Analysis Results" sheetId="12" r:id="rId12"/>
+    <sheet name="Analysis Criteria" sheetId="13" r:id="rId13"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -357,7 +363,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -375,48 +381,635 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>define_version</t>
+          <t>StudyName</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2.1.10</t>
+          <t>CDISC-Sample</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>StudyName</t>
+          <t>StudyDescription</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CDISC-Sample</t>
+          <t>CDISC-Sample Data Definition</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>StudyDescription</t>
+          <t>ProtocolName</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CDISC-Sample Data Definition</t>
+          <t>CDISC-Sample</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ProtocolName</t>
+          <t>DefineVersion</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CDISC-Sample</t>
+          <t>2.1.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>StudyOID</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>STDY.www.cdisc.org/CDISC-Sample/ADaM</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>FileOID</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>www.cdisc.org/CDISC-Sample/ADaM/1/Define-XML_2.1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Context</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Submission</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>MetaDataVersionOID</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>MDV.CDISC01.ADaMIG.1.1.ADaM.2.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>MetaDataVersionName</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Study CDISC-Sample, Data Definitions</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>MetaDataVersionDescription</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Study CDISC-Sample, Data Definitions</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Originator</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>CDISC Data Exchange Standards Team</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>StandardName</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ADaM-IG</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>StandardVersion</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Version</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Publishing Set</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>STD.01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ADaMIG</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>IG</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>STD.CT.01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CDISC/NCI</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2017-09-29</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>ADaM</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>COM.STDCT.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>STD.CT.02</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CDISC/NCI</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2018-06-29</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>SDTM</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>COM.STDCT.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>STD.5</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CDISC/NCI</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>DEFINE-XML</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>COM.STD5</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>RD.Table_14-5.02</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Table 14-5.02</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Incidence of Treatment Emergent Serious Adverse Events by Treatment Group</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>LF.CSR</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Display</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Reason</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Purpose</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Variables</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Where Clause</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Selection Criteria</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Join Comment</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Documentation Refs</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Programming Context</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Programming Code</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Programming Document</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>RD.Table_14-5.02</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>AR.Table_14-5.02.R.1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Incidence of Treatment Emergent Serious Adverse Events by Treatment Group</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>SPECIFIED IN SAP</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>PRIMARY OUTCOME MEASURE</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>COM.JOIN-ADSL-ADAE</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Unique count of subjects that experienced an Adverse Event by Preferred Term, System Organ Class, and Treatment Group and percentages based on the number of subjects in the safety population within each treatment group. The total number of times an event occurred was recorded by Preferred Term, System Organ Class, and Treatment Group. Fisher's exact test was used for treatment comparison of event rates.</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>LF.CSR</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>SAS version 9.2</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>LF.at14-5-02.sas</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Display</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Variables</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Where Clause</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>RD.Table_14-5.02</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>AR.Table_14-5.02.R.1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ADAE</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>AEBODSYS AEDECOD</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>WC.Table_14-5.02.R.1.ADAE</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>RD.Table_14-5.02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>AR.Table_14-5.02.R.1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ADSL</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>WC.Table_14-5.02.R.1.ADSL</t>
         </is>
       </c>
     </row>
@@ -427,7 +1020,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -471,6 +1064,36 @@
           <t>Comment</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>SAS Dataset Name</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Purpose</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Repeating</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Reference Data</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Has No Data</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -508,6 +1131,26 @@
           <t>COM.ADSL</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>ADSL</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Analysis</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -525,6 +1168,11 @@
           <t>OCCURRENCE DATA STRUCTURE</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ADVERSE EVENT</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>one record per subject per adverse event</t>
@@ -543,6 +1191,26 @@
       <c r="H3" t="inlineStr">
         <is>
           <t>COM.ADAE</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ADAE</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Analysis</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -553,7 +1221,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R105"/>
+  <dimension ref="A1:U105"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -624,27 +1292,42 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>Origin Document</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>Pages</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Method</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Predecessor</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Comment</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>SAS Field Name</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Has No Data</t>
         </is>
       </c>
     </row>
@@ -669,7 +1352,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F2">
@@ -683,6 +1366,11 @@
       <c r="L2" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>STUDYID</t>
         </is>
       </c>
     </row>
@@ -707,7 +1395,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F3">
@@ -721,6 +1409,11 @@
       <c r="L3" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>USUBJID</t>
         </is>
       </c>
     </row>
@@ -745,7 +1438,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F4">
@@ -759,6 +1452,11 @@
       <c r="L4" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>SUBJID</t>
         </is>
       </c>
     </row>
@@ -783,7 +1481,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F5">
@@ -797,6 +1495,11 @@
       <c r="L5" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>SITEID</t>
         </is>
       </c>
     </row>
@@ -821,7 +1524,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F6">
@@ -837,9 +1540,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>MT.ADSL.SITEGR1</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>SITEGR1</t>
         </is>
       </c>
     </row>
@@ -864,7 +1577,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F7">
@@ -883,6 +1596,11 @@
       <c r="L7" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>ARM</t>
         </is>
       </c>
     </row>
@@ -907,7 +1625,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F8">
@@ -926,6 +1644,11 @@
       <c r="L8" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>TRT01P</t>
         </is>
       </c>
     </row>
@@ -971,9 +1694,19 @@
           <t>Assigned</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>COM.ADSL.TRT01PN</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>TRT01PN</t>
         </is>
       </c>
     </row>
@@ -998,7 +1731,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F10">
@@ -1019,9 +1752,19 @@
           <t>Assigned</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>COM.ADSL.TRT01A</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>TRT01A</t>
         </is>
       </c>
     </row>
@@ -1067,9 +1810,19 @@
           <t>Assigned</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
         <is>
           <t>COM.ADSL.TRT01AN</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>TRT01AN</t>
         </is>
       </c>
     </row>
@@ -1115,9 +1868,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
         <is>
           <t>MT.ADSL.TRTSDT</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>TRTSDT</t>
         </is>
       </c>
     </row>
@@ -1163,9 +1926,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
         <is>
           <t>MT.ADSL.TRTEDT</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>TRTEDT</t>
         </is>
       </c>
     </row>
@@ -1206,9 +1979,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
         <is>
           <t>MT.ADSL.TRTDURD</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>TRTDURD</t>
         </is>
       </c>
     </row>
@@ -1257,9 +2040,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
         <is>
           <t>MT.ADSL.AVGDD</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>AVGDD</t>
         </is>
       </c>
     </row>
@@ -1308,9 +2101,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
         <is>
           <t>MT.ADSL.CUMDOSE</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>CUMDOSE</t>
         </is>
       </c>
     </row>
@@ -1351,6 +2154,11 @@
           <t>Predecessor</t>
         </is>
       </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>AGE</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18">
@@ -1373,7 +2181,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F18">
@@ -1394,9 +2202,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
         <is>
           <t>MT.ADSL.AGEGR1</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>AGEGR1</t>
         </is>
       </c>
     </row>
@@ -1442,9 +2260,19 @@
           <t>Assigned</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
         <is>
           <t>COM.ADSL.AGEGR1N</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>AGEGR1N</t>
         </is>
       </c>
     </row>
@@ -1469,7 +2297,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F20">
@@ -1488,6 +2316,11 @@
       <c r="L20" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>AGEU</t>
         </is>
       </c>
     </row>
@@ -1512,7 +2345,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F21">
@@ -1531,6 +2364,11 @@
       <c r="L21" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>RACE</t>
         </is>
       </c>
     </row>
@@ -1576,9 +2414,19 @@
           <t>Assigned</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
         <is>
           <t>COM.ADSL.RACEN</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>RACEN</t>
         </is>
       </c>
     </row>
@@ -1603,7 +2451,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F23">
@@ -1622,6 +2470,11 @@
       <c r="L23" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>SEX</t>
         </is>
       </c>
     </row>
@@ -1646,7 +2499,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F24">
@@ -1665,6 +2518,11 @@
       <c r="L24" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>ETHNIC</t>
         </is>
       </c>
     </row>
@@ -1689,7 +2547,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F25">
@@ -1710,9 +2568,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
         <is>
           <t>MT.ADSL.SAFFL</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>SAFFL</t>
         </is>
       </c>
     </row>
@@ -1737,7 +2605,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F26">
@@ -1758,9 +2626,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
         <is>
           <t>MT.ADSL.ITTFL</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>ITTFL</t>
         </is>
       </c>
     </row>
@@ -1785,7 +2663,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F27">
@@ -1806,9 +2684,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
         <is>
           <t>MT.ADSL.EFFFL</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>EFFFL</t>
         </is>
       </c>
     </row>
@@ -1833,7 +2721,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F28">
@@ -1854,9 +2742,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
         <is>
           <t>MT.ADSL.COMP8FL</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>COMP8FL</t>
         </is>
       </c>
     </row>
@@ -1881,7 +2779,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F29">
@@ -1902,9 +2800,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
         <is>
           <t>MT.ADSL.COMP16FL</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>COMP16FL</t>
         </is>
       </c>
     </row>
@@ -1929,7 +2837,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F30">
@@ -1950,9 +2858,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
         <is>
           <t>MT.ADSL.COMP24FL</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>COMP24FL</t>
         </is>
       </c>
     </row>
@@ -1977,7 +2895,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F31">
@@ -1998,9 +2916,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
         <is>
           <t>MT.ADSL.DISCONFL</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>DISCONFL</t>
         </is>
       </c>
     </row>
@@ -2025,7 +2953,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F32">
@@ -2046,9 +2974,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
         <is>
           <t>MT.ADSL.DSRAEFL</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>DSRAEFL</t>
         </is>
       </c>
     </row>
@@ -2073,7 +3011,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F33">
@@ -2092,6 +3030,11 @@
       <c r="L33" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>DTHFL</t>
         </is>
       </c>
     </row>
@@ -2140,9 +3083,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
         <is>
           <t>MT.ADSL.BMIBL</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>BMIBL</t>
         </is>
       </c>
     </row>
@@ -2167,7 +3120,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F35">
@@ -2188,9 +3141,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
         <is>
           <t>MT.ADSL.BMIBLGR1</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>BMIBLGR1</t>
         </is>
       </c>
     </row>
@@ -2239,9 +3202,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
         <is>
           <t>MT.ADSL.HEIGHTBL</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>HEIGHTBL</t>
         </is>
       </c>
     </row>
@@ -2290,9 +3263,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
         <is>
           <t>MT.ADSL.WEIGHTBL</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>WEIGHTBL</t>
         </is>
       </c>
     </row>
@@ -2333,9 +3316,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
         <is>
           <t>MT.ADSL.EDUCLVL</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>EDUCLVL</t>
         </is>
       </c>
     </row>
@@ -2381,9 +3374,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
         <is>
           <t>MT.ADSL.DISONDT</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>DISONDT</t>
         </is>
       </c>
     </row>
@@ -2432,9 +3435,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr">
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
         <is>
           <t>MT.ADSL.DURDIS</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>DURDIS</t>
         </is>
       </c>
     </row>
@@ -2459,7 +3472,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F41">
@@ -2480,9 +3493,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
         <is>
           <t>MT.ADSL.DURDSGR1</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>DURDSGR1</t>
         </is>
       </c>
     </row>
@@ -2528,9 +3551,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
         <is>
           <t>MT.ADSL.VISIT1DT</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>VISIT1DT</t>
         </is>
       </c>
     </row>
@@ -2568,6 +3601,11 @@
           <t>Predecessor</t>
         </is>
       </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>RFSTDTC</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44">
@@ -2603,6 +3641,11 @@
           <t>Predecessor</t>
         </is>
       </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>RFENDTC</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45">
@@ -2641,9 +3684,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
         <is>
           <t>MT.ADSL.VISNUMEN</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>VISNUMEN</t>
         </is>
       </c>
     </row>
@@ -2684,9 +3737,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr">
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
         <is>
           <t>MT.ADSL.RFENDT</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>RFENDT</t>
         </is>
       </c>
     </row>
@@ -2711,7 +3774,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F47">
@@ -2732,9 +3795,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr">
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
         <is>
           <t>MT.ADSL.EOSSTT</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>EOSSTT</t>
         </is>
       </c>
     </row>
@@ -2759,7 +3832,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F48">
@@ -2780,9 +3853,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr">
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
         <is>
           <t>MT.ADSL.DCSREAS</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>DCSREAS</t>
         </is>
       </c>
     </row>
@@ -2807,7 +3890,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F49">
@@ -2826,6 +3909,11 @@
       <c r="L49" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>EOSDISP</t>
         </is>
       </c>
     </row>
@@ -2866,9 +3954,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
         <is>
           <t>MT.ADSL.MMS1TSBL</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>MMS1TSBL</t>
         </is>
       </c>
     </row>
@@ -2893,7 +3991,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F51">
@@ -2907,6 +4005,11 @@
       <c r="L51" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>STUDYID</t>
         </is>
       </c>
     </row>
@@ -2931,7 +4034,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F52">
@@ -2945,6 +4048,11 @@
       <c r="L52" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>SITEID</t>
         </is>
       </c>
     </row>
@@ -2969,7 +4077,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F53">
@@ -2983,6 +4091,11 @@
       <c r="L53" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>USUBJID</t>
         </is>
       </c>
     </row>
@@ -3007,7 +4120,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F54">
@@ -3026,6 +4139,11 @@
       <c r="L54" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>TRTA</t>
         </is>
       </c>
     </row>
@@ -3071,6 +4189,11 @@
           <t>Predecessor</t>
         </is>
       </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>TRTAN</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56">
@@ -3109,6 +4232,11 @@
           <t>Predecessor</t>
         </is>
       </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>AGE</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57">
@@ -3131,7 +4259,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F57">
@@ -3150,6 +4278,11 @@
       <c r="L57" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>AGEGR1</t>
         </is>
       </c>
     </row>
@@ -3195,6 +4328,11 @@
           <t>Predecessor</t>
         </is>
       </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>AGEGR1N</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59">
@@ -3217,7 +4355,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F59">
@@ -3236,6 +4374,11 @@
       <c r="L59" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>RACE</t>
         </is>
       </c>
     </row>
@@ -3281,6 +4424,11 @@
           <t>Predecessor</t>
         </is>
       </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>RACEN</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61">
@@ -3303,7 +4451,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F61">
@@ -3322,6 +4470,11 @@
       <c r="L61" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>SEX</t>
         </is>
       </c>
     </row>
@@ -3346,7 +4499,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F62">
@@ -3365,6 +4518,11 @@
       <c r="L62" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>SAFFL</t>
         </is>
       </c>
     </row>
@@ -3410,6 +4568,11 @@
           <t>Predecessor</t>
         </is>
       </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>TRTSDT</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64">
@@ -3453,6 +4616,11 @@
           <t>Predecessor</t>
         </is>
       </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>TRTEDT</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65">
@@ -3496,9 +4664,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O65" t="inlineStr">
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
         <is>
           <t>MT.ADAE.ASTDT</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>ASTDT</t>
         </is>
       </c>
     </row>
@@ -3523,7 +4701,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F66">
@@ -3544,9 +4722,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O66" t="inlineStr">
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
         <is>
           <t>MT.ADAE.ASTDTF</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>ASTDTF</t>
         </is>
       </c>
     </row>
@@ -3587,9 +4775,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O67" t="inlineStr">
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
         <is>
           <t>MT.ADAE.ASTDY</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>ASTDY</t>
         </is>
       </c>
     </row>
@@ -3635,9 +4833,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O68" t="inlineStr">
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
         <is>
           <t>MT.ADAE.AENDT</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>AENDT</t>
         </is>
       </c>
     </row>
@@ -3678,9 +4886,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O69" t="inlineStr">
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
         <is>
           <t>MT.ADAE.AENDY</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>AENDY</t>
         </is>
       </c>
     </row>
@@ -3721,9 +4939,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O70" t="inlineStr">
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
         <is>
           <t>MT.ADAE.ADURN</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>ADURN</t>
         </is>
       </c>
     </row>
@@ -3748,7 +4976,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F71">
@@ -3764,9 +4992,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O71" t="inlineStr">
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
         <is>
           <t>MT.ADAE.ADURU</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>ADURU</t>
         </is>
       </c>
     </row>
@@ -3791,7 +5029,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F72">
@@ -3805,6 +5043,11 @@
       <c r="L72" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>AETERM</t>
         </is>
       </c>
     </row>
@@ -3829,7 +5072,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F73">
@@ -3840,9 +5083,19 @@
           <t>No</t>
         </is>
       </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>CL.AEDICT</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>AELLT</t>
         </is>
       </c>
     </row>
@@ -3878,9 +5131,19 @@
           <t>No</t>
         </is>
       </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>CL.AEDICTN</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>AELLTCD</t>
         </is>
       </c>
     </row>
@@ -3905,7 +5168,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F75">
@@ -3916,9 +5179,19 @@
           <t>No</t>
         </is>
       </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>CL.AEDICT</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>AEDECOD</t>
         </is>
       </c>
     </row>
@@ -3954,9 +5227,19 @@
           <t>No</t>
         </is>
       </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>CL.AEDICTN</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>AEPTCD</t>
         </is>
       </c>
     </row>
@@ -3981,7 +5264,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F77">
@@ -3992,9 +5275,19 @@
           <t>No</t>
         </is>
       </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>CL.AEDICT</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>AEHLT</t>
         </is>
       </c>
     </row>
@@ -4030,9 +5323,19 @@
           <t>No</t>
         </is>
       </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>CL.AEDICTN</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>AEHLTCD</t>
         </is>
       </c>
     </row>
@@ -4057,7 +5360,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F79">
@@ -4068,9 +5371,19 @@
           <t>No</t>
         </is>
       </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>CL.AEDICT</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>AEHLGT</t>
         </is>
       </c>
     </row>
@@ -4106,9 +5419,19 @@
           <t>No</t>
         </is>
       </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>CL.AEDICTN</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>AEHLGTCD</t>
         </is>
       </c>
     </row>
@@ -4133,7 +5456,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F81">
@@ -4144,9 +5467,19 @@
           <t>No</t>
         </is>
       </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>CL.AEDICT</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>AEBODSYS</t>
         </is>
       </c>
     </row>
@@ -4171,7 +5504,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F82">
@@ -4182,9 +5515,19 @@
           <t>No</t>
         </is>
       </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>CL.AEDICT</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>AESOC</t>
         </is>
       </c>
     </row>
@@ -4220,9 +5563,19 @@
           <t>No</t>
         </is>
       </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>CL.AEDICTN</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>AESOCCD</t>
         </is>
       </c>
     </row>
@@ -4247,7 +5600,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F84">
@@ -4266,6 +5619,11 @@
       <c r="L84" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>AESEV</t>
         </is>
       </c>
     </row>
@@ -4290,7 +5648,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F85">
@@ -4309,6 +5667,11 @@
       <c r="L85" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>AESER</t>
         </is>
       </c>
     </row>
@@ -4333,7 +5696,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F86">
@@ -4352,6 +5715,11 @@
       <c r="L86" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>AESCAN</t>
         </is>
       </c>
     </row>
@@ -4376,7 +5744,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F87">
@@ -4395,6 +5763,11 @@
       <c r="L87" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>AESCONG</t>
         </is>
       </c>
     </row>
@@ -4419,7 +5792,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F88">
@@ -4438,6 +5811,11 @@
       <c r="L88" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>AESDISAB</t>
         </is>
       </c>
     </row>
@@ -4462,7 +5840,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F89">
@@ -4481,6 +5859,11 @@
       <c r="L89" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>AESDTH</t>
         </is>
       </c>
     </row>
@@ -4505,7 +5888,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F90">
@@ -4524,6 +5907,11 @@
       <c r="L90" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>AESHOSP</t>
         </is>
       </c>
     </row>
@@ -4548,7 +5936,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F91">
@@ -4567,6 +5955,11 @@
       <c r="L91" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>AESLIFE</t>
         </is>
       </c>
     </row>
@@ -4591,7 +5984,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F92">
@@ -4610,6 +6003,11 @@
       <c r="L92" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>AESOD</t>
         </is>
       </c>
     </row>
@@ -4634,7 +6032,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F93">
@@ -4653,6 +6051,11 @@
       <c r="L93" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>AEREL</t>
         </is>
       </c>
     </row>
@@ -4677,7 +6080,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F94">
@@ -4691,6 +6094,11 @@
       <c r="L94" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>AEACN</t>
         </is>
       </c>
     </row>
@@ -4715,7 +6123,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F95">
@@ -4734,6 +6142,11 @@
       <c r="L95" t="inlineStr">
         <is>
           <t>Predecessor</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>AEOUT</t>
         </is>
       </c>
     </row>
@@ -4774,6 +6187,11 @@
           <t>Predecessor</t>
         </is>
       </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>AESEQ</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97">
@@ -4796,7 +6214,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F97">
@@ -4817,9 +6235,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O97" t="inlineStr">
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
         <is>
           <t>MT.ADAE.TRTEMFL</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>TRTEMFL</t>
         </is>
       </c>
     </row>
@@ -4844,7 +6272,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F98">
@@ -4865,9 +6293,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O98" t="inlineStr">
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
         <is>
           <t>MT.ADAE.AOCCFL</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>AOCCFL</t>
         </is>
       </c>
     </row>
@@ -4892,7 +6330,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F99">
@@ -4913,9 +6351,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O99" t="inlineStr">
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
         <is>
           <t>MT.ADAE.AOCCSFL</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>AOCCSFL</t>
         </is>
       </c>
     </row>
@@ -4940,7 +6388,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F100">
@@ -4961,9 +6409,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O100" t="inlineStr">
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
         <is>
           <t>MT.ADAE.AOCCPFL</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>AOCCPFL</t>
         </is>
       </c>
     </row>
@@ -4988,7 +6446,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F101">
@@ -5009,9 +6467,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O101" t="inlineStr">
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
         <is>
           <t>MT.ADAE.AOCC02FL</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>AOCC02FL</t>
         </is>
       </c>
     </row>
@@ -5036,7 +6504,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F102">
@@ -5057,9 +6525,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O102" t="inlineStr">
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
         <is>
           <t>MT.ADAE.AOCC03FL</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>AOCC03FL</t>
         </is>
       </c>
     </row>
@@ -5084,7 +6562,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F103">
@@ -5105,9 +6583,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O103" t="inlineStr">
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
         <is>
           <t>MT.ADAE.AOCC04FL</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>AOCC04FL</t>
         </is>
       </c>
     </row>
@@ -5132,7 +6620,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F104">
@@ -5148,9 +6636,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O104" t="inlineStr">
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
         <is>
           <t>MT.ADAE.CQ01NAM</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>CQ01NAM</t>
         </is>
       </c>
     </row>
@@ -5175,7 +6673,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F105">
@@ -5196,9 +6694,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O105" t="inlineStr">
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
         <is>
           <t>MT.ADAE.AOCC01FL</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>AOCC01FL</t>
         </is>
       </c>
     </row>
@@ -5209,7 +6717,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D202"/>
+  <dimension ref="A1:K69"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -5233,6 +6741,41 @@
           <t>Decoded Value</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>NCI Codelist Code</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>SAS Format Name</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>NCI Term Code</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5245,6 +6788,19 @@
           <t>&lt;65</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Age Group</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5257,6 +6813,19 @@
           <t>65-80</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Age Group</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5269,6 +6838,19 @@
           <t>&gt;80</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Age Group</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="K4">
+        <v>3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5289,6 +6871,16 @@
           <t>&lt;65</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Age Group (N)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5309,6 +6901,16 @@
           <t>65-80</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Age Group (N)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5329,6 +6931,16 @@
           <t>&gt;80</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Age Group (N)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5341,6 +6953,26 @@
           <t>YEARS</t>
         </is>
       </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Age Unit</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>C66781</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>C29848</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5356,6 +6988,16 @@
           <t>Placebo</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Actual Treatment</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5371,6 +7013,16 @@
           <t>Xanomeline Low Dose</t>
         </is>
       </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Actual Treatment</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5386,6 +7038,16 @@
           <t>Xanomeline High Dose</t>
         </is>
       </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Actual Treatment</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5406,6 +7068,16 @@
           <t>Placebo</t>
         </is>
       </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Actual Treatment (N)</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5426,6 +7098,16 @@
           <t>Xanomeline Low Dose</t>
         </is>
       </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Actual Treatment (N)</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5446,274 +7128,546 @@
           <t>Xanomeline High Dose</t>
         </is>
       </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Actual Treatment (N)</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CL.AVISIT</t>
-        </is>
-      </c>
-      <c r="B15">
+          <t>CL.BMICAT</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>&lt;25</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Body Mass Index Category</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="K15">
         <v>1</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CL.AVISIT</t>
-        </is>
-      </c>
-      <c r="B16">
+          <t>CL.BMICAT</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>25-&lt;30</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Overweight</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Body Mass Index Category</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="K16">
         <v>2</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Week 8</t>
-        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CL.AVISIT</t>
-        </is>
-      </c>
-      <c r="B17">
+          <t>CL.BMICAT</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>&gt;30</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Obese</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Body Mass Index Category</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="K17">
         <v>3</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Week 16</t>
-        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CL.AVISIT</t>
+          <t>CL.DATEFL</t>
         </is>
       </c>
       <c r="B18">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Week 24</t>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Day Imputed: Day is imputed</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Date Imputation Flag</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>C81223</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>C81212</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CL.AVISITN</t>
+          <t>CL.DATEFL</t>
         </is>
       </c>
       <c r="B19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Baseline</t>
+          <t>Month Imputed: Month and day are imputed</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Date Imputation Flag</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>C81223</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>C81211</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CL.AVISITN</t>
+          <t>CL.DATEFL</t>
         </is>
       </c>
       <c r="B20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Week 8</t>
+          <t>Year Imputed: Entire date (year, month and day) is imputed</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Date Imputation Flag</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>C81223</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>C81210</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CL.AVISITN</t>
+          <t>CL.DISCCD</t>
         </is>
       </c>
       <c r="B21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Week 16</t>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Completion/Reason for Non-Completion</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>C66727</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>C25250</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CL.AVISITN</t>
+          <t>CL.DISCCD</t>
         </is>
       </c>
       <c r="B22">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Week 24</t>
+          <t>ADVERSE EVENT</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Completion/Reason for Non-Completion</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>C66727</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>C41331</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CL.AWU</t>
-        </is>
+          <t>CL.DISCCD</t>
+        </is>
+      </c>
+      <c r="B23">
+        <v>3</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>DAYS</t>
+          <t>DEATH</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Completion/Reason for Non-Completion</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>C66727</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>C28554</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CL.BMICAT</t>
-        </is>
+          <t>CL.DISCCD</t>
+        </is>
+      </c>
+      <c r="B24">
+        <v>4</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>&lt;25</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Normal</t>
+          <t>LACK OF EFFICACY</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Completion/Reason for Non-Completion</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>C66727</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>C48226</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CL.BMICAT</t>
-        </is>
+          <t>CL.DISCCD</t>
+        </is>
+      </c>
+      <c r="B25">
+        <v>5</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>25-&lt;30</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Overweight</t>
+          <t>LOST TO FOLLOW-UP</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Completion/Reason for Non-Completion</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>C66727</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>C48227</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CL.BMICAT</t>
-        </is>
+          <t>CL.DISCCD</t>
+        </is>
+      </c>
+      <c r="B26">
+        <v>6</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>&gt;30</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Obese</t>
+          <t>PHYSICIAN DECISION</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Completion/Reason for Non-Completion</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>C66727</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>C48250</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CL.DATEFL</t>
+          <t>CL.DISCCD</t>
         </is>
       </c>
       <c r="B27">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Day Imputed: Day is imputed</t>
+          <t>PROTOCOL VIOLATION</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Completion/Reason for Non-Completion</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>C66727</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>C142185</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CL.DATEFL</t>
+          <t>CL.DISCCD</t>
         </is>
       </c>
       <c r="B28">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Month Imputed: Month and day are imputed</t>
+          <t>STUDY TERMINATED BY SPONSOR</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Completion/Reason for Non-Completion</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>C66727</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>C49632</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CL.DATEFL</t>
+          <t>CL.DISCCD</t>
         </is>
       </c>
       <c r="B29">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Year Imputed: Entire date (year, month and day) is imputed</t>
+          <t>WITHDRAWAL BY SUBJECT</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Completion/Reason for Non-Completion</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>C66727</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>C49634</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CL.DISCCD</t>
+          <t>CL.DISCREAS</t>
         </is>
       </c>
       <c r="B30">
@@ -5721,14 +7675,24 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Reason for Discontinuation</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>text</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CL.DISCCD</t>
+          <t>CL.DISCREAS</t>
         </is>
       </c>
       <c r="B31">
@@ -5736,14 +7700,24 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ADVERSE EVENT</t>
+          <t>Adverse Event</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Reason for Discontinuation</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>text</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CL.DISCCD</t>
+          <t>CL.DISCREAS</t>
         </is>
       </c>
       <c r="B32">
@@ -5751,14 +7725,24 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>DEATH</t>
+          <t>Death</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Reason for Discontinuation</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>text</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CL.DISCCD</t>
+          <t>CL.DISCREAS</t>
         </is>
       </c>
       <c r="B33">
@@ -5766,14 +7750,24 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>LACK OF EFFICACY</t>
+          <t>I/E Not Met</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Reason for Discontinuation</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>text</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CL.DISCCD</t>
+          <t>CL.DISCREAS</t>
         </is>
       </c>
       <c r="B34">
@@ -5781,14 +7775,24 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>LOST TO FOLLOW-UP</t>
+          <t>Lack of Efficacy</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Reason for Discontinuation</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>text</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CL.DISCCD</t>
+          <t>CL.DISCREAS</t>
         </is>
       </c>
       <c r="B35">
@@ -5796,14 +7800,24 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>PHYSICIAN DECISION</t>
+          <t>Lost to Follow-up</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Reason for Discontinuation</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>text</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CL.DISCCD</t>
+          <t>CL.DISCREAS</t>
         </is>
       </c>
       <c r="B36">
@@ -5811,14 +7825,24 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>PROTOCOL VIOLATION</t>
+          <t>Physician Decision</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Reason for Discontinuation</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>text</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CL.DISCCD</t>
+          <t>CL.DISCREAS</t>
         </is>
       </c>
       <c r="B37">
@@ -5826,14 +7850,24 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>STUDY TERMINATED BY SPONSOR</t>
+          <t>Protocol Violation</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Reason for Discontinuation</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>text</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CL.DISCCD</t>
+          <t>CL.DISCREAS</t>
         </is>
       </c>
       <c r="B38">
@@ -5841,7 +7875,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>WITHDRAWAL BY SUBJECT</t>
+          <t>Sponsor Decision</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Reason for Discontinuation</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>text</t>
         </is>
       </c>
     </row>
@@ -5852,2780 +7896,985 @@
         </is>
       </c>
       <c r="B39">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Withdrew Consent</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Reason for Discontinuation</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>text</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CL.DISCREAS</t>
-        </is>
-      </c>
-      <c r="B40">
-        <v>2</v>
+          <t>CL.DURDISC</t>
+        </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Adverse Event</t>
-        </is>
+          <t>&lt;12</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Disease Duration Group</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="K40">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CL.DISCREAS</t>
-        </is>
-      </c>
-      <c r="B41">
-        <v>3</v>
+          <t>CL.DURDISC</t>
+        </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Death</t>
-        </is>
+          <t>&gt;=12</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Disease Duration Group</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="K41">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CL.DISCREAS</t>
-        </is>
-      </c>
-      <c r="B42">
-        <v>4</v>
+          <t>CL.EOSSTT</t>
+        </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>I/E Not Met</t>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Subject Trial Status</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>C124296</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>C25250</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CL.DISCREAS</t>
-        </is>
-      </c>
-      <c r="B43">
-        <v>5</v>
+          <t>CL.EOSSTT</t>
+        </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Lack of Efficacy</t>
+          <t>DISCONTINUED</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Subject Trial Status</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>C124296</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>C25484</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CL.DISCREAS</t>
-        </is>
-      </c>
-      <c r="B44">
-        <v>6</v>
+          <t>CL.ETHNIC</t>
+        </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Lost to Follow-up</t>
+          <t>HISPANIC OR LATINO</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Ethnic Group</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>C66790</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>C17459</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CL.DISCREAS</t>
-        </is>
-      </c>
-      <c r="B45">
-        <v>7</v>
+          <t>CL.ETHNIC</t>
+        </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Physician Decision</t>
+          <t>NOT HISPANIC OR LATINO</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Ethnic Group</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>C66790</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>C41222</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CL.DISCREAS</t>
+          <t>CL.RACE</t>
         </is>
       </c>
       <c r="B46">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Protocol Violation</t>
+          <t>WHITE</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>C74457</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>C41261</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CL.DISCREAS</t>
+          <t>CL.RACE</t>
         </is>
       </c>
       <c r="B47">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sponsor Decision</t>
+          <t>BLACK OR AFRICAN AMERICAN</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>C74457</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>C16352</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CL.DISCREAS</t>
+          <t>CL.RACE</t>
         </is>
       </c>
       <c r="B48">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Withdrew Consent</t>
+          <t>ASIAN</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>C74457</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>C41260</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>CL.DTYPE</t>
-        </is>
+          <t>CL.RACE</t>
+        </is>
+      </c>
+      <c r="B49">
+        <v>4</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>LOCF</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Last Observation Carried Forward</t>
+          <t>AMERICAN INDIAN OR ALASKA NATIVE</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>C74457</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>C41259</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>CL.DURDISC</t>
+          <t>CL.RACEN</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>&lt;12</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>WHITE</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Race (N)</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>integer</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CL.DURDISC</t>
+          <t>CL.RACEN</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>&gt;=12</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>BLACK OR AFRICAN AMERICAN</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Race (N)</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>integer</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CL.EOSSTT</t>
+          <t>CL.RACEN</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>AMERICAN INDIAN OR ALASKA NATIVE</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Race (N)</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>integer</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CL.EOSSTT</t>
+          <t>CL.RACEN</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>DISCONTINUED</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>ASIAN</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Race (N)</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>integer</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CL.ETHNIC</t>
+          <t>CL.SEX</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>HISPANIC OR LATINO</t>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Sex</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>C66731</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>C16576</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>CL.ETHNIC</t>
+          <t>CL.SEX</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>NOT HISPANIC OR LATINO</t>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Sex</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>C66731</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>C20197</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CL.PARAMCD_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B56">
-        <v>1</v>
+          <t>CL.SEX</t>
+        </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ACITM01</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Word Recall Task</t>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Sex</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>C66731</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>C17998</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>CL.PARAMCD_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B57">
-        <v>2</v>
+          <t>CL.YN</t>
+        </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ACITM02</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Naming Objects And Fingers (Refer To 5 C</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>No Yes Response</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>C66742</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>C49487</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>CL.PARAMCD_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B58">
-        <v>3</v>
+          <t>CL.YN</t>
+        </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ACITM03</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Delayed Word Recall</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>No Yes Response</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>C66742</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>C49488</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>CL.PARAMCD_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B59">
-        <v>4</v>
+          <t>CL.Y_BLANK</t>
+        </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ACITM04</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Commands</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>No Yes Response - Y subset</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>C66742</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>C49488</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>CL.PARAMCD_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B60">
-        <v>5</v>
+          <t>CL.AESEV</t>
+        </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ACITM05</t>
+          <t>MILD</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Constructional Praxis</t>
-        </is>
+          <t>Grade 1</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Severity/Intensity Scale for Adverse Events</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>C66769</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>C41338</t>
+        </is>
+      </c>
+      <c r="K60">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>CL.PARAMCD_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B61">
-        <v>6</v>
+          <t>CL.AESEV</t>
+        </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ACITM06</t>
+          <t>MODERATE</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Ideational Praxis</t>
-        </is>
+          <t>Grade 2</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Severity/Intensity Scale for Adverse Events</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>C66769</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>C41339</t>
+        </is>
+      </c>
+      <c r="K61">
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>CL.PARAMCD_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B62">
-        <v>7</v>
+          <t>CL.AESEV</t>
+        </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ACITM07</t>
+          <t>SEVERE</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Orientation</t>
-        </is>
+          <t>Grade 3</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Severity/Intensity Scale for Adverse Events</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>C66769</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>C41340</t>
+        </is>
+      </c>
+      <c r="K62">
+        <v>3</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>CL.PARAMCD_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B63">
-        <v>8</v>
+          <t>CL.AECAUS</t>
+        </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ACITM08</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Word Recognition</t>
-        </is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Causality</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="K63">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>CL.PARAMCD_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B64">
-        <v>9</v>
+          <t>CL.AECAUS</t>
+        </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ACITM09</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Attention/Visual Search Task</t>
-        </is>
+          <t>POSSIBLE</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Causality</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="K64">
+        <v>2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>CL.PARAMCD_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B65">
-        <v>10</v>
+          <t>CL.AECAUS</t>
+        </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ACITM10</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Maze Solution</t>
-        </is>
+          <t>PROBABLE</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Causality</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="K65">
+        <v>3</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>CL.PARAMCD_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B66">
-        <v>11</v>
+          <t>CL.AECAUS</t>
+        </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ACITM11</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>Spoken Language Ability</t>
-        </is>
+          <t>REMOTE</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Causality</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="K66">
+        <v>4</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>CL.PARAMCD_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B67">
-        <v>12</v>
+          <t>CL.OUT</t>
+        </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ACITM12</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Comprehension Of Spoken Language</t>
+          <t>RECOVERED/RESOLVED</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Outcome of Adverse Event</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>C66768</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>C49498</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>CL.PARAMCD_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B68">
-        <v>13</v>
+          <t>CL.OUT</t>
+        </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ACITM13</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>Word Finding Difficulty In Spontaneous Speech</t>
+          <t>NOT RECOVERED/NOT RESOLVED</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Outcome of Adverse Event</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>C66768</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>C49494</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CL.PARAMCD_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B69">
-        <v>14</v>
+          <t>CL.OUT</t>
+        </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ACITM14</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>Recall Of Test Instructions</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>CL.PARAMCD_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B70">
-        <v>15</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>ACTOT</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>Adas-Cog(11) Subscore</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>CL.PARAMN_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B71">
-        <v>1</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Word Recall Task</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>CL.PARAMN_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B72">
-        <v>2</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>Naming Objects And Fingers (Refer To 5 C</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>CL.PARAMN_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B73">
-        <v>3</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Delayed Word Recall</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>CL.PARAMN_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B74">
-        <v>4</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>Commands</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>CL.PARAMN_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B75">
-        <v>5</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>Constructional Praxis</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>CL.PARAMN_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B76">
-        <v>6</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>Ideational Praxis</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>CL.PARAMN_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B77">
-        <v>7</v>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>Orientation</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>CL.PARAMN_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B78">
-        <v>8</v>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>Word Recognition</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>CL.PARAMN_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B79">
-        <v>9</v>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>Attention/Visual Search Task</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>CL.PARAMN_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B80">
-        <v>10</v>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>Maze Solution</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>CL.PARAMN_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B81">
-        <v>11</v>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>Spoken Language Ability</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>CL.PARAMN_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B82">
-        <v>12</v>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>Comprehension Of Spoken Language</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>CL.PARAMN_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B83">
-        <v>13</v>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>Word Finding Difficulty In Spontaneous S</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>CL.PARAMN_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B84">
-        <v>14</v>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>Recall Of Test Instructions</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>CL.PARAMN_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B85">
-        <v>15</v>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>Adas-Cog(11) Subscore</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>CL.PARAM_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B86">
-        <v>1</v>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Word Recall Task</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>CL.PARAM_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B87">
-        <v>2</v>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Naming Objects And Fingers (Refer To 5 C</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>CL.PARAM_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B88">
-        <v>3</v>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Delayed Word Recall</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>CL.PARAM_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B89">
-        <v>4</v>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Commands</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>CL.PARAM_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B90">
-        <v>5</v>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Constructional Praxis</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>CL.PARAM_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B91">
-        <v>6</v>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Ideational Praxis</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>CL.PARAM_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B92">
-        <v>7</v>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Orientation</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>CL.PARAM_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B93">
-        <v>8</v>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Word Recognition</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>CL.PARAM_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B94">
-        <v>9</v>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Attention/Visual Search Task</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>CL.PARAM_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B95">
-        <v>10</v>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Maze Solution</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>CL.PARAM_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B96">
-        <v>11</v>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Spoken Language Ability</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>CL.PARAM_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B97">
-        <v>12</v>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Comprehension Of Spoken Language</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>CL.PARAM_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B98">
-        <v>13</v>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Word Finding Difficulty In Spontaneous S</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>CL.PARAM_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B99">
-        <v>14</v>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Recall Of Test Instructions</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>CL.PARAM_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B100">
-        <v>15</v>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Adas-Cog(11) Subscore</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>CL.AWRANGE_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B101">
-        <v>1</v>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>&lt;=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>CL.AWRANGE_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B102">
-        <v>2</v>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>2-84</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>CL.AWRANGE_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B103">
-        <v>3</v>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>85-140</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>CL.AWRANGE_ADQSADAS</t>
-        </is>
-      </c>
-      <c r="B104">
-        <v>4</v>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>&gt;140</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>CL.RACE</t>
-        </is>
-      </c>
-      <c r="B105">
-        <v>1</v>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>WHITE</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>CL.RACE</t>
-        </is>
-      </c>
-      <c r="B106">
-        <v>2</v>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>BLACK OR AFRICAN AMERICAN</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>CL.RACE</t>
-        </is>
-      </c>
-      <c r="B107">
-        <v>3</v>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>ASIAN</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>CL.RACE</t>
-        </is>
-      </c>
-      <c r="B108">
-        <v>4</v>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>AMERICAN INDIAN OR ALASKA NATIVE</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>CL.RACEN</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>WHITE</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>CL.RACEN</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>BLACK OR AFRICAN AMERICAN</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>CL.RACEN</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>AMERICAN INDIAN OR ALASKA NATIVE</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>CL.RACEN</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>ASIAN</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>CL.SEX</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>CL.SEX</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>CL.SEX</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>CL.VISIT</t>
-        </is>
-      </c>
-      <c r="B116">
-        <v>1</v>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>SCREENING 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>CL.VISIT</t>
-        </is>
-      </c>
-      <c r="B117">
-        <v>2</v>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>UNSCHEDULED 1.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>CL.VISIT</t>
-        </is>
-      </c>
-      <c r="B118">
-        <v>3</v>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>UNSCHEDULED 1.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>CL.VISIT</t>
-        </is>
-      </c>
-      <c r="B119">
-        <v>4</v>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>UNSCHEDULED 1.3</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>CL.VISIT</t>
-        </is>
-      </c>
-      <c r="B120">
-        <v>5</v>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>SCREENING 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>CL.VISIT</t>
-        </is>
-      </c>
-      <c r="B121">
-        <v>6</v>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>BASELINE</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>CL.VISIT</t>
-        </is>
-      </c>
-      <c r="B122">
-        <v>7</v>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>UNSCHEDULED 3.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>CL.VISIT</t>
-        </is>
-      </c>
-      <c r="B123">
-        <v>8</v>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>AMBUL ECG PLACEMENT</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>CL.VISIT</t>
-        </is>
-      </c>
-      <c r="B124">
-        <v>9</v>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>WEEK 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>CL.VISIT</t>
-        </is>
-      </c>
-      <c r="B125">
-        <v>10</v>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>UNSCHEDULED 4.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>CL.VISIT</t>
-        </is>
-      </c>
-      <c r="B126">
-        <v>11</v>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>UNSCHEDULED 4.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>CL.VISIT</t>
-        </is>
-      </c>
-      <c r="B127">
-        <v>12</v>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>WEEK 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>CL.VISIT</t>
-        </is>
-      </c>
-      <c r="B128">
-        <v>13</v>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>UNSCHEDULED 5.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>CL.VISIT</t>
-        </is>
-      </c>
-      <c r="B129">
-        <v>14</v>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>AMBUL ECG REMOVAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>CL.VISIT</t>
-        </is>
-      </c>
-      <c r="B130">
-        <v>15</v>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>UNSCHEDULED 6.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>CL.VISIT</t>
-        </is>
-      </c>
-      <c r="B131">
-        <v>16</v>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>WEEK 6</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>CL.VISIT</t>
-        </is>
-      </c>
-      <c r="B132">
-        <v>17</v>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>UNSCHEDULED 7.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>CL.VISIT</t>
-        </is>
-      </c>
-      <c r="B133">
-        <v>18</v>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>WEEK 8</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>CL.VISIT</t>
-        </is>
-      </c>
-      <c r="B134">
-        <v>19</v>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>WEEK 10 (T)</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>CL.VISIT</t>
-        </is>
-      </c>
-      <c r="B135">
-        <v>20</v>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>UNSCHEDULED 8.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>CL.VISIT</t>
-        </is>
-      </c>
-      <c r="B136">
-        <v>21</v>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>WEEK 12</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>CL.VISIT</t>
-        </is>
-      </c>
-      <c r="B137">
-        <v>22</v>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>WEEK 14 (T)</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>CL.VISIT</t>
-        </is>
-      </c>
-      <c r="B138">
-        <v>23</v>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>UNSCHEDULED 9.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>CL.VISIT</t>
-        </is>
-      </c>
-      <c r="B139">
-        <v>24</v>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>UNSCHEDULED 9.3</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>CL.VISIT</t>
-        </is>
-      </c>
-      <c r="B140">
-        <v>25</v>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>WEEK 16</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>CL.VISIT</t>
-        </is>
-      </c>
-      <c r="B141">
-        <v>26</v>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>WEEK 18 (T)</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>CL.VISIT</t>
-        </is>
-      </c>
-      <c r="B142">
-        <v>27</v>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>UNSCHEDULED 10.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>CL.VISIT</t>
-        </is>
-      </c>
-      <c r="B143">
-        <v>28</v>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>WEEK 20</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>CL.VISIT</t>
-        </is>
-      </c>
-      <c r="B144">
-        <v>29</v>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>WEEK 22 (T)</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>CL.VISIT</t>
-        </is>
-      </c>
-      <c r="B145">
-        <v>30</v>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>UNSCHEDULED 11.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>CL.VISIT</t>
-        </is>
-      </c>
-      <c r="B146">
-        <v>31</v>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>WEEK 24</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>CL.VISIT</t>
-        </is>
-      </c>
-      <c r="B147">
-        <v>32</v>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>UNSCHEDULED 12.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>CL.VISIT</t>
-        </is>
-      </c>
-      <c r="B148">
-        <v>33</v>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>WEEK 26</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>CL.VISIT</t>
-        </is>
-      </c>
-      <c r="B149">
-        <v>34</v>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>UNSCHEDULED 13.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>CL.VISIT</t>
-        </is>
-      </c>
-      <c r="B150">
-        <v>35</v>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>AE FOLLOW-UP</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>CL.VISIT</t>
-        </is>
-      </c>
-      <c r="B151">
-        <v>36</v>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>RETRIEVAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>CL.VISIT</t>
-        </is>
-      </c>
-      <c r="B152">
-        <v>37</v>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Rash followup</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>CL.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B153">
-        <v>1</v>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>SCREENING 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>CL.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B154">
-        <v>2</v>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>UNSCHEDULED 1.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>CL.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B155">
-        <v>3</v>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>UNSCHEDULED 1.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>CL.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B156">
-        <v>4</v>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>1.3</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>UNSCHEDULED 1.3</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>CL.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B157">
-        <v>5</v>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>SCREENING 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>CL.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B158">
-        <v>6</v>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>BASELINE</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>CL.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B159">
-        <v>7</v>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>UNSCHEDULED 3.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>CL.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B160">
-        <v>8</v>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>AMBUL ECG PLACEMENT</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>CL.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B161">
-        <v>9</v>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>WEEK 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>CL.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B162">
-        <v>10</v>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>4.1</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>UNSCHEDULED 4.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>CL.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B163">
-        <v>11</v>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>4.2</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>UNSCHEDULED 4.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>CL.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B164">
-        <v>12</v>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>WEEK 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>CL.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B165">
-        <v>13</v>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>5.1</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>UNSCHEDULED 5.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>CL.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B166">
-        <v>14</v>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>AMBUL ECG REMOVAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>CL.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B167">
-        <v>15</v>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>6.1</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>UNSCHEDULED 6.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>CL.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B168">
-        <v>16</v>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>WEEK 6</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>CL.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B169">
-        <v>17</v>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>7.1</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>UNSCHEDULED 7.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>CL.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B170">
-        <v>18</v>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>WEEK 8</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>CL.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B171">
-        <v>19</v>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>8.1</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>WEEK 10 (T)</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>CL.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B172">
-        <v>20</v>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>8.2</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>UNSCHEDULED 8.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>CL.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B173">
-        <v>21</v>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>WEEK 12</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>CL.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B174">
-        <v>22</v>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>9.1</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>WEEK 14 (T)</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>CL.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B175">
-        <v>23</v>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>9.2</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>UNSCHEDULED 9.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>CL.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B176">
-        <v>24</v>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>9.3</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>UNSCHEDULED 9.3</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>CL.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B177">
-        <v>25</v>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>WEEK 16</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>CL.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B178">
-        <v>26</v>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>10.1</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>WEEK 18 (T)</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>CL.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B179">
-        <v>27</v>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>10.2</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>UNSCHEDULED 10.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>CL.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B180">
-        <v>28</v>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>WEEK 20</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>CL.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B181">
-        <v>29</v>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>11.1</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>WEEK 22 (T)</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>CL.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B182">
-        <v>30</v>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>11.2</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>UNSCHEDULED 11.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>CL.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B183">
-        <v>31</v>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>WEEK 24</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>CL.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B184">
-        <v>32</v>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>12.1</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>UNSCHEDULED 12.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>CL.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B185">
-        <v>33</v>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>WEEK 26</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>CL.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B186">
-        <v>34</v>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>13.1</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>UNSCHEDULED 13.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>CL.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B187">
-        <v>35</v>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>AE FOLLOW-UP</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>CL.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B188">
-        <v>36</v>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>RETRIEVAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>CL.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B189">
-        <v>37</v>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>501</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>Rash followup</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>CL.YN</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>CL.YN</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>CL.Y_BLANK</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>CL.AESEV</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>MILD</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>Grade 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>CL.AESEV</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>MODERATE</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>Grade 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>CL.AESEV</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>SEVERE</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>Grade 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>CL.AECAUS</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>CL.AECAUS</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>POSSIBLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>CL.AECAUS</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>PROBABLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>CL.AECAUS</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>REMOTE</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>CL.OUT</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>RECOVERED/RESOLVED</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>CL.OUT</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>NOT RECOVERED/NOT RESOLVED</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>CL.OUT</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
           <t>FATAL</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Outcome of Adverse Event</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>C66768</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>C48275</t>
         </is>
       </c>
     </row>
@@ -8636,7 +8885,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H55"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -8684,12 +8933,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MT.ADQSADAS.AVISIT</t>
+          <t>MT.ADSL.SITEGR1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MT.ADQSADAS.AVISIT</t>
+          <t>MT.ADSL.SITEGR1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -8699,19 +8948,19 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Derived based on windowing algorithm described in SAP, Section 8.2</t>
+          <t>refer to SAP, Section 7.1 - if not pooled then SITEGR1=SITEID. If pooled, SITEGR1 will be 900</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MT.ADQSADAS.ADY</t>
+          <t>MT.ADSL.TRTSDT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MT.ADQSADAS.ADY</t>
+          <t>MT.ADSL.TRTSDT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -8721,19 +8970,19 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ADY = ADT - TRTSDT + 1, if ADT&gt;=TRTSDT. ADY = ADT - TRTSDT, if ADT&lt;TRTSDT.</t>
+          <t>SV.SVSTDTC where SV.VISITNUM=3, converted to SAS date</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MT.ADQSADAS.ADT</t>
+          <t>MT.ADSL.TRTEDT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MT.ADQSADAS.ADT</t>
+          <t>MT.ADSL.TRTEDT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -8743,19 +8992,19 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SAS date from QS.QSDTC</t>
+          <t>The date of final dose (from the CRF) is EX.EXENDTC on the subject's last EX record. If the date of final dose is missing for the subject and the subject discontinued after visit 3, use the date of discontinuation as the date of last dose. Convert the date to a SAS date.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MT.ADQSADAS.BASE</t>
+          <t>MT.ADSL.TRTDURD</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MT.ADQSADAS.BASE</t>
+          <t>MT.ADSL.TRTDURD</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -8765,19 +9014,19 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>QS.QSSTRESN where QS.QSBLFL=Y (QS.VISITNUM=3)</t>
+          <t>TRTEDT-TRTSDT+1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MT.ADQSADAS.CHG</t>
+          <t>MT.ADSL.AVGDD</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MT.ADQSADAS.CHG</t>
+          <t>MT.ADSL.AVGDD</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -8787,19 +9036,19 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>AVAL - BASE</t>
+          <t>CUMDOSE/TRTDURD</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MT.ADQSADAS.PCHG</t>
+          <t>MT.ADSL.CUMDOSE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MT.ADQSADAS.PCHG</t>
+          <t>MT.ADSL.CUMDOSE</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -8808,182 +9057,6 @@
         </is>
       </c>
       <c r="D7" t="inlineStr">
-        <is>
-          <t>100* (CHG/BASE)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>MT.ADQSADAS.ANL01FL</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>MT.ADQSADAS.ANL01FL</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Computation</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>If multiple visits fall into the same visit window, then the one closest to the target day is chosen for analysis. These are flagged with ANL01FL="Y".</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>MT.ADQSADAS.AWTDIFF</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>MT.ADQSADAS.AWTDIFF</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Computation</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Absolute difference between AWTARGET and ADY</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>MT.ADSL.SITEGR1</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>MT.ADSL.SITEGR1</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Computation</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>refer to SAP, Section 7.1 - if not pooled then SITEGR1=SITEID. If pooled, SITEGR1 will be 900</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>MT.ADSL.TRTSDT</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>MT.ADSL.TRTSDT</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Computation</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>SV.SVSTDTC where SV.VISITNUM=3, converted to SAS date</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>MT.ADSL.TRTEDT</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>MT.ADSL.TRTEDT</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Computation</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>The date of final dose (from the CRF) is EX.EXENDTC on the subject's last EX record. If the date of final dose is missing for the subject and the subject discontinued after visit 3, use the date of discontinuation as the date of last dose. Convert the date to a SAS date.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>MT.ADSL.TRTDURD</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>MT.ADSL.TRTDURD</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Computation</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>TRTEDT-TRTSDT+1</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>MT.ADSL.AVGDD</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>MT.ADSL.AVGDD</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Computation</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>CUMDOSE/TRTDURD</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>MT.ADSL.CUMDOSE</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>MT.ADSL.CUMDOSE</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Computation</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
         <is>
           <t>For TRT01PN=0 or 54: CUMDOSE=TRT01PN*TRTDURD. 
 For TRT01PN=81: CUMDOSE will be based on 
@@ -8996,15 +9069,191 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>MT.ADSL.AGEGR1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>MT.ADSL.AGEGR1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Grouping of AGE into &lt;65, 65-80, and &gt;80</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>MT.ADSL.SAFFL</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>MT.ADSL.SAFFL</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Y if ITTFL='Y' and TRTSDT ne missing. N otherwise</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>MT.ADSL.ITTFL</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>MT.ADSL.ITTFL</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Y if ARMCD ne ' '. N otherwise</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>MT.ADSL.EFFFL</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>MT.ADSL.EFFFL</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Y if SAFFL='Y AND subject has at least one record in QS for ADAS-Cog with QS.VISITNUM&gt;3 AND at least one record in QS for CIBIC+ with QS.VISITNUM&gt;3, N otherwise</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>MT.ADSL.COMP8FL</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>MT.ADSL.COMP8FL</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Y if subject has a SV.VISITNUM=8 and TRTEDT&gt;= date of visit 8, N otherwise</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>MT.ADSL.COMP16FL</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>MT.ADSL.COMP16FL</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Y if subject has a SV.VISITNUM=10 and TRTEDT&gt;=date of visit 10, N otherwise</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>MT.ADSL.COMP24FL</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>MT.ADSL.COMP24FL</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Y if subject has a SV.VISITNUM=12 and TRTEDT&gt;= date of visit 12 , N otherwise</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>MT.ADSL.DISCONFL</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>MT.ADSL.DISCONFL</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Y if EOSSTT='DISCONTINUED'. Null otherwise</t>
+        </is>
+      </c>
+    </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MT.ADSL.AGEGR1</t>
+          <t>MT.ADSL.DSRAEFL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MT.ADSL.AGEGR1</t>
+          <t>MT.ADSL.DSRAEFL</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -9014,19 +9263,19 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Grouping of AGE into &lt;65, 65-80, and &gt;80</t>
+          <t>Y if DCSREAS='Adverse Event'. Null otherwise</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MT.ADSL.SAFFL</t>
+          <t>MT.ADSL.BMIBL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MT.ADSL.SAFFL</t>
+          <t>MT.ADSL.BMIBL</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -9036,19 +9285,19 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Y if ITTFL='Y' and TRTSDT ne missing. N otherwise</t>
+          <t>WEIGHTBL / ((HEIGHTBL*100)**2)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MT.ADSL.ITTFL</t>
+          <t>MT.ADSL.BMIBLGR1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MT.ADSL.ITTFL</t>
+          <t>MT.ADSL.BMIBLGR1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -9058,19 +9307,19 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Y if ARMCD ne ' '. N otherwise</t>
+          <t>BMIBLGR1=Normal if . &lt; BMIBL &lt;25. BMIBLGR1=Overweight if 25 &lt;=BMIBL &lt;30. BMIBLGR1=Obese if BMIBL &gt;=30</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MT.ADSL.EFFFL</t>
+          <t>MT.ADSL.HEIGHTBL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MT.ADSL.EFFFL</t>
+          <t>MT.ADSL.HEIGHTBL</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -9080,19 +9329,19 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Y if SAFFL='Y AND subject has at least one record in QS for ADAS-Cog with QS.VISITNUM&gt;3 AND at least one record in QS for CIBIC+ with QS.VISITNUM&gt;3, N otherwise</t>
+          <t>VS.VSSTRESN where VS.VSTESTCD='HEIGHT' and VS.VISITNUM=1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MT.ADSL.COMP8FL</t>
+          <t>MT.ADSL.WEIGHTBL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MT.ADSL.COMP8FL</t>
+          <t>MT.ADSL.WEIGHTBL</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -9102,19 +9351,19 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Y if subject has a SV.VISITNUM=8 and TRTEDT&gt;= date of visit 8, N otherwise</t>
+          <t>VS.VSSTRESN where VS.VSTESTCD='WEIGHT' and VS.VISITNUM=3</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MT.ADSL.COMP16FL</t>
+          <t>MT.ADSL.EDUCLVL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MT.ADSL.COMP16FL</t>
+          <t>MT.ADSL.EDUCLVL</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -9124,19 +9373,19 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Y if subject has a SV.VISITNUM=10 and TRTEDT&gt;=date of visit 10, N otherwise</t>
+          <t>SC.SCSTRESN where SC.SCTESTCD="EDLEVEL"</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MT.ADSL.COMP24FL</t>
+          <t>MT.ADSL.DISONDT</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MT.ADSL.COMP24FL</t>
+          <t>MT.ADSL.DISONDT</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -9146,19 +9395,19 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Y if subject has a SV.VISITNUM=12 and TRTEDT&gt;= date of visit 12 , N otherwise</t>
+          <t>MH.MHSTDTC where MH.MHCAT='PRIMARY DIAGNOSIS' converted to SAS date</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MT.ADSL.DISCONFL</t>
+          <t>MT.ADSL.DURDIS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MT.ADSL.DISCONFL</t>
+          <t>MT.ADSL.DURDIS</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -9168,19 +9417,19 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Y if EOSSTT='DISCONTINUED'. Null otherwise</t>
+          <t>number of months between Date of VISIT 1 and DISONDT</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MT.ADSL.DSRAEFL</t>
+          <t>MT.ADSL.DURDSGR1</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MT.ADSL.DSRAEFL</t>
+          <t>MT.ADSL.DURDSGR1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -9190,19 +9439,19 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Y if DCSREAS='Adverse Event'. Null otherwise</t>
+          <t>grouping DURDIS values as &lt;12 and &gt;=12</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MT.ADSL.BMIBL</t>
+          <t>MT.ADSL.VISIT1DT</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MT.ADSL.BMIBL</t>
+          <t>MT.ADSL.VISIT1DT</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -9212,19 +9461,19 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>WEIGHTBL / ((HEIGHTBL*100)**2)</t>
+          <t>SV.SVSTDTC where SV.VISITNUM=1, converted to SAS date</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MT.ADSL.BMIBLGR1</t>
+          <t>MT.ADSL.VISNUMEN</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MT.ADSL.BMIBLGR1</t>
+          <t>MT.ADSL.VISNUMEN</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -9234,19 +9483,19 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>BMIBLGR1=Normal if . &lt; BMIBL &lt;25. BMIBLGR1=Overweight if 25 &lt;=BMIBL &lt;30. BMIBLGR1=Obese if BMIBL &gt;=30</t>
+          <t>If DS.VISITNUM=13 where DS.DSTERM='PROTOCOL COMPLETED' then VISNUMEN=12, otherwise VISNUMEN=DS.VISITNUM where DS.DSTERM='PROTOCOL COMPLETED'</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MT.ADSL.HEIGHTBL</t>
+          <t>MT.ADSL.RFENDT</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MT.ADSL.HEIGHTBL</t>
+          <t>MT.ADSL.RFENDT</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -9256,19 +9505,19 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VS.VSSTRESN where VS.VSTESTCD='HEIGHT' and VS.VISITNUM=1</t>
+          <t>RFENDTC converted to SAS date</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>MT.ADSL.WEIGHTBL</t>
+          <t>MT.ADSL.EOSSTT</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>MT.ADSL.WEIGHTBL</t>
+          <t>MT.ADSL.EOSSTT</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -9278,19 +9527,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VS.VSSTRESN where VS.VSTESTCD='WEIGHT' and VS.VISITNUM=3</t>
+          <t>If DS.DSDECOD='COMPLETED' then EOSSTT='COMPLETED'. Otherwise EOSSTT='DISCONTINUED'.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MT.ADSL.EDUCLVL</t>
+          <t>MT.ADSL.DCSREAS</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MT.ADSL.EDUCLVL</t>
+          <t>MT.ADSL.DCSREAS</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -9300,19 +9549,19 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>SC.SCSTRESN where SC.SCTESTCD="EDLEVEL"</t>
+          <t>If DS.DSCAT='DISPOSITION EVENT' and DS.DSTERM in('I/E NOT MET' 'SPONSOR DECISION' 'WITHDREW CONSENT') then DCSREAS=DS.DSTERM. Otherwise if DS.DSCAT='DISPOSITION EVENT' then DCSREAS=DS.DSDECOD. Convert to mixed case to match display format.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MT.ADSL.DISONDT</t>
+          <t>MT.ADSL.MMS1TSBL</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>MT.ADSL.DISONDT</t>
+          <t>MT.ADSL.MMS1TSBL</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -9322,19 +9571,19 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>MH.MHSTDTC where MH.MHCAT='PRIMARY DIAGNOSIS' converted to SAS date</t>
+          <t>Sum of FT.FTSTRESN values where FT.FTCAT="MMSE" for the subject (FT.FTTESTCD= 'MMS101A'-'MMS111')</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MT.ADSL.DURDIS</t>
+          <t>MT.ADAE.ASTDT</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>MT.ADSL.DURDIS</t>
+          <t>MT.ADAE.ASTDT</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -9344,19 +9593,19 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>number of months between Date of VISIT 1 and DISONDT</t>
+          <t>AE.AESTDTC, converted to a numeric SAS date. Some events with partial dates are imputed in a conservative manner. If the day component is missing, a value of '01' is used. If both the month and day are missing no imputation is performed as these dates clearly indicate a start prior to the beginning of treatment. There are no events with completely missing start dates.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MT.ADSL.DURDSGR1</t>
+          <t>MT.ADAE.ASTDTF</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>MT.ADSL.DURDSGR1</t>
+          <t>MT.ADAE.ASTDTF</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -9366,19 +9615,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>grouping DURDIS values as &lt;12 and &gt;=12</t>
+          <t>ASTDTF='D' if the day value within the character date is imputed. Note that only day values needed to be imputed for this study</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MT.ADSL.VISIT1DT</t>
+          <t>MT.ADAE.ASTDY</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>MT.ADSL.VISIT1DT</t>
+          <t>MT.ADAE.ASTDY</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -9388,19 +9637,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>SV.SVSTDTC where SV.VISITNUM=1, converted to SAS date</t>
+          <t>IF ASTDT&gt;=TRTSDT&gt;MISSING then ASTDY=ASTDT-TRTSDT+1 Else if TRTSDT&gt;ASTDT&gt;MISSING then ASTDY=ASTDT-TRTSDT</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MT.ADSL.VISNUMEN</t>
+          <t>MT.ADAE.AENDT</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>MT.ADSL.VISNUMEN</t>
+          <t>MT.ADAE.AENDT</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -9410,19 +9659,19 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>If DS.VISITNUM=13 where DS.DSTERM='PROTOCOL COMPLETED' then VISNUMEN=12, otherwise VISNUMEN=DS.VISITNUM where DS.DSTERM='PROTOCOL COMPLETED'</t>
+          <t>AE.AEENDTC, converted to a numeric SAS date</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MT.ADSL.RFENDT</t>
+          <t>MT.ADAE.AENDY</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>MT.ADSL.RFENDT</t>
+          <t>MT.ADAE.AENDY</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -9432,19 +9681,19 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>RFENDTC converted to SAS date</t>
+          <t>IF AENDT&gt;=TRTSDT&gt;MISSING then AENDY=AENDT-TRTSDT+1 Else if TRTSDT&gt;AENDT&gt;MISSING then AENDY=AENDT-TRTSDT</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MT.ADSL.EOSSTT</t>
+          <t>MT.ADAE.ADURN</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>MT.ADSL.EOSSTT</t>
+          <t>MT.ADAE.ADURN</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -9454,19 +9703,19 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>If DS.DSDECOD='COMPLETED' then EOSSTT='COMPLETED'. Otherwise EOSSTT='DISCONTINUED'.</t>
+          <t>ADURN=AENDT-ASTDT+1</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MT.ADSL.DCSREAS</t>
+          <t>MT.ADAE.ADURU</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>MT.ADSL.DCSREAS</t>
+          <t>MT.ADAE.ADURU</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -9476,19 +9725,19 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>If DS.DSCAT='DISPOSITION EVENT' and DS.DSTERM in('I/E NOT MET' 'SPONSOR DECISION' 'WITHDREW CONSENT') then DCSREAS=DS.DSTERM. Otherwise if DS.DSCAT='DISPOSITION EVENT' then DCSREAS=DS.DSDECOD. Convert to mixed case to match display format.</t>
+          <t>If ADURN is not missing then ADURU='DAY'</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MT.ADSL.MMS1TSBL</t>
+          <t>MT.ADAE.TRTEMFL</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>MT.ADSL.MMS1TSBL</t>
+          <t>MT.ADAE.TRTEMFL</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -9498,19 +9747,19 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Sum of FT.FTSTRESN values where FT.FTCAT="MMSE" for the subject (FT.FTTESTCD= 'MMS101A'-'MMS111')</t>
+          <t>If ASTDT &gt;= TRTSDT &gt; . then TRTEMFL='Y'. Otherwise TRTEMFL='N'</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MT.ADQSADAS.AVAL.ACTOT</t>
+          <t>MT.ADAE.AOCCFL</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>MT.ADQSADAS.AVAL.ACTOT</t>
+          <t>MT.ADAE.AOCCFL</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -9520,29 +9769,19 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Sum of ADAS scores for items 1, 2, 4, 5, 6, 7, 8, 11, 12, 13, and 14, see ADRG for details on adjusting for missing values.</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>LF.ADRG</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>Subset to TRTEMFL='Y' and sort by Subject (USUBJID), Start Date (ASTDT), and Sequence Number (AESEQ) and flag the first record (set AOCCFL=’Y’) within each Subject</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>MT.ADAE.ASTDT</t>
+          <t>MT.ADAE.AOCCSFL</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>MT.ADAE.ASTDT</t>
+          <t>MT.ADAE.AOCCSFL</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -9552,19 +9791,19 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>AE.AESTDTC, converted to a numeric SAS date. Some events with partial dates are imputed in a conservative manner. If the day component is missing, a value of '01' is used. If both the month and day are missing no imputation is performed as these dates clearly indicate a start prior to the beginning of treatment. There are no events with completely missing start dates.</t>
+          <t>Subset to TRTEMFL='Y' and sort by Subject (USUBJID), System Organ Class (AEBODSYS), Start Date (ASTDT), and Sequence Number (AESEQ) and flag the first record (set AOCCSFL=’Y’) within each Subject and SOC</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MT.ADAE.ASTDTF</t>
+          <t>MT.ADAE.AOCCPFL</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>MT.ADAE.ASTDTF</t>
+          <t>MT.ADAE.AOCCPFL</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -9574,19 +9813,19 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ASTDTF='D' if the day value within the character date is imputed. Note that only day values needed to be imputed for this study</t>
+          <t>Subset to TRTEMFL='Y' and sort by Subject (USUBJID), System Organ Class (AEBODSYS), Preferred Term (AEDECOD), Start Date (ASTDT), and Sequence Number (AESEQ) and flag the first record (set AOCCPFL=’Y’) within each Subject, SOC, and PT</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>MT.ADAE.ASTDY</t>
+          <t>MT.ADAE.AOCC02FL</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>MT.ADAE.ASTDY</t>
+          <t>MT.ADAE.AOCC02FL</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -9596,19 +9835,19 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>IF ASTDT&gt;=TRTSDT&gt;MISSING then ASTDY=ASTDT-TRTSDT+1 Else if TRTSDT&gt;ASTDT&gt;MISSING then ASTDY=ASTDT-TRTSDT</t>
+          <t>Subset to TRTEMFL='Y' and AESER='Y' and sort by Subject (USUBJID), Start Date (ASTDT), and Sequence Number (AESEQ) and flag the first record (set AOCC02FL=’Y’) within each Subject</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MT.ADAE.AENDT</t>
+          <t>MT.ADAE.AOCC03FL</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>MT.ADAE.AENDT</t>
+          <t>MT.ADAE.AOCC03FL</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -9618,19 +9857,19 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>AE.AEENDTC, converted to a numeric SAS date</t>
+          <t>Subset to TRTEMFL='Y' and AESER='Y' and sort by Subject (USUBJID), System Organ Class (AEBODSYS), Start Date (ASTDT), and Sequence Number (AESEQ) and flag the first record (set AOCC03FL=’Y’) within each Subject and SOC</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MT.ADAE.AENDY</t>
+          <t>MT.ADAE.AOCC04FL</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>MT.ADAE.AENDY</t>
+          <t>MT.ADAE.AOCC04FL</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -9640,19 +9879,19 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>IF AENDT&gt;=TRTSDT&gt;MISSING then AENDY=AENDT-TRTSDT+1 Else if TRTSDT&gt;AENDT&gt;MISSING then AENDY=AENDT-TRTSDT</t>
+          <t>Subset to TRTEMFL='Y' and AESER='Y' and sort by Subject (USUBJID), System Organ Class (AEBODSYS), Preferred Term (AEDECOD), Start Date (ASTDT), and Sequence Number (AESEQ) and flag the first record (set AOCC04FL=’Y’) within each Subject, SOC, and PT</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MT.ADAE.ADURN</t>
+          <t>MT.ADAE.CQ01NAM</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>MT.ADAE.ADURN</t>
+          <t>MT.ADAE.CQ01NAM</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -9662,19 +9901,19 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ADURN=AENDT-ASTDT+1</t>
+          <t>If AEDECOD contains any of the character strings of ('APPLICATION', 'DERMATITIS', 'ERYTHEMA', 'BLISTER') OR if AEBODSYS='SKIN AND SUBC UTANEOUS TISSUE DISORDERS' but AEDECOD is not in ('COLD SWEAT', 'HYPERHIDROSIS', 'ALOPECIA') then CQ01NAM='DERMATOLOGIC EVENTS' Otherwise CQ01NAM=NULL</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MT.ADAE.ADURU</t>
+          <t>MT.ADAE.AOCC01FL</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>MT.ADAE.ADURU</t>
+          <t>MT.ADAE.AOCC01FL</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -9683,204 +9922,6 @@
         </is>
       </c>
       <c r="D46" t="inlineStr">
-        <is>
-          <t>If ADURN is not missing then ADURU='DAY'</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>MT.ADAE.TRTEMFL</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>MT.ADAE.TRTEMFL</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Computation</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>If ASTDT &gt;= TRTSDT &gt; . then TRTEMFL='Y'. Otherwise TRTEMFL='N'</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>MT.ADAE.AOCCFL</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>MT.ADAE.AOCCFL</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Computation</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Subset to TRTEMFL='Y' and sort by Subject (USUBJID), Start Date (ASTDT), and Sequence Number (AESEQ) and flag the first record (set AOCCFL=’Y’) within each Subject</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>MT.ADAE.AOCCSFL</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>MT.ADAE.AOCCSFL</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Computation</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Subset to TRTEMFL='Y' and sort by Subject (USUBJID), System Organ Class (AEBODSYS), Start Date (ASTDT), and Sequence Number (AESEQ) and flag the first record (set AOCCSFL=’Y’) within each Subject and SOC</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>MT.ADAE.AOCCPFL</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>MT.ADAE.AOCCPFL</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Computation</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Subset to TRTEMFL='Y' and sort by Subject (USUBJID), System Organ Class (AEBODSYS), Preferred Term (AEDECOD), Start Date (ASTDT), and Sequence Number (AESEQ) and flag the first record (set AOCCPFL=’Y’) within each Subject, SOC, and PT</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>MT.ADAE.AOCC02FL</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>MT.ADAE.AOCC02FL</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Computation</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Subset to TRTEMFL='Y' and AESER='Y' and sort by Subject (USUBJID), Start Date (ASTDT), and Sequence Number (AESEQ) and flag the first record (set AOCC02FL=’Y’) within each Subject</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>MT.ADAE.AOCC03FL</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>MT.ADAE.AOCC03FL</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Computation</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Subset to TRTEMFL='Y' and AESER='Y' and sort by Subject (USUBJID), System Organ Class (AEBODSYS), Start Date (ASTDT), and Sequence Number (AESEQ) and flag the first record (set AOCC03FL=’Y’) within each Subject and SOC</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>MT.ADAE.AOCC04FL</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>MT.ADAE.AOCC04FL</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Computation</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Subset to TRTEMFL='Y' and AESER='Y' and sort by Subject (USUBJID), System Organ Class (AEBODSYS), Preferred Term (AEDECOD), Start Date (ASTDT), and Sequence Number (AESEQ) and flag the first record (set AOCC04FL=’Y’) within each Subject, SOC, and PT</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>MT.ADAE.CQ01NAM</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>MT.ADAE.CQ01NAM</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Computation</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>If AEDECOD contains any of the character strings of ('APPLICATION', 'DERMATITIS', 'ERYTHEMA', 'BLISTER') OR if AEBODSYS='SKIN AND SUBC UTANEOUS TISSUE DISORDERS' but AEDECOD is not in ('COLD SWEAT', 'HYPERHIDROSIS', 'ALOPECIA') then CQ01NAM='DERMATOLOGIC EVENTS' Otherwise CQ01NAM=NULL</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>MT.ADAE.AOCC01FL</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>MT.ADAE.AOCC01FL</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Computation</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
         <is>
           <t>Subset to CQ01NAM='' and TRTEMFL='Y' and sort by Subject (USUBJID), Start Date (ASTDT), and Sequence Number (AESEQ) and flag the first record (set AOCC01FL=’Y’) within each Subject (Flag First Treatment Emergent Dermatological Event for Time to Event Analysis)</t>
         </is>
@@ -9893,7 +9934,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -9955,243 +9996,106 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>COM.ADQSADAS</t>
+          <t>COM.JOIN-ADSL-ADAE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>See referenced dataset creation program and ADRG</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>LF.ADQSADAS.PGM</t>
+          <t>Get denominators for percentages from ADSL and counts and numerators from ADAE. Join ADAE with ADSL based on the unique subject identifier (USUBJID) keeping only records in ADAE for the numerator.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>COM.JOIN-ADSL-ADAE</t>
+          <t>COM.ADSL.TRT01PN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Get denominators for percentages from ADSL and counts and numerators from ADAE. Join ADAE with ADSL based on the unique subject identifier (USUBJID) keeping only records in ADAE for the numerator.</t>
+          <t>Numeric code for TRT01P</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>COM.ADQSADAS.AVISITN</t>
+          <t>COM.ADSL.TRT01A</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Numeric code for AVISIT</t>
+          <t>TRT01A=TRT01P, i.e., no difference between actual and randomized treatment in this study.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>COM.ADQSADAS.PARAMN</t>
+          <t>COM.ADSL.TRT01AN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Numeric code for PARAM</t>
+          <t>Numeric code for TRT01A</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>COM.ADQSADAS.AWRANGE</t>
+          <t>COM.ADSL.AGEGR1N</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Window range, specified in the SAP.</t>
+          <t>Numeric code for AGEGR1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>COM.ADQSADAS.AWTARGET</t>
+          <t>COM.ADSL.RACEN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Target day within the window, specified in the SAP.</t>
+          <t>Numeric code for RACE</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>COM.ADQSADAS.AWLO</t>
+          <t>COM.STDCT.01</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Start day of the window, specified in the SAP.</t>
+          <t>ADaM specific CT is applicable for a few variables only.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>COM.ADQSADAS.AWHI</t>
+          <t>COM.STDCT.02</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>End day of the window, specified in the SAP.</t>
+          <t>SDTM CT is applicable for variables copied from SDTM to ADaM.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>COM.ADQSADAS.AWU</t>
+          <t>COM.STD5</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
-        <is>
-          <t>Assigned as "DAYS".</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>COM.ADSL.TRT01PN</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Numeric code for TRT01P</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>COM.ADSL.TRT01A</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>TRT01A=TRT01P, i.e., no difference between actual and randomized treatment in this study.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>COM.ADSL.TRT01AN</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Numeric code for TRT01A</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>COM.ADSL.AGEGR1N</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Numeric code for AGEGR1</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>COM.ADSL.RACEN</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Numeric code for RACE</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>COM.ADQSADAS.DTYPE.ACITM01-ACITM14</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Value: null</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>COM.ADQSADAS.DTYPE.ACTOT</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Value: LOCF denotes that the LOCF imputation method was used to impute the value for the given parameter and analysis visit.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>COM.ADQSADAS.QSSEQ.ACTOT</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Set QSSEQ to missing for post baseline records. Set to QS.QSSEQ where QS.VISIT=BASELINE and QS.QSTESTCD=ACTOT.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>COM.STDCT.01</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>ADaM specific CT is applicable for a few variables only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>COM.STDCT.02</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>SDTM CT is applicable for variables copied from SDTM to ADaM.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>COM.STD5</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
         <is>
           <t>This is the CDISC CT Package 60 (2025-09-26) associated to the CDISC Define-XML Specification Version 2.1.10.</t>
         </is>
@@ -10204,7 +10108,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -10223,6 +10127,11 @@
           <t>Href</t>
         </is>
       </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10240,6 +10149,11 @@
           <t>adsl.xpt</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>archive</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10257,6 +10171,11 @@
           <t>adqsadas.xpt</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>archive</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10274,6 +10193,11 @@
           <t>adae.xpt</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>archive</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10291,89 +10215,331 @@
           <t>adrg.pdf</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>supplemental</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LF.ADQSADAS.PGM</t>
+          <t>LF.CODE.001</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>adqsadas.sas</t>
+          <t>adae.sas</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>../programs/adqsadas-sas.txt</t>
+          <t>../programs/adae-sas.txt</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LF.CODE.001</t>
+          <t>LF.ADSL.PGM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>adae.sas</t>
+          <t>adsl.sas</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>../programs/adae-sas.txt</t>
+          <t>../programs/adsl-sas.txt</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LF.ADSL.PGM</t>
+          <t>LF.CSR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>adsl.sas</t>
+          <t>Clinical Study Report</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>../programs/adsl-sas.txt</t>
+          <t>../dummy-csr/dummy-csr.pdf</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LF.CSR</t>
+          <t>LF.at14-5-02.sas</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Clinical Study Report</t>
+          <t>at14-5-02.sas</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>../dummy-csr/dummy-csr.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>LF.at14-5-02.sas</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>at14-5-02.sas</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
           <t>../programs/at14-5-02-sas.txt</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Comparator</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>WC.Table_14-5.02.R.1.ADAE</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ADAE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>TRTEMFL</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>EQ</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>WC.Table_14-5.02.R.1.ADAE</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ADAE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>AESER</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>EQ</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>WC.Table_14-5.02.R.1.ADSL</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ADSL</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>SAFFL</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>EQ</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Dictionary</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Version</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Href</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CL.AEDICT</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Adverse Event Dictionary</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>MedDRA</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>http://www.meddra.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CL.AEDICTN</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Adverse Event Dictionary (N)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>MedDRA</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>http://www.meddra.org/</t>
         </is>
       </c>
     </row>
